--- a/data/export/batch1.xlsx
+++ b/data/export/batch1.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5592,27 +5592,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Biomedical Engineering</t>
+          <t>Psychological &amp; Brain Sciences; Graduate Program for Neuroscience (faculty); Center for Systems Neuroscience</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Junjie Yao</t>
+          <t>Arthur Lee</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jeffrey N. Vinik Associate Professor of Biomedical Engineering</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5622,48 +5622,44 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>medical-AI</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Photoacoustic tomography technology and image reconstruction for functional brain imaging and cancer.</t>
+          <t>Card has no research text or papers.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>junjie.yao@duke.edu</t>
+          <t>artlee@bu.edu</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>https://bme.duke.edu/people/junjie-yao/</t>
+          <t>https://www.bu.edu/psych/profile/arthur-sangil-lee/</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://photoacoustics.pratt.duke.edu/</t>
+          <t>http://thedecodinglab.com/</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>“Three-dimensional photoacoustic tomography with ultrasound localization priors.” Photoacoustics 51 (October 2026)</t>
+          <t>Neural decoders: saving the baby from the bathwater</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>“Noninvasive whole-brain imaging of glymphatic dynamics.” Sci Adv 12, no. 25 (June 19, 2026)</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Flexible ultrasound array for subcortical brain stimulation in humans: a simulation study (2026) | Hepatocyte hedgehog signaling controls ferroptosis to alleviate aging-related organ dysfunction (2026)</t>
-        </is>
-      </c>
+          <t>Distinguishing deception from its confounds by improving the validity of fMRI-based neural prediction</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>https://bme.duke.edu/people/page/3/?group=faculty</t>
+          <t>https://www.bu.edu/psych/people/faculty/</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5673,20 +5669,28 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Yes: There are typically 1-2 openings for graduate students each year. Candidates should apply to the Biomedical Engineering Department and specify interest in working with Dr. Yao</t>
+          <t>Yes: We are looking for Ph.D. students interested in our research.</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Please feel free to send an email to Arthur (see contact) to let him know to look out for your application.</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>His interest in validating neural decoders (confounds, interpretability) connects to the EEG motor-imagery decoder with run-grouped validation.</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>imaging hardware/optics lab, ML is secondary; associate professor; start year not found (lab 'Founded in 2016')</t>
+          <t>psychology department; applications go through Psychology or Neuroscience program, not CS/Stats</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+; dossier reader says C: Downgraded B-&gt;C: lab builds photoacoustic/ultrasound systems; computational work is a minor part and no applicant projec</t>
+          <t>also listed as Arthur Sangil Lee</t>
         </is>
       </c>
     </row>
@@ -5701,17 +5705,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Biostatistics &amp; Bioinformatics (SOM)</t>
+          <t>Biomedical Engineering</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Lin Lin</t>
+          <t>Junjie Yao</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Associate Professor of Biostatistics &amp; Bioinformatics</t>
+          <t>Jeffrey N. Vinik Associate Professor of Biomedical Engineering</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5731,39 +5735,43 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Cytometry-based outcome prediction (cytoGPNet) alongside transplant and lung cancer immune studies.</t>
+          <t>Photoacoustic tomography technology and image reconstruction for functional brain imaging and cancer.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>lynn.lin@duke.edu</t>
+          <t>junjie.yao@duke.edu</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/profile/lin-lin</t>
+          <t>https://bme.duke.edu/people/junjie-yao/</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/profile/lin-lin</t>
+          <t>https://photoacoustics.pratt.duke.edu/</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>cytoGPNet: Enhancing clinical outcome prediction accuracy using longitudinal cytometry data in small cohort studies</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr"/>
+          <t>“Three-dimensional photoacoustic tomography with ultrasound localization priors.” Photoacoustics 51 (October 2026)</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>“Noninvasive whole-brain imaging of glymphatic dynamics.” Sci Adv 12, no. 25 (June 19, 2026)</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>CD154 blockade effectively controls antibody-mediated rejection in highly sensitized nonhuman primate kidney transplant recipients (2025) | Perioperative pembrolizumab in early-stage non-small cell lung cancer (NSCLC): conventional and distribution-based immune profiling of the tumor microenvironment and peripheral circulation (2025)</t>
+          <t>Flexible ultrasound array for subcortical brain stimulation in humans: a simulation study (2026) | Hepatocyte hedgehog signaling controls ferroptosis to alleviate aging-related organ dysfunction (2026)</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/people/faculty?page=3</t>
+          <t>https://bme.duke.edu/people/page/3/?group=faculty</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -5773,24 +5781,20 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unspecified: </t>
+          <t>Yes: There are typically 1-2 openings for graduate students each year. Candidates should apply to the Biomedical Engineering Department and specify interest in working with Dr. Yao</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Her cytoGPNet work on prediction in small cohorts relates to the applicant's leakage-aware, multi-seed evaluation of the arborphy fusion model.</t>
-        </is>
-      </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
-          <t>no lab site found (1 search + 1 targeted); paper page is a journal article, not her own publications page; associate professor; promotion year not found; recruiting info not found</t>
+          <t>imaging hardware/optics lab, ML is secondary; associate professor; start year not found (lab 'Founded in 2016')</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+; fit based on name-matched papers only: check they are this person's</t>
+          <t>associate: confirm promoted 2020+; dossier reader says C: Downgraded B-&gt;C: lab builds photoacoustic/ultrasound systems; computational work is a minor part and no applicant projec</t>
         </is>
       </c>
     </row>
@@ -5810,17 +5814,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Pan Xu</t>
+          <t>Lin Lin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biostatistics &amp; Bioinformatics</t>
+          <t>Associate Professor of Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5835,43 +5839,39 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Reinforcement learning for decision support in ECMO management.</t>
+          <t>Cytometry-based outcome prediction (cytoGPNet) alongside transplant and lung cancer immune studies.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>pan.xu@duke.edu</t>
+          <t>lynn.lin@duke.edu</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/profile/pan-xu</t>
+          <t>https://biostat.duke.edu/profile/lin-lin</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://panxulab.github.io/</t>
+          <t>https://biostat.duke.edu/profile/lin-lin</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Extremely Sparse Supervision Incentivizes Reasoning Ability</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Decoupled Marginal Sharpening for Training-Free Inference-Time Scaling</t>
-        </is>
-      </c>
+          <t>cytoGPNet: Enhancing clinical outcome prediction accuracy using longitudinal cytometry data in small cohort studies</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>rECMOmender: Reinforcement Learning for Decision Support in Venovenous Extracorporeal Membrane Oxygenation Management (2026)</t>
+          <t>CD154 blockade effectively controls antibody-mediated rejection in highly sensitized nonhuman primate kidney transplant recipients (2025) | Perioperative pembrolizumab in early-stage non-small cell lung cancer (NSCLC): conventional and distribution-based immune profiling of the tumor microenvironment and peripheral circulation (2025)</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/people/faculty?page=6</t>
+          <t>https://biostat.duke.edu/people/faculty?page=3</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5881,24 +5881,24 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes: I am always happy to collaborate with highly motivated and self-driven students who are genuinely interested in our research. Before contacting me, please take the time to carefully read at least one </t>
+          <t xml:space="preserve">Unspecified: </t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>His 'Extremely Sparse Supervision' paper runs on-policy distillation experiments on the Qwen3 family, which touches the applicant's Qwen3 probing/steering interp work (evaluation-focused, not a causal claim).</t>
+          <t>Her cytoGPNet work on prediction in small cohorts relates to the applicant's leakage-aware, multi-seed evaluation of the arborphy fusion model.</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>site requires reading a lab paper and a specific 5-8 sentence note (CV + which paper/why/background) before he replies; start year not stated; original panxu-ai.github.io redirects to panxulab.github.io</t>
+          <t>no lab site found (1 search + 1 targeted); paper page is a journal article, not her own publications page; associate professor; promotion year not found; recruiting info not found</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>dossier reader says A: Upgraded B-&gt;A: ML-core (RL, LLMs, data-efficient learning), tenure-track assistant professor with healthcare application</t>
+          <t>associate: confirm promoted 2020+; fit based on name-matched papers only: check they are this person's</t>
         </is>
       </c>
     </row>
@@ -5913,12 +5913,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Biostatistics &amp; Bioinformatics (SOM); CBB program</t>
+          <t>Biostatistics &amp; Bioinformatics (SOM)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Pixu Shi</t>
+          <t>Pan Xu</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5938,40 +5938,48 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>AI-for-science</t>
+          <t>medical-AI</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Trajectory-guided dimensionality reduction for multi-sample single-cell RNA-seq data.</t>
+          <t>Reinforcement learning for decision support in ECMO management.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>pixu.shi@duke.edu</t>
+          <t>pan.xu@duke.edu</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/profile/pixu-shi</t>
+          <t>https://biostat.duke.edu/profile/pan-xu</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/profile/pixu-shi</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
+          <t>https://panxulab.github.io/</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Extremely Sparse Supervision Incentivizes Reasoning Ability</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Decoupled Marginal Sharpening for Training-Free Inference-Time Scaling</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Branched chain amino acid metabolism and microbiome in adolescents with obesity during weight loss therapy (2026) | Characterizing the composition and diversity of the vaginal microbiome in ovarian cancer (2026)</t>
+          <t>rECMOmender: Reinforcement Learning for Decision Support in Venovenous Extracorporeal Membrane Oxygenation Management (2026)</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/people/faculty?page=5</t>
+          <t>https://biostat.duke.edu/people/faculty?page=6</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5981,20 +5989,24 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unspecified: </t>
+          <t xml:space="preserve">Yes: I am always happy to collaborate with highly motivated and self-driven students who are genuinely interested in our research. Before contacting me, please take the time to carefully read at least one </t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>His 'Extremely Sparse Supervision' paper runs on-policy distillation experiments on the Qwen3 family, which touches the applicant's Qwen3 probing/steering interp work (evaluation-focused, not a causal claim).</t>
+        </is>
+      </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>no lab/personal site found (1 search); official profile has no research text; her 2026 Bioinformatics paper is listed only on Wenpin Hou's page, not hers, so not recorded as paper; recruiting info not found</t>
+          <t>site requires reading a lab paper and a specific 5-8 sentence note (CV + which paper/why/background) before he replies; start year not stated; original panxu-ai.github.io redirects to panxulab.github.io</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>fit based on name-matched papers only: check they are this person's</t>
+          <t>dossier reader says A: Upgraded B-&gt;A: ML-core (RL, LLMs, data-efficient learning), tenure-track assistant professor with healthcare application</t>
         </is>
       </c>
     </row>
@@ -6014,12 +6026,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wenpin Hou</t>
+          <t>Pixu Shi</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Assistant Professor in Biostatistics &amp; Bioinformatics</t>
+          <t>Assistant Professor of Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6039,47 +6051,35 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>AI-agent network structure compared with human social networks; scRNA dimensionality reduction.</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>multi-agent LLM systems</t>
-        </is>
-      </c>
+          <t>Trajectory-guided dimensionality reduction for multi-sample single-cell RNA-seq data.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>wenpin.hou@duke.edu</t>
+          <t>pixu.shi@duke.edu</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/profile/wenpin-hou</t>
+          <t>https://biostat.duke.edu/profile/pixu-shi</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://winnie09.github.io/Wenpin_Hou</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>MethylProphet: A Generalized Gene-Contextual Model for Inferring Whole-Genome DNA Methylation Landscape</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>Benchmarking large language models for genomic knowledge with GeneTuring</t>
-        </is>
-      </c>
+          <t>https://biostat.duke.edu/profile/pixu-shi</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Structural Divergence Between the Moltbook AI-Agent Network and Human Social Networks (2026) | Trajectory-guided dimensionality reduction for multi-sample single-cell RNA-seq data reveals biologically relevant sample-level heterogeneity (2026)</t>
+          <t>Branched chain amino acid metabolism and microbiome in adolescents with obesity during weight loss therapy (2026) | Characterizing the composition and diversity of the vaginal microbiome in ovarian cancer (2026)</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/people/faculty?page=2</t>
+          <t>https://biostat.duke.edu/people/faculty?page=5</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -6089,26 +6089,20 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Yes: I have fundings to support 1-2 PhD students. If you are interested, please send me your CV and, at the same time, list me as your preferred mentor in your PhD application.</t>
-        </is>
-      </c>
-      <c r="T56" t="n">
-        <v>2026</v>
-      </c>
+          <t xml:space="preserve">Unspecified: </t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Her multimodal representation learning / foundation models for cells and 'one-shot learning and interpretability' paper connect to the applicant's BioCLIP-based fusion work and leakage-aware evaluation (arborphy).</t>
-        </is>
-      </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
-          <t>start year 2026 inferred from Feb 2026 'Meet' article; Columbia appointment (research leave) still held; applicant is a Columbia student: lab collaborates with Columbia, mention nothing beyond applicant.yaml</t>
+          <t>no lab/personal site found (1 search); official profile has no research text; her 2026 Bioinformatics paper is listed only on Wenpin Hou's page, not hers, so not recorded as paper; recruiting info not found</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>fit based on name-matched papers only: check they are this person's; dossier reader says A: Upgraded B-&gt;A: Bio-AI foundation-model lab, new Duke assistant professor, explicitly funded for 1-2 PhD students and sta</t>
+          <t>fit based on name-matched papers only: check they are this person's</t>
         </is>
       </c>
     </row>
@@ -6118,27 +6112,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Icahn School of Medicine at Mount Sinai</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Diagnostic, Molecular and Interventional Radiology</t>
+          <t>Biostatistics &amp; Bioinformatics (SOM); CBB program</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Christine Chen</t>
+          <t>Wenpin Hou</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ASSOCIATE PROFESSOR</t>
+          <t>Assistant Professor in Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6148,40 +6142,52 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>medical-AI</t>
+          <t>AI-for-science</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Radiology lab on ultrasound AI decision support for breast and sarcoma lesions; radiomics integration.</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+          <t>AI-agent network structure compared with human social networks; scRNA dimensionality reduction.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>multi-agent LLM systems</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>christine.chen@mountsinai.org</t>
+          <t>wenpin.hou@duke.edu</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/christine-chen4</t>
+          <t>https://biostat.duke.edu/profile/wenpin-hou</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/christine-chen4</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+          <t>https://winnie09.github.io/Wenpin_Hou</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>MethylProphet: A Generalized Gene-Contextual Model for Inferring Whole-Genome DNA Methylation Landscape</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Benchmarking large language models for genomic knowledge with GeneTuring</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Integration of advanced ultrasound techniques, radiomics, and artificial intelligence for improved diagnosis of cystic breast lesions (2026) | Breast lymphoma: Imaging features, clinical presentation, and ultrasound artificial intelligence (AI) decision support (DS) (2025)</t>
+          <t>Structural Divergence Between the Moltbook AI-Agent Network and Human Social Networks (2026) | Trajectory-guided dimensionality reduction for multi-sample single-cell RNA-seq data reveals biologically relevant sample-level heterogeneity (2026)</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470074622153001&amp;selectedFilter=department&amp;tab=faculty&amp;start=20</t>
+          <t>https://biostat.duke.edu/people/faculty?page=2</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -6191,20 +6197,26 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unspecified: </t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr"/>
+          <t>Yes: I have fundings to support 1-2 PhD students. If you are interested, please send me your CV and, at the same time, list me as your preferred mentor in your PhD application.</t>
+        </is>
+      </c>
+      <c r="T57" t="n">
+        <v>2026</v>
+      </c>
       <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Her multimodal representation learning / foundation models for cells and 'one-shot learning and interpretability' paper connect to the applicant's BioCLIP-based fusion work and leakage-aware evaluation (arborphy).</t>
+        </is>
+      </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>clinical radiologist (prostate MRI, TULSA lead); no lab site found on profile</t>
+          <t>start year 2026 inferred from Feb 2026 'Meet' article; Columbia appointment (research leave) still held; applicant is a Columbia student: lab collaborates with Columbia, mention nothing beyond applicant.yaml</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+; fit based on name-matched papers only: check they are this person's; dossier reader says C: Profile: Dr. Chen specializes in prostate MRI and MRI-guided interventions; clinical, no lab/ML group found (profile men</t>
+          <t>fit based on name-matched papers only: check they are this person's; dossier reader says A: Upgraded B-&gt;A: Bio-AI foundation-model lab, new Duke assistant professor, explicitly funded for 1-2 PhD students and sta</t>
         </is>
       </c>
     </row>
@@ -6219,22 +6231,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Genetics and Genomic Sciences</t>
+          <t>Diagnostic, Molecular and Interventional Radiology</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Erming Wang</t>
+          <t>Christine Chen</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ASSISTANT PROFESSOR</t>
+          <t>ASSOCIATE PROFESSOR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6244,40 +6256,40 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>AI-for-science</t>
+          <t>medical-AI</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Bioinformatics and systems-biology tools integrating omics data for Alzheimer disease.</t>
+          <t>Radiology lab on ultrasound AI decision support for breast and sarcoma lesions; radiomics integration.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>erming.wang@mssm.edu</t>
+          <t>christine.chen@mountsinai.org</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/erming-wang</t>
+          <t>https://profiles.icahn.mssm.edu/christine-chen4</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/erming-wang</t>
+          <t>https://profiles.icahn.mssm.edu/christine-chen4</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sex and APOE genotype specific brain regional vulnerability to Alzheimer's Disease (2026) | Molecular Networks and Key Regulators Underlying Resilience of the Human Brain to Aging and Dementia (2026)</t>
+          <t>Integration of advanced ultrasound techniques, radiomics, and artificial intelligence for improved diagnosis of cystic breast lesions (2026) | Breast lymphoma: Imaging features, clinical presentation, and ultrasound artificial intelligence (AI) decision support (DS) (2025)</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470001513038352&amp;selectedFilter=department&amp;tab=faculty&amp;start=120</t>
+          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470074622153001&amp;selectedFilter=department&amp;tab=faculty&amp;start=20</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -6295,10 +6307,14 @@
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
-          <t>no lab site found (2 searches); official profile only; no recruiting info</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+          <t>clinical radiologist (prostate MRI, TULSA lead); no lab site found on profile</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+; fit based on name-matched papers only: check they are this person's; dossier reader says C: Profile: Dr. Chen specializes in prostate MRI and MRI-guided interventions; clinical, no lab/ML group found (profile men</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6311,12 +6327,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Diagnostic, Molecular and Interventional Radiology; BMEII core + AI</t>
+          <t>Genetics and Genomic Sciences</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Hao Chih Lee</t>
+          <t>Erming Wang</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6336,40 +6352,40 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>medical-AI</t>
+          <t>AI-for-science</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Cardiovascular imaging AI and deep learning; retinal imaging with supervised learning; LLM extraction from imaging reports.</t>
+          <t>Bioinformatics and systems-biology tools integrating omics data for Alzheimer disease.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>hao-chih.lee@mssm.edu</t>
+          <t>erming.wang@mssm.edu</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/hao-chih-lee</t>
+          <t>https://profiles.icahn.mssm.edu/erming-wang</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/hao-chih-lee</t>
+          <t>https://profiles.icahn.mssm.edu/erming-wang</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>AI and Deep Learning in Cardiovascular Imaging: From Risk Stratification to Precision Phenotyping (2026) | Retinal imaging and supervised learning predict hospitalizations and kidney and heart-lung damage in sickle cell disease (2026)</t>
+          <t>Sex and APOE genotype specific brain regional vulnerability to Alzheimer's Disease (2026) | Molecular Networks and Key Regulators Underlying Resilience of the Human Brain to Aging and Dementia (2026)</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470074622153001&amp;selectedFilter=department&amp;tab=faculty&amp;start=110</t>
+          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470001513038352&amp;selectedFilter=department&amp;tab=faculty&amp;start=120</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -6387,14 +6403,10 @@
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
-          <t>Radiology assistant prof; profile has no bio; no lab site found (WebSearch); co-founder of Crossmodal Intelligence Inc. per industry disclosure</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>fit based on name-matched papers only: check they are this person's; also listed as Hao-Chih Lee</t>
-        </is>
-      </c>
+          <t>no lab site found (2 searches); official profile only; no recruiting info</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6407,22 +6419,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Diagnostic, Molecular and Interventional Radiology</t>
+          <t>Diagnostic, Molecular and Interventional Radiology; BMEII core + AI</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Michael S Chung</t>
+          <t>Hao Chih Lee</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ASSOCIATE PROFESSOR</t>
+          <t>ASSISTANT PROFESSOR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6437,35 +6449,35 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>NLP model predicting radiation pneumonitis; AI system integrating longitudinal data for lung disease.</t>
+          <t>Cardiovascular imaging AI and deep learning; retinal imaging with supervised learning; LLM extraction from imaging reports.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>michael.chung@mountsinai.org</t>
+          <t>hao-chih.lee@mssm.edu</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/michael-s-chung</t>
+          <t>https://profiles.icahn.mssm.edu/hao-chih-lee</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/michael-s-chung</t>
+          <t>https://profiles.icahn.mssm.edu/hao-chih-lee</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Natural language processing-based model to predict radiation pneumonitis in patients with locally advanced non-small cell lung cancer undergoing chemoradiotherapy: a retrospective cohort study (2026) | Postoperative CT surveillance in the evaluation of local recurrence after sub-lobar resection of neoplastic lesions of the lung (2024)</t>
+          <t>AI and Deep Learning in Cardiovascular Imaging: From Risk Stratification to Precision Phenotyping (2026) | Retinal imaging and supervised learning predict hospitalizations and kidney and heart-lung damage in sickle cell disease (2026)</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470074622153001&amp;selectedFilter=department&amp;tab=faculty&amp;start=30</t>
+          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470074622153001&amp;selectedFilter=department&amp;tab=faculty&amp;start=110</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -6483,12 +6495,12 @@
       <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
-          <t>clinical radiologist/cardiology; profile lists education only, no research or ML; no lab site</t>
+          <t>Radiology assistant prof; profile has no bio; no lab site found (WebSearch); co-founder of Crossmodal Intelligence Inc. per industry disclosure</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+; fit based on name-matched papers only: check they are this person's; dossier reader says C: Profile shows clinical radiology (cardiothoracic) credentials only; no ML research stated.</t>
+          <t>fit based on name-matched papers only: check they are this person's; also listed as Hao-Chih Lee</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6520,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mingqian Huang</t>
+          <t>Michael S Chung</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6533,35 +6545,35 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Deep-learning knee MRI reconstruction; deepfake radiograph detection; DeepSeek LLM medical benchmarking.</t>
+          <t>NLP model predicting radiation pneumonitis; AI system integrating longitudinal data for lung disease.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>mingqian.huang@mountsinai.org</t>
+          <t>michael.chung@mountsinai.org</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/mingqian-huang</t>
+          <t>https://profiles.icahn.mssm.edu/michael-s-chung</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/mingqian-huang</t>
+          <t>https://profiles.icahn.mssm.edu/michael-s-chung</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>The Rise of Deepfake Medical Imaging: Radiologists' Diagnostic Accuracy in Detecting ChatGPT-generated Radiographs (2026) | Comparison of Deep-Learning-Based Reconstruction of Knee MRI with Conventional Sequences in Patients with Knee Pain (2026)</t>
+          <t>Natural language processing-based model to predict radiation pneumonitis in patients with locally advanced non-small cell lung cancer undergoing chemoradiotherapy: a retrospective cohort study (2026) | Postoperative CT surveillance in the evaluation of local recurrence after sub-lobar resection of neoplastic lesions of the lung (2024)</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470074622153001&amp;selectedFilter=department&amp;tab=faculty&amp;start=80</t>
+          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470074622153001&amp;selectedFilter=department&amp;tab=faculty&amp;start=30</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -6579,12 +6591,12 @@
       <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
-          <t>clinical MSK radiologist; profile lists education only, no research or ML; no lab site</t>
+          <t>clinical radiologist/cardiology; profile lists education only, no research or ML; no lab site</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+; fit based on name-matched papers only: check they are this person's; dossier reader says C: Profile shows clinical musculoskeletal radiology credentials only; no ML research stated.</t>
+          <t>associate: confirm promoted 2020+; fit based on name-matched papers only: check they are this person's; dossier reader says C: Profile shows clinical radiology (cardiothoracic) credentials only; no ML research stated.</t>
         </is>
       </c>
     </row>
@@ -6599,12 +6611,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Genetics and Genomic Sciences</t>
+          <t>Diagnostic, Molecular and Interventional Radiology</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Won Min Song</t>
+          <t>Mingqian Huang</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6624,44 +6636,40 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>AI-for-science</t>
+          <t>medical-AI</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Network modeling and embedding of multiscale proteomic and gene interaction data in Alzheimer disease.</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Bayesian SBM on connectome</t>
-        </is>
-      </c>
+          <t>Deep-learning knee MRI reconstruction; deepfake radiograph detection; DeepSeek LLM medical benchmarking.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>won-min.song@mssm.edu</t>
+          <t>mingqian.huang@mountsinai.org</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/won-min-song</t>
+          <t>https://profiles.icahn.mssm.edu/mingqian-huang</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://labs.icahn.mssm.edu/songlab/</t>
+          <t>https://profiles.icahn.mssm.edu/mingqian-huang</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Multiscale proteomic modeling reveals protein networks driving Alzheimer's disease pathogenesis (2025) | DAP12 deletion reduces neuronal SLIT2 and demyelination and enhances brain resilience in female tauopathy mice (2025)</t>
+          <t>The Rise of Deepfake Medical Imaging: Radiologists' Diagnostic Accuracy in Detecting ChatGPT-generated Radiographs (2026) | Comparison of Deep-Learning-Based Reconstruction of Knee MRI with Conventional Sequences in Patients with Knee Pain (2026)</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470001513038352&amp;selectedFilter=department&amp;tab=faculty&amp;start=110</t>
+          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470074622153001&amp;selectedFilter=department&amp;tab=faculty&amp;start=80</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -6671,28 +6679,20 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Unspecified: We are looking for another postdoc to join the lab.</t>
+          <t xml:space="preserve">Unspecified: </t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Please send your CV, letter of intent, two recommendation letters to won-min.song@mssm.edu.</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Network modeling for latent structure connects to the FlyWire Bayesian stochastic block model project.</t>
-        </is>
-      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
-          <t>site looks stale (latest post Feb 2023; no paper after 2021 listed); hiring only a postdoc; start_year not found (associate)</t>
+          <t>clinical MSK radiologist; profile lists education only, no research or ML; no lab site</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+</t>
+          <t>associate: confirm promoted 2020+; fit based on name-matched papers only: check they are this person's; dossier reader says C: Profile shows clinical musculoskeletal radiology credentials only; no ML research stated.</t>
         </is>
       </c>
     </row>
@@ -6712,17 +6712,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Xianxiao Zhou</t>
+          <t>Won Min Song</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ASSISTANT PROFESSOR</t>
+          <t>ASSOCIATE PROFESSOR</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6737,56 +6737,164 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Transcriptomic network models of neurodegenerative disease at single-cell level.</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
+          <t>Network modeling and embedding of multiscale proteomic and gene interaction data in Alzheimer disease.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Bayesian SBM on connectome</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>xianxiao.zhou@mssm.edu</t>
+          <t>won-min.song@mssm.edu</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/xianxiao-zhou</t>
+          <t>https://profiles.icahn.mssm.edu/won-min-song</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/xianxiao-zhou</t>
+          <t>https://labs.icahn.mssm.edu/songlab/</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
+          <t>Multiscale proteomic modeling reveals protein networks driving Alzheimer's disease pathogenesis (2025) | DAP12 deletion reduces neuronal SLIT2 and demyelination and enhances brain resilience in female tauopathy mice (2025)</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470001513038352&amp;selectedFilter=department&amp;tab=faculty&amp;start=110</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Unspecified: We are looking for another postdoc to join the lab.</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Please send your CV, letter of intent, two recommendation letters to won-min.song@mssm.edu.</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Network modeling for latent structure connects to the FlyWire Bayesian stochastic block model project.</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>site looks stale (latest post Feb 2023; no paper after 2021 listed); hiring only a postdoc; start_year not found (associate)</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Icahn School of Medicine at Mount Sinai</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Genetics and Genomic Sciences</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Xianxiao Zhou</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ASSISTANT PROFESSOR</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>AI-for-science</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Transcriptomic network models of neurodegenerative disease at single-cell level.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>xianxiao.zhou@mssm.edu</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>https://profiles.icahn.mssm.edu/xianxiao-zhou</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://profiles.icahn.mssm.edu/xianxiao-zhou</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
           <t>Sex and APOE genotype specific brain regional vulnerability to Alzheimer's Disease (2026) | Multiscale Transcriptomic Network Models of Parkinson's Disease at the Single Cell Level (2026)</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470001513038352&amp;selectedFilter=department&amp;tab=faculty&amp;start=140</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t xml:space="preserve">Unspecified: </t>
         </is>
       </c>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr">
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
         <is>
           <t>profile has no bio; no lab site found (WebSearch x1)</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>fit based on name-matched papers only: check they are this person's</t>
         </is>
@@ -6803,7 +6911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7516,17 +7624,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>University of California San Francisco</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Psychological &amp; Brain Sciences; Graduate Program for Neuroscience (faculty); Center for Systems Neuroscience</t>
+          <t>Radiology and Biomedical Imaging</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Arthur Lee</t>
+          <t>Congyu Liao</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7546,44 +7654,36 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>medical-AI</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Card has no research text or papers.</t>
+          <t>Developing diffusion and quantitative MRI techniques, magnetic resonance fingerprinting, for neurodevelopment.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>artlee@bu.edu</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>https://www.bu.edu/psych/profile/arthur-sangil-lee/</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>http://thedecodinglab.com/</t>
+          <t>https://researcherprofiles.org/profile/612476762</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Neural decoders: saving the baby from the bathwater</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Distinguishing deception from its confounds by improving the validity of fMRI-based neural prediction</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
+          <t>Effects of diffusion MRI spatial resolution on human brain short-range association fiber reconstruction and structural connectivity estimation (2026)</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Self-calibrated B&amp;lt;sub&amp;gt;1&amp;lt;/sub&amp;gt; &amp;lt;sup&amp;gt;+&amp;lt;/sup&amp;gt; and B&amp;lt;sub&amp;gt;0&amp;lt;/sub&amp;gt; Field Inhomogeneities Estimation (SAFE) in 3D Magnetic Resonance Fingerprinting (2026)</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/psych/people/faculty/</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -7593,30 +7693,20 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Yes: We are looking for Ph.D. students interested in our research.</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Please feel free to send an email to Arthur (see contact) to let him know to look out for your application.</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>His interest in validating neural decoders (confounds, interpretability) connects to the EEG motor-imagery decoder with run-grouped validation.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Unspecified: </t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
-          <t>psychology department; applications go through Psychology or Neuroscience program, not CS/Stats</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>also listed as Arthur Sangil Lee</t>
-        </is>
-      </c>
+          <t>no lab site found; radiology.ucsf.edu pages returned 403 (not bypassed); MRI physics/acquisition first; ML role unclear</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7629,22 +7719,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Radiology and Biomedical Imaging</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Congyu Liao</t>
+          <t>Jian Shi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -7659,7 +7749,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Developing diffusion and quantitative MRI techniques, magnetic resonance fingerprinting, for neurodevelopment.</t>
+          <t>Machine learning with molecular experiments to decode Alzheimer disease, brain injury, brain tumor mechanisms.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -7667,23 +7757,19 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/612476762</t>
+          <t>https://researcherprofiles.org/profile/681177372</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Effects of diffusion MRI spatial resolution on human brain short-range association fiber reconstruction and structural connectivity estimation (2026)</t>
+          <t>Blood Markers Show Neural Consequences of LongCOVID-19 (2024)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Self-calibrated B&amp;lt;sub&amp;gt;1&amp;lt;/sub&amp;gt; &amp;lt;sup&amp;gt;+&amp;lt;/sup&amp;gt; and B&amp;lt;sub&amp;gt;0&amp;lt;/sub&amp;gt; Field Inhomogeneities Estimation (SAFE) in 3D Magnetic Resonance Fingerprinting (2026)</t>
-        </is>
-      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurology)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -7696,17 +7782,19 @@
           <t xml:space="preserve">Unspecified: </t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>2025</v>
-      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
-          <t>no lab site found; radiology.ucsf.edu pages returned 403 (not bypassed); MRI physics/acquisition first; ML role unclear</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr"/>
+          <t>no lab site found; wet-lab neuroinflammation/stroke/glioblastoma group with ML as one tool; Associate Professor</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+; dossier reader says C: Biology-first (Alzheimer's, injury, tumors with animal models); ML is supporting.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7719,22 +7807,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Radiology and Biomedical Imaging</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Jian Shi</t>
+          <t>Jonathan Liu</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -7749,7 +7837,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Machine learning with molecular experiments to decode Alzheimer disease, brain injury, brain tumor mechanisms.</t>
+          <t>Radiologist with quantitative SPECT methods and AI applications in thoracic and cardiovascular radiology.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -7757,19 +7845,19 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/681177372</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Blood Markers Show Neural Consequences of LongCOVID-19 (2024)</t>
-        </is>
-      </c>
+          <t>https://researcherprofiles.org/profile/319885321</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Multimodality Imaging in Myocarditis: Integrating Etiology, Diagnosis, and Risk Stratification (2026)</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurology)</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -7782,17 +7870,19 @@
           <t xml:space="preserve">Unspecified: </t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>2022</v>
+      </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
-          <t>no lab site found; wet-lab neuroinflammation/stroke/glioblastoma group with ML as one tool; Associate Professor</t>
+          <t>clinical thoracic radiologist; no lab; likely not a PhD advisor</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+; dossier reader says C: Biology-first (Alzheimer's, injury, tumors with animal models); ML is supporting.</t>
+          <t>dossier reader says C: Clinical radiologist; AI is a side interest, no lab found.</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7902,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Jonathan Liu</t>
+          <t>Kang Wang</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -7837,22 +7927,30 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Radiologist with quantitative SPECT methods and AI applications in thoracic and cardiovascular radiology.</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>Develops anatomy-aware vision-language AI for CT detection of metastatic colorectal cancer.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>BioCLIP/EfficientNet fusion (CV)</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/319885321</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>https://researcherprofiles.org/profile/523574019</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Zero-Shot Large Language Model-Powered Data Curation for Pancreatic Cyst Surveillance: Promise, Progress, and the Path to Practice (2026)</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Multimodality Imaging in Myocarditis: Integrating Etiology, Diagnosis, and Risk Stratification (2026)</t>
+          <t>Imaging Evaluation for Steatotic Liver Disease (2026) | Diagnostic performance of CT/MRI LI-RADS radiation treatment response algorithm v2024 for Y-90 radioembolization (2026)</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -7870,21 +7968,15 @@
           <t xml:space="preserve">Unspecified: </t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>2022</v>
-      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
-          <t>clinical thoracic radiologist; no lab; likely not a PhD advisor</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>dossier reader says C: Clinical radiologist; AI is a side interest, no lab found.</t>
-        </is>
-      </c>
+          <t>no lab site; radiology.ucsf.edu 403 (not bypassed); web-search summary (not fetched page) says AI-based quantitative liver MRI, vision-language models for abdominal oncology, NIH R01 2025-2029</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7902,7 +7994,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Kang Wang</t>
+          <t>Maggie Chung</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -7927,32 +8019,28 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Develops anatomy-aware vision-language AI for CT detection of metastatic colorectal cancer.</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>BioCLIP/EfficientNet fusion (CV)</t>
-        </is>
-      </c>
+          <t>Breast imaging radiologist; deep learning synthetic contrast MRI, AI risk stratification, language-model report extraction.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/523574019</t>
+          <t>https://researcherprofiles.org/profile/14904495</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Zero-Shot Large Language Model-Powered Data Curation for Pancreatic Cyst Surveillance: Promise, Progress, and the Path to Practice (2026)</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Imaging Evaluation for Steatotic Liver Disease (2026) | Diagnostic performance of CT/MRI LI-RADS radiation treatment response algorithm v2024 for Y-90 radioembolization (2026)</t>
-        </is>
-      </c>
+          <t>Cryoablation Versus Breast-Conserving Surgery for Early-Stage, Low-Risk Breast Cancer ≤ 1.5 cm: A Cost-Effectiveness Analysis (2026)</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>From Risk Prediction to Coordinated Care (2026)</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
           <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
@@ -7973,7 +8061,7 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>no lab site; radiology.ucsf.edu 403 (not bypassed); web-search summary (not fetched page) says AI-based quantitative liver MRI, vision-language models for abdominal oncology, NIH R01 2025-2029</t>
+          <t>clinical breast radiologist (MD); no lab site found</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
@@ -7994,17 +8082,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Maggie Chung</t>
+          <t>Yan Li</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8019,7 +8107,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Breast imaging radiologist; deep learning synthetic contrast MRI, AI risk stratification, language-model report extraction.</t>
+          <t>Brain MR spectroscopic imaging methods, statistical methods, and machine learning for glioma recurrence.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -8027,20 +8115,16 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/14904495</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Cryoablation Versus Breast-Conserving Surgery for Early-Stage, Low-Risk Breast Cancer ≤ 1.5 cm: A Cost-Effectiveness Analysis (2026)</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>From Risk Prediction to Coordinated Care (2026)</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
+          <t>https://researcherprofiles.org/profile/189562</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Radiobiological dosimetry using hybrid imaging-derived spatiotemporal dose distributions for&amp;lt;sup&amp;gt;131&amp;lt;/sup&amp;gt;I therapy of metastatic thyroid cancer (2026) | Spatially identifying regions of tumor recurrence in patients with suspected recurrent glioma using physiologic MRI and machine learning (2026)</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
@@ -8061,10 +8145,14 @@
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
-          <t>clinical breast radiologist (MD); no lab site found</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr"/>
+          <t>lab site lilabimaging.ucsf.edu returned 403 (not bypassed); no page text read; web search only: MR spectroscopic imaging methods, Associate Professor</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8082,7 +8170,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Yan Li</t>
+          <t>Yang Yang</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -8107,7 +8195,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Brain MR spectroscopic imaging methods, statistical methods, and machine learning for glioma recurrence.</t>
+          <t>MRI sequence development, motion correction and AI; predicting Alzheimer outcomes from single MRI.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -8115,14 +8203,18 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/189562</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>https://researcherprofiles.org/profile/327403539</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Predicting categorical and continuous Alzheimer's disease outcomes from a single MRI scan (2026)</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Radiobiological dosimetry using hybrid imaging-derived spatiotemporal dose distributions for&amp;lt;sup&amp;gt;131&amp;lt;/sup&amp;gt;I therapy of metastatic thyroid cancer (2026) | Spatially identifying regions of tumor recurrence in patients with suspected recurrent glioma using physiologic MRI and machine learning (2026)</t>
+          <t>Determinants of image quality in respiratory triggered free breathing lung MRI at 0.55 T in adults (2026) | Self-calibrated B&amp;lt;sub&amp;gt;1&amp;lt;/sub&amp;gt; &amp;lt;sup&amp;gt;+&amp;lt;/sup&amp;gt; and B&amp;lt;sub&amp;gt;0&amp;lt;/sub&amp;gt; Field Inhomogeneities Estimation (SAFE) in 3D Magnetic Resonance Fingerprinting (2026)</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -8145,102 +8237,10 @@
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
-          <t>lab site lilabimaging.ucsf.edu returned 403 (not bypassed); no page text read; web search only: MR spectroscopic imaging methods, Associate Professor</t>
+          <t>no lab site found; MR sequence/physics first; AI component per search summary only</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
-        <is>
-          <t>associate: confirm promoted 2020+</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>University of California San Francisco</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Radiology and Biomedical Imaging</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Yang Yang</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Associate Professor</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>associate</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>medical-AI</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>MRI sequence development, motion correction and AI; predicting Alzheimer outcomes from single MRI.</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>https://researcherprofiles.org/profile/327403539</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Predicting categorical and continuous Alzheimer's disease outcomes from a single MRI scan (2026)</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Determinants of image quality in respiratory triggered free breathing lung MRI at 0.55 T in adults (2026) | Self-calibrated B&amp;lt;sub&amp;gt;1&amp;lt;/sub&amp;gt; &amp;lt;sup&amp;gt;+&amp;lt;/sup&amp;gt; and B&amp;lt;sub&amp;gt;0&amp;lt;/sub&amp;gt; Field Inhomogeneities Estimation (SAFE) in 3D Magnetic Resonance Fingerprinting (2026)</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unspecified: </t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>no lab site found; MR sequence/physics first; AI component per search summary only</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
         <is>
           <t>associate: confirm promoted 2020+</t>
         </is>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>people 10 | need email 2 | check 1 | dropped C 18</t>
+          <t>people 11 | need email 1 | check 1 | dropped C 18</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>

--- a/data/export/batch1.xlsx
+++ b/data/export/batch1.xlsx
@@ -12211,7 +12211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X153"/>
+  <dimension ref="A1:X157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Biological and Medical Informatics (BMI) PhD program core+affiliate faculty (Wayback 2026-05 copy); Neurology</t>
+          <t>Biological and Medical Informatics (BMI) PhD program core+affiliate faculty (Wayback 2026-05 copy); Neurology; Neuroscience Graduate Program (faculty)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -20705,17 +20705,17 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cell and Tissue Biology</t>
+          <t>Biomedical Sciences (BMS) PhD program faculty (Wayback 2026-07 copy, pages 0-12 and 26 only)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Bo Gong</t>
+          <t>Benjamin Huang</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Asst Professor in Residence</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -20735,7 +20735,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Cell biology of cell fate decisions in development and neurodegeneration.</t>
+          <t>Pediatric leukemia biology and clinical outcomes (MD, Pediatrics-Oncology)</t>
         </is>
       </c>
       <c r="J106" t="inlineStr"/>
@@ -20743,23 +20743,19 @@
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/686563008</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>Pulling the Back to Steer Cell Migration: Mechanisms of Structural Polarity in Confining Signaling and Protrusion (2026)</t>
-        </is>
-      </c>
+          <t>https://bms.ucsf.edu/people/benjamin-huang-md</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>SEC14L2 couples chaperone-mediated autophagy to microtubule stability by targeting Stathmin 1 (2026)</t>
+          <t>Multiselective RAS(ON) inhibition targets oncogenic RAS and overcomes RAS-mediated resistance to FLT3i and BCL2i in AML (2026) | Reactive oxygen species define leukemia stem cell identity in pediatric acute myeloid leukemia (2026)</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Cell and Tissue Biology)</t>
+          <t>https://web.archive.org/web/20260710111852/https://bms.ucsf.edu/faculty?page=10</t>
         </is>
       </c>
       <c r="R106" t="inlineStr"/>
@@ -20781,12 +20777,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Psychiatry</t>
+          <t>Cell and Tissue Biology</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Bo Hu</t>
+          <t>Bo Gong</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -20811,7 +20807,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Intravenous ketamine protocol for psychiatric conditions in medical and surgical units.</t>
+          <t>Cell biology of cell fate decisions in development and neurodegeneration.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -20819,19 +20815,23 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/518025861</t>
+          <t>https://researcherprofiles.org/profile/686563008</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Implementation and Preliminary Evaluation of an Intravenous Ketamine Protocol for Psychiatric Conditions in Medical and Surgical Units: A 1-Year Pilot Study (2026)</t>
+          <t>Pulling the Back to Steer Cell Migration: Mechanisms of Structural Polarity in Confining Signaling and Protrusion (2026)</t>
         </is>
       </c>
       <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>SEC14L2 couples chaperone-mediated autophagy to microtubule stability by targeting Stathmin 1 (2026)</t>
+        </is>
+      </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Psychiatry)</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Cell and Tissue Biology)</t>
         </is>
       </c>
       <c r="R107" t="inlineStr"/>
@@ -20853,16 +20853,24 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Quantitative Biosciences Institute (home dept: Pharmaceutical Chemistry)</t>
+          <t>Psychiatry</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Bo Huang</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+          <t>Bo Hu</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>C</t>
@@ -20875,7 +20883,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Fluorescence microscopy binders and transcriptional condensates.</t>
+          <t>Intravenous ketamine protocol for psychiatric conditions in medical and surgical units.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr"/>
@@ -20883,19 +20891,19 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>http://huanglab.ucsf.edu</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
+          <t>https://researcherprofiles.org/profile/518025861</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Implementation and Preliminary Evaluation of an Intravenous Ketamine Protocol for Psychiatric Conditions in Medical and Surgical Units: A 1-Year Pilot Study (2026)</t>
+        </is>
+      </c>
       <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>De novo pan-rhodamine binders for fluorescence microscopy from mammalian cells to extremophiles (2026) | YAP charge patterning mediates signal integration through transcriptional co-condensates (2025)</t>
-        </is>
-      </c>
+      <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>https://qbi.ucsf.edu/investigators</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Psychiatry)</t>
         </is>
       </c>
       <c r="R108" t="inlineStr"/>
@@ -20917,24 +20925,16 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Radiology and Biomedical Imaging</t>
+          <t>Quantitative Biosciences Institute (home dept: Pharmaceutical Chemistry)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Charlie Wang</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Assistant Professor</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
+          <t>Bo Huang</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
           <t>C</t>
@@ -20947,7 +20947,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Hyperpolarized 13C MRI for brain perfusion and glioma; imaging physics without ML.</t>
+          <t>Fluorescence microscopy binders and transcriptional condensates.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr"/>
@@ -20955,27 +20955,19 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/126038969</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>Translation of hyperpolarized [13C,15N2]urea MRI for novel human brain perfusion studies (2025)</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>A flexible MRF approach to improve kinetic rate estimation with bSSFP‐based hyperpolarized [1‐ 13C]pyruvate MRI (2025)</t>
-        </is>
-      </c>
+          <t>http://huanglab.ucsf.edu</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>IMG-97. Advancing hyperpolarized13C MRI for non-invasive assessment of blood-brain barrier integrity and IDH mutation status in glioma (2025)</t>
+          <t>De novo pan-rhodamine binders for fluorescence microscopy from mammalian cells to extremophiles (2026) | YAP charge patterning mediates signal integration through transcriptional co-condensates (2025)</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
+          <t>https://qbi.ucsf.edu/investigators</t>
         </is>
       </c>
       <c r="R109" t="inlineStr"/>
@@ -21002,7 +20994,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Cheng Hong</t>
+          <t>Charlie Wang</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -21027,7 +21019,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Clinical liver MRI and LI-RADS imaging evaluation studies.</t>
+          <t>Hyperpolarized 13C MRI for brain perfusion and glioma; imaging physics without ML.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
@@ -21035,22 +21027,22 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/328148685</t>
+          <t>https://researcherprofiles.org/profile/126038969</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Imaging Evaluation for Steatotic Liver Disease (2026)</t>
+          <t>Translation of hyperpolarized [13C,15N2]urea MRI for novel human brain perfusion studies (2025)</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Diagnostic performance of CT/MRI LI-RADS radiation treatment response algorithm v2024 for Y-90 radioembolization (2026)</t>
+          <t>A flexible MRF approach to improve kinetic rate estimation with bSSFP‐based hyperpolarized [1‐ 13C]pyruvate MRI (2025)</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lessons learned: strategies for implementing and the ongoing use of LI-RADS in your practice (2025)</t>
+          <t>IMG-97. Advancing hyperpolarized13C MRI for non-invasive assessment of blood-brain barrier integrity and IDH mutation status in glioma (2025)</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -21077,12 +21069,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Psychiatry</t>
+          <t>Radiology and Biomedical Imaging</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Cheng Qian</t>
+          <t>Cheng Hong</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -21107,7 +21099,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Psychiatry; child behavioral health programs, clinical training lead.</t>
+          <t>Clinical liver MRI and LI-RADS imaging evaluation studies.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -21115,15 +21107,27 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/343574317</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
+          <t>https://researcherprofiles.org/profile/328148685</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Imaging Evaluation for Steatotic Liver Disease (2026)</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Diagnostic performance of CT/MRI LI-RADS radiation treatment response algorithm v2024 for Y-90 radioembolization (2026)</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Lessons learned: strategies for implementing and the ongoing use of LI-RADS in your practice (2025)</t>
+        </is>
+      </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Psychiatry)</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
         </is>
       </c>
       <c r="R111" t="inlineStr"/>
@@ -21150,17 +21154,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Chuan Mei Lee</t>
+          <t>Cheng Qian</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -21175,7 +21179,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Child psychiatry access programs and integration of mental health services in pediatric primary care.</t>
+          <t>Psychiatry; child behavioral health programs, clinical training lead.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -21183,24 +21187,12 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/188250</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>Location of Crisis Service Delivery for Medicaid-Enrolled Youths with Behavioral Health Conditions (2026)</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>Substance Use Services at Child Psychiatry Access Programs. (2026)</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>5.24 Behavioral Problems and Chronic Pain Among Children and Adolescents in the United States: An Analysis From 2016 to 2023 (2025) | 4.74 Addressing the Youth Mental Health Crisis Through Psychiatric Consultation to Primary Care: The California Child and Adolescent Mental Health Access Program (2025)</t>
-        </is>
-      </c>
+          <t>https://researcherprofiles.org/profile/343574317</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr">
         <is>
           <t>https://profiles.ucsf.edu/search/advanced (Department=Psychiatry)</t>
@@ -21212,11 +21204,7 @@
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>associate: confirm promoted 2020+</t>
-        </is>
-      </c>
+      <c r="X112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -21229,22 +21217,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Radiology and Biomedical Imaging</t>
+          <t>Psychiatry</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Connie Lu</t>
+          <t>Chuan Mei Lee</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -21259,7 +21247,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Radiology MD; diagnostic radiology residency, clinical profile.</t>
+          <t>Child psychiatry access programs and integration of mental health services in pediatric primary care.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -21267,15 +21255,27 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/681177355</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
+          <t>https://researcherprofiles.org/profile/188250</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Location of Crisis Service Delivery for Medicaid-Enrolled Youths with Behavioral Health Conditions (2026)</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Substance Use Services at Child Psychiatry Access Programs. (2026)</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>5.24 Behavioral Problems and Chronic Pain Among Children and Adolescents in the United States: An Analysis From 2016 to 2023 (2025) | 4.74 Addressing the Youth Mental Health Crisis Through Psychiatric Consultation to Primary Care: The California Child and Adolescent Mental Health Access Program (2025)</t>
+        </is>
+      </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Psychiatry)</t>
         </is>
       </c>
       <c r="R113" t="inlineStr"/>
@@ -21284,7 +21284,11 @@
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
       <c r="W113" t="inlineStr"/>
-      <c r="X113" t="inlineStr"/>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -21297,12 +21301,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Biomedical Sciences (BMS) PhD program faculty (Wayback 2026-07 copy, pages 0-12 and 26 only)</t>
+          <t>Radiology and Biomedical Imaging</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Edward Hsiao</t>
+          <t>Connie Lu</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -21327,7 +21331,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Patient-reported outcomes and trials for fibrodysplasia ossificans progressiva and fibrous dysplasia.</t>
+          <t>Radiology MD; diagnostic radiology residency, clinical profile.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -21335,19 +21339,15 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://bms.ucsf.edu/people/edward-hsiao-md-phd</t>
+          <t>https://researcherprofiles.org/profile/681177355</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>Development of the Fibrodysplasia Ossificans Progressiva FLare EXperience Revised (FOP-FLEX-R©) Questionnaire: A Patient-Reported Outcome Measure (2026) | Palovarotene impact on fibrodysplasia ossificans progressiva (FOP): data from month 48 of the phase III MOVE trial (2026)</t>
-        </is>
-      </c>
+      <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260710111852/https://bms.ucsf.edu/faculty?page=10</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
         </is>
       </c>
       <c r="R114" t="inlineStr"/>
@@ -21369,22 +21369,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Radiology and Biomedical Imaging</t>
+          <t>Biomedical Sciences (BMS) PhD program faculty (Wayback 2026-07 copy, pages 0-12 and 26 only)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Ellen Chang</t>
+          <t>Edward Hsiao</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -21399,7 +21399,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Nasopharyngeal carcinoma screening and population survival epidemiology.</t>
+          <t>Patient-reported outcomes and trials for fibrodysplasia ossificans progressiva and fibrous dysplasia.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr"/>
@@ -21407,19 +21407,19 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/327403537</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>Population-based nasopharyngeal carcinoma survival in southern China (2026)</t>
-        </is>
-      </c>
+          <t>https://bms.ucsf.edu/people/edward-hsiao-md-phd</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Development of the Fibrodysplasia Ossificans Progressiva FLare EXperience Revised (FOP-FLEX-R©) Questionnaire: A Patient-Reported Outcome Measure (2026) | Palovarotene impact on fibrodysplasia ossificans progressiva (FOP): data from month 48 of the phase III MOVE trial (2026)</t>
+        </is>
+      </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
+          <t>https://web.archive.org/web/20260710111852/https://bms.ucsf.edu/faculty?page=10</t>
         </is>
       </c>
       <c r="R115" t="inlineStr"/>
@@ -21428,11 +21428,7 @@
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr"/>
       <c r="W115" t="inlineStr"/>
-      <c r="X115" t="inlineStr">
-        <is>
-          <t>associate: confirm promoted 2020+</t>
-        </is>
-      </c>
+      <c r="X115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -21445,12 +21441,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Biochemistry and Biophysics</t>
+          <t>Radiology and Biomedical Imaging</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Eric Chow</t>
+          <t>Ellen Chang</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -21475,7 +21471,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Single-cell multiomic CRISPR screens and compact guide RNA libraries for gene regulation.</t>
+          <t>Nasopharyngeal carcinoma screening and population survival epidemiology.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -21483,23 +21479,19 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/185237</t>
+          <t>https://researcherprofiles.org/profile/327403537</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Simultaneous capture of single cell RNA-seq, ATAC-seq, and CRISPR perturbation enables multiomic screens to identify gene regulatory relationships (2025)</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>Compact CRISPR genetic screens enabled by improved guide RNA library cloning (2024)</t>
-        </is>
-      </c>
+          <t>Population-based nasopharyngeal carcinoma survival in southern China (2026)</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Biochemistry and Biophysics)</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
         </is>
       </c>
       <c r="R116" t="inlineStr"/>
@@ -21525,22 +21517,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Biochemistry and Biophysics</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Greta Peng</t>
+          <t>Eric Chow</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -21555,7 +21547,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Neurohumanities education and neurology outcomes in neonatal seizures and DIPG.</t>
+          <t>Single-cell multiomic CRISPR screens and compact guide RNA libraries for gene regulation.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
@@ -21563,23 +21555,23 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/308694444</t>
+          <t>https://researcherprofiles.org/profile/185237</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>The DIPG/DMG National Tumor Board: The power of advocacy (2026)</t>
+          <t>Simultaneous capture of single cell RNA-seq, ATAC-seq, and CRISPR perturbation enables multiomic screens to identify gene regulatory relationships (2025)</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Preferred Parental Language and Neurodevelopmental Outcomes Among Infants With Acute Provoked Neonatal Seizures in the United States (2025)</t>
+          <t>Compact CRISPR genetic screens enabled by improved guide RNA library cloning (2024)</t>
         </is>
       </c>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurology)</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Biochemistry and Biophysics)</t>
         </is>
       </c>
       <c r="R117" t="inlineStr"/>
@@ -21588,7 +21580,11 @@
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr"/>
       <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr"/>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -21601,16 +21597,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Quantitative Biosciences Institute (home dept: Biochemistry &amp; Biophysics)</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Hao Li</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
+          <t>Greta Peng</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
           <t>C</t>
@@ -21623,7 +21627,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Molecular mechanisms of aging, genetic determinants of complex traits, gene regulatory networks.</t>
+          <t>Neurohumanities education and neurology outcomes in neonatal seizures and DIPG.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
@@ -21631,19 +21635,23 @@
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>http://mobydick.ucsf.edu/</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>Inferring Gene Regulatory Network Architecture Underlying Complex Traits: An Integrative Analysis of Mutant Lifespan and Gene Expression Profiles Identifies Master Regulators and Key Functional Modules for Yeast Aging (2026) | Complement C4b as a key mediator of synaptic loss and cognitive decline in brain aging (2025)</t>
-        </is>
-      </c>
+          <t>https://researcherprofiles.org/profile/308694444</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>The DIPG/DMG National Tumor Board: The power of advocacy (2026)</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Preferred Parental Language and Neurodevelopmental Outcomes Among Infants With Acute Provoked Neonatal Seizures in the United States (2025)</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>https://qbi.ucsf.edu/investigators</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurology)</t>
         </is>
       </c>
       <c r="R118" t="inlineStr"/>
@@ -21665,24 +21673,16 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Psychiatry</t>
+          <t>Quantitative Biosciences Institute (home dept: Biochemistry &amp; Biophysics)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Hohui Wang</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Associate Professor</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>associate</t>
-        </is>
-      </c>
+          <t>Hao Li</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
           <t>C</t>
@@ -21695,7 +21695,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Inflammatory bowel disease links to depression, dementia and suicide risk.</t>
+          <t>Molecular mechanisms of aging, genetic determinants of complex traits, gene regulatory networks.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr"/>
@@ -21703,23 +21703,19 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/195581</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>Inflammatory Bowel Disease and Neurodegenerative Diseases (2023)</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>Risk of Attempted Suicide Among Patients With IBD: A Nationwide Longitudinal Follow-up Study (2023)</t>
-        </is>
-      </c>
-      <c r="P119" t="inlineStr"/>
+          <t>http://mobydick.ucsf.edu/</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Inferring Gene Regulatory Network Architecture Underlying Complex Traits: An Integrative Analysis of Mutant Lifespan and Gene Expression Profiles Identifies Master Regulators and Key Functional Modules for Yeast Aging (2026) | Complement C4b as a key mediator of synaptic loss and cognitive decline in brain aging (2025)</t>
+        </is>
+      </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Psychiatry)</t>
+          <t>https://qbi.ucsf.edu/investigators</t>
         </is>
       </c>
       <c r="R119" t="inlineStr"/>
@@ -21728,11 +21724,7 @@
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr"/>
       <c r="W119" t="inlineStr"/>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>associate: confirm promoted 2020+</t>
-        </is>
-      </c>
+      <c r="X119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -21750,17 +21742,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Jessica Hua</t>
+          <t>Hohui Wang</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -21775,7 +21767,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Neuromodulation and cognition in schizophrenia; cortical thickness and social determinants.</t>
+          <t>Inflammatory bowel disease links to depression, dementia and suicide risk.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr"/>
@@ -21783,17 +21775,17 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/371173157</t>
+          <t>https://researcherprofiles.org/profile/195581</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Social Determinants of Health and Neurobiology Across the Schizophrenia Course: A Systematic Review (2026)</t>
+          <t>Inflammatory Bowel Disease and Neurodegenerative Diseases (2023)</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Adjustment of Regional Cortical Thickness Measures for Global Cortical Thickness Obscures Deficits Across the Schizophrenia Spectrum: A Cautionary Note About Normative Modeling of Brain Imaging Data (2025)</t>
+          <t>Risk of Attempted Suicide Among Patients With IBD: A Nationwide Longitudinal Follow-up Study (2023)</t>
         </is>
       </c>
       <c r="P120" t="inlineStr"/>
@@ -21808,7 +21800,11 @@
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr"/>
       <c r="W120" t="inlineStr"/>
-      <c r="X120" t="inlineStr"/>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -21821,12 +21817,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Neurological Surgery</t>
+          <t>Psychiatry</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>John Yue</t>
+          <t>Jessica Hua</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -21851,7 +21847,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Blood-based biomarkers for brain injury classification and prognosis.</t>
+          <t>Neuromodulation and cognition in schizophrenia; cortical thickness and social determinants.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -21859,23 +21855,23 @@
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/176762</t>
+          <t>https://researcherprofiles.org/profile/371173157</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Clinical Utility of Structural Blood-Based Biomarkers in Pediatric Traumatic Brain Injury: A Focused Review of Glial Fibrillary Acidic Protein, Ubiquitin C-Terminal Hydrolase L1, and S100 Calcium-Binding Protein B (2026)</t>
+          <t>Social Determinants of Health and Neurobiology Across the Schizophrenia Course: A Systematic Review (2026)</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Insurance-based disparities in traumatic brain injury length of stay and discharge dispositions: A retrospective cohort analysis of the national trauma data bank (2026)</t>
+          <t>Adjustment of Regional Cortical Thickness Measures for Global Cortical Thickness Obscures Deficits Across the Schizophrenia Spectrum: A Cautionary Note About Normative Modeling of Brain Imaging Data (2025)</t>
         </is>
       </c>
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurological Surgery)</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Psychiatry)</t>
         </is>
       </c>
       <c r="R121" t="inlineStr"/>
@@ -21897,16 +21893,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Quantitative Biosciences Institute (home dept: Bioengineering)</t>
+          <t>Neurological Surgery</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Kevin Lou</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+          <t>John Yue</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
           <t>C</t>
@@ -21919,7 +21923,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Kinase inhibitor design; clinical trial listing in neuro-oncology.</t>
+          <t>Blood-based biomarkers for brain injury classification and prognosis.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr"/>
@@ -21927,19 +21931,23 @@
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/kevin.lou</t>
+          <t>https://researcherprofiles.org/profile/176762</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>A design approach for bitopic kinase inhibitors (2026)</t>
-        </is>
-      </c>
-      <c r="O122" t="inlineStr"/>
+          <t>Clinical Utility of Structural Blood-Based Biomarkers in Pediatric Traumatic Brain Injury: A Focused Review of Glial Fibrillary Acidic Protein, Ubiquitin C-Terminal Hydrolase L1, and S100 Calcium-Binding Protein B (2026)</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Insurance-based disparities in traumatic brain injury length of stay and discharge dispositions: A retrospective cohort analysis of the national trauma data bank (2026)</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>https://qbi.ucsf.edu/investigators</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurological Surgery)</t>
         </is>
       </c>
       <c r="R122" t="inlineStr"/>
@@ -21961,22 +21969,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Neurological Surgery</t>
+          <t>Biomedical Sciences (BMS) PhD program faculty (Wayback 2026-07 copy, pages 0-12 and 26 only)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Lee Tan</t>
+          <t>Jonathan Chou</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Asst. Professor In Residence</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -21991,7 +21999,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Minimally invasive and open spine surgery, including robotic and motion-preservation techniques.</t>
+          <t>Cancer cell biology and clinical oncology trials (MD/PhD, Hematology-Oncology)</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -21999,27 +22007,19 @@
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/196680</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>When Is Fusion Necessary in Addressing Symptomatic Adjacent Level Pathology - A Commentary on "How to Treat Adjacent-Segment Pathology Following Lumbar Fusion Surgery: Decompression Alone or Decompression With Extended Fusion Surgery?" (2026)</t>
-        </is>
-      </c>
-      <c r="O123" t="inlineStr">
-        <is>
-          <t>Safety and Efficacy of Real-Time Intraoperative Ultrasound-Guided Posterolateral Thoracic Diskectomy: Using Technology to Minimize Complication and Improve Surgical Outcome (2026)</t>
-        </is>
-      </c>
+          <t>https://bms.ucsf.edu/people/jonathan-chou-md-phd</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Risk Factors, Biomechanics, and Prevention Strategies for Proximal Junctional Failure in Adult Spinal Deformity Surgery - A Commentary on "Proximal Junctional Failure Development Despite Achieving Ideal Sagittal Correction According to Age-Adjusted Alignment Target in Patients With Adult Spinal Deformity: Risk Factor Analysis of 196 Cases Undergoing Low Thoracic to Pelvic Fusion" (2024)</t>
+          <t>Autophagolysosomal exocytosis inverts Src kinase onto the cell surface in cancer (2026) | Prognostic Implications of Personalized Circulating Tumor DNA Testing in Patients with Advanced Urothelial Carcinoma Treated with Enfortumab Vedotin ± Pembrolizumab (2026)</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurological Surgery)</t>
+          <t>https://web.archive.org/web/20260710111852/https://bms.ucsf.edu/faculty?page=5</t>
         </is>
       </c>
       <c r="R123" t="inlineStr"/>
@@ -22028,11 +22028,7 @@
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr"/>
       <c r="W123" t="inlineStr"/>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>associate: confirm promoted 2020+</t>
-        </is>
-      </c>
+      <c r="X123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -22045,24 +22041,16 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Quantitative Biosciences Institute (home dept: Bioengineering)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Ling-Ya Chao</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Assistant Professor</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
+          <t>Kevin Lou</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>C</t>
@@ -22075,7 +22063,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Meta-analysis of bilateral centromedian nucleus neuromodulation for epilepsy.</t>
+          <t>Kinase inhibitor design; clinical trial listing in neuro-oncology.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -22083,19 +22071,19 @@
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/695092660</t>
+          <t>https://profiles.ucsf.edu/kevin.lou</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Systematic Review and Meta-Analysis of Bilateral Centromedian Nucleus Neuromodulation for Multifocal and Generalized Epilepsy. (2025)</t>
+          <t>A design approach for bitopic kinase inhibitors (2026)</t>
         </is>
       </c>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurology)</t>
+          <t>https://qbi.ucsf.edu/investigators</t>
         </is>
       </c>
       <c r="R124" t="inlineStr"/>
@@ -22117,12 +22105,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Neurological Surgery</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Min Kang</t>
+          <t>Lee Tan</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -22147,7 +22135,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Multidisciplinary care and clinical trials in myasthenia gravis.</t>
+          <t>Minimally invasive and open spine surgery, including robotic and motion-preservation techniques.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -22155,19 +22143,27 @@
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/181165</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
+          <t>https://researcherprofiles.org/profile/196680</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>When Is Fusion Necessary in Addressing Symptomatic Adjacent Level Pathology - A Commentary on "How to Treat Adjacent-Segment Pathology Following Lumbar Fusion Surgery: Decompression Alone or Decompression With Extended Fusion Surgery?" (2026)</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Safety and Efficacy of Real-Time Intraoperative Ultrasound-Guided Posterolateral Thoracic Diskectomy: Using Technology to Minimize Complication and Improve Surgical Outcome (2026)</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Optimising well-being in myasthenia gravis: a multidisciplinary approach (2026) | Switching to subcutaneous zilucoplan from intravenous complement component 5 inhibitors in generalised myasthenia gravis: a phase IIIb, open-label study (2025)</t>
+          <t>Risk Factors, Biomechanics, and Prevention Strategies for Proximal Junctional Failure in Adult Spinal Deformity Surgery - A Commentary on "Proximal Junctional Failure Development Despite Achieving Ideal Sagittal Correction According to Age-Adjusted Alignment Target in Patients With Adult Spinal Deformity: Risk Factor Analysis of 196 Cases Undergoing Low Thoracic to Pelvic Fusion" (2024)</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurology)</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurological Surgery)</t>
         </is>
       </c>
       <c r="R125" t="inlineStr"/>
@@ -22193,12 +22189,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Neurological Surgery</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Ritchie Chen</t>
+          <t>Ling-Ya Chao</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -22223,7 +22219,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Engineers genetically targeted bioelectronic and optogenetic tools to map and control brain-body circuits.</t>
+          <t>Meta-analysis of bilateral centromedian nucleus neuromodulation for epilepsy.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -22231,23 +22227,19 @@
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/359584750</t>
+          <t>https://researcherprofiles.org/profile/695092660</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Interoceptive modulation of emotions (2025)</t>
-        </is>
-      </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>Integrated Bioelectronic and Optogenetic Methods to Study Brain-Body Circuits (2024)</t>
-        </is>
-      </c>
+          <t>Systematic Review and Meta-Analysis of Bilateral Centromedian Nucleus Neuromodulation for Multifocal and Generalized Epilepsy. (2025)</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurological Surgery)</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurology)</t>
         </is>
       </c>
       <c r="R126" t="inlineStr"/>
@@ -22269,12 +22261,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Neurological Surgery</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Rongze Lu</t>
+          <t>Min Kang</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -22299,7 +22291,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Brain tumor immune evasion mechanisms and chromatin programs in glioblastoma.</t>
+          <t>Multidisciplinary care and clinical trials in myasthenia gravis.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -22307,27 +22299,19 @@
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/317918332</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>Protein phosphatase 2A regulates senescence and immunogenicity in medulloblastoma models (2026)</t>
-        </is>
-      </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>Tumor-intrinsic chromatin programs enforce immune evasion in glioblastoma (2026)</t>
-        </is>
-      </c>
+          <t>https://researcherprofiles.org/profile/181165</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Advances in the understanding and therapeutic manipulation of cancer immune responsiveness: a Society for Immunotherapy of Cancer (SITC) review (2025) | Co-evolution of glioma and immune microenvironment (2024)</t>
+          <t>Optimising well-being in myasthenia gravis: a multidisciplinary approach (2026) | Switching to subcutaneous zilucoplan from intravenous complement component 5 inhibitors in generalised myasthenia gravis: a phase IIIb, open-label study (2025)</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurological Surgery)</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurology)</t>
         </is>
       </c>
       <c r="R127" t="inlineStr"/>
@@ -22353,24 +22337,16 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Psychiatry</t>
+          <t>Neuroscience Graduate Program (faculty)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Sara Chung</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Assistant Professor</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
+          <t>Qili Liu</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
           <t>C</t>
@@ -22383,31 +22359,23 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Developmental psychology: parenting, ADHD and stress in Asian American college students.</t>
+          <t>Fly neurobiology of nutrient-specific appetite (wet lab)</t>
         </is>
       </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>https://researcherprofiles.org/profile/171132582</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>Parsing Day-to-Day Dynamics of ADHD and Perceived Stress in College Students: An Ecological Momentary Assessment Study (2026)</t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>ADHD Knowledge as a Barrier to Problem Recognition in Asian American and Native Hawaiian/Pacific Islander Versus White College Students (2026)</t>
-        </is>
-      </c>
-      <c r="P128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Targeted cravings: Unraveling the drivers of nutrient-specific appetite (2025) | Opposing GPCR signaling programs protein intake setpoint in Drosophila (2024)</t>
+        </is>
+      </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Psychiatry)</t>
+          <t>https://neurograd.ucsf.edu/faculty</t>
         </is>
       </c>
       <c r="R128" t="inlineStr"/>
@@ -22429,17 +22397,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Psychiatry</t>
+          <t>Biomedical Sciences (BMS) PhD program faculty (Wayback 2026-07 copy, pages 0-12 and 26 only); Neurological Surgery; Neuroscience Graduate Program (faculty)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Selena Chan</t>
+          <t>Ritchie Chen</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Asst Professor In Residence</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -22459,7 +22427,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Psychiatry; community care programs, clinical and wellness work.</t>
+          <t>Engineers genetically targeted bioelectronic and optogenetic tools to map and control brain-body circuits.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -22467,15 +22435,19 @@
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/174541</t>
+          <t>https://bms.ucsf.edu/people/ritchie-chen-phd-msc-bs</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Interoceptive modulation of emotions (2025) | Integrated Bioelectronic and Optogenetic Methods to Study Brain-Body Circuits (2024)</t>
+        </is>
+      </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Psychiatry)</t>
+          <t>https://web.archive.org/web/20260710111852/https://bms.ucsf.edu/faculty?page=4</t>
         </is>
       </c>
       <c r="R129" t="inlineStr"/>
@@ -22497,22 +22469,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Neurological Surgery</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Sharon Chiang</t>
+          <t>Rongze Lu</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -22527,7 +22499,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Quality-of-life outcome sets and vagus nerve stimulation outcomes in drug-resistant epilepsy.</t>
+          <t>Brain tumor immune evasion mechanisms and chromatin programs in glioblastoma.</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -22535,23 +22507,27 @@
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/14718920</t>
+          <t>https://researcherprofiles.org/profile/317918332</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>Integrating longitudinal seizure, medication, and quality of life data into epilepsy eare: A randomized crossover study of an Epic-integrated dashboard (2026)</t>
+          <t>Protein phosphatase 2A regulates senescence and immunogenicity in medulloblastoma models (2026)</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Influences of electrode density on intracranial seizure localisation: a single-blinded randomised crossover study (2025)</t>
-        </is>
-      </c>
-      <c r="P130" t="inlineStr"/>
+          <t>Tumor-intrinsic chromatin programs enforce immune evasion in glioblastoma (2026)</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Advances in the understanding and therapeutic manipulation of cancer immune responsiveness: a Society for Immunotherapy of Cancer (SITC) review (2025) | Co-evolution of glioma and immune microenvironment (2024)</t>
+        </is>
+      </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurology)</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurological Surgery)</t>
         </is>
       </c>
       <c r="R130" t="inlineStr"/>
@@ -22560,7 +22536,11 @@
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr"/>
       <c r="W130" t="inlineStr"/>
-      <c r="X130" t="inlineStr"/>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -22573,22 +22553,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Radiology and Biomedical Imaging</t>
+          <t>Psychiatry</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Shinn-Huey Chou</t>
+          <t>Sara Chung</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -22603,7 +22583,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Breast imaging radiologist focused on high-risk screening and radiology training.</t>
+          <t>Developmental psychology: parenting, ADHD and stress in Asian American college students.</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -22611,19 +22591,23 @@
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/540198469</t>
+          <t>https://researcherprofiles.org/profile/171132582</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>The parenthood journey in radiology: Challenges and opportunities (2025)</t>
-        </is>
-      </c>
-      <c r="O131" t="inlineStr"/>
+          <t>Parsing Day-to-Day Dynamics of ADHD and Perceived Stress in College Students: An Ecological Momentary Assessment Study (2026)</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>ADHD Knowledge as a Barrier to Problem Recognition in Asian American and Native Hawaiian/Pacific Islander Versus White College Students (2026)</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Psychiatry)</t>
         </is>
       </c>
       <c r="R131" t="inlineStr"/>
@@ -22632,11 +22616,7 @@
       <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr"/>
       <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>associate: confirm promoted 2020+</t>
-        </is>
-      </c>
+      <c r="X131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -22654,7 +22634,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Stephen Leung</t>
+          <t>Selena Chan</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -22679,7 +22659,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Benzodiazepine tapering recommendations for inpatient and residential care.</t>
+          <t>Psychiatry; community care programs, clinical and wellness work.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -22687,14 +22667,10 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/506961717</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>Toward clarifying ASAM's inpatient and residential benzodiazepine tapering recommendations (2026)</t>
-        </is>
-      </c>
+          <t>https://researcherprofiles.org/profile/174541</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr">
@@ -22721,22 +22697,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Neurological Surgery</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Sze Chun Winson Ho</t>
+          <t>Sharon Chiang</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -22751,7 +22727,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Pediatric neurosurgery and PP2A-targeted immunotherapy for brain tumors.</t>
+          <t>Quality-of-life outcome sets and vagus nerve stimulation outcomes in drug-resistant epilepsy.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
@@ -22759,15 +22735,23 @@
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/325717114</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
+          <t>https://researcherprofiles.org/profile/14718920</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Integrating longitudinal seizure, medication, and quality of life data into epilepsy eare: A randomized crossover study of an Epic-integrated dashboard (2026)</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Influences of electrode density on intracranial seizure localisation: a single-blinded randomised crossover study (2025)</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurological Surgery)</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurology)</t>
         </is>
       </c>
       <c r="R133" t="inlineStr"/>
@@ -22776,11 +22760,7 @@
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr"/>
       <c r="W133" t="inlineStr"/>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t>associate: confirm promoted 2020+</t>
-        </is>
-      </c>
+      <c r="X133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -22793,16 +22773,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Quantitative Biosciences Institute (home dept: Medicine)</t>
+          <t>Radiology and Biomedical Imaging</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Terrelea Wong</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
+          <t>Shinn-Huey Chou</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
       <c r="G134" t="inlineStr">
         <is>
           <t>C</t>
@@ -22815,7 +22803,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Card has no research text or papers.</t>
+          <t>Breast imaging radiologist focused on high-risk screening and radiology training.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -22823,36 +22811,32 @@
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/terrelea.wong</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
+          <t>https://researcherprofiles.org/profile/540198469</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>The parenthood journey in radiology: Challenges and opportunities (2025)</t>
+        </is>
+      </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>https://qbi.ucsf.edu/investigators</t>
-        </is>
-      </c>
-      <c r="R134" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unspecified: </t>
-        </is>
-      </c>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr"/>
       <c r="T134" t="inlineStr"/>
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr"/>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>Search snippet (unfetched; profile 404s via fetch) indicates volunteer clinical professor in Medicine, not a PI; No research text</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr"/>
+      <c r="W134" t="inlineStr"/>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -22870,7 +22854,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tianyi Zhang</t>
+          <t>Stephen Leung</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -22895,7 +22879,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Elder financial exploitation in the digital age.</t>
+          <t>Benzodiazepine tapering recommendations for inpatient and residential care.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -22903,12 +22887,12 @@
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/173787</t>
+          <t>https://researcherprofiles.org/profile/506961717</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>Elder Financial Exploitation in the Digital Age (2023)</t>
+          <t>Toward clarifying ASAM's inpatient and residential benzodiazepine tapering recommendations (2026)</t>
         </is>
       </c>
       <c r="O135" t="inlineStr"/>
@@ -22937,12 +22921,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Neurological Surgery</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Virgina Lee</t>
+          <t>Sze Chun Winson Ho</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -22967,7 +22951,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Genetic variants in SNAP25 and OTUD6B in developmental and epileptic disorders.</t>
+          <t>Pediatric neurosurgery and PP2A-targeted immunotherapy for brain tumors.</t>
         </is>
       </c>
       <c r="J136" t="inlineStr"/>
@@ -22975,19 +22959,15 @@
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/31165493</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>Biallelic OTUD6B variants associated with a Kabuki syndrome‐like disorder in three siblings: A clinical report and literature review (2024)</t>
-        </is>
-      </c>
+          <t>https://researcherprofiles.org/profile/325717114</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurology)</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurological Surgery)</t>
         </is>
       </c>
       <c r="R136" t="inlineStr"/>
@@ -23013,24 +22993,16 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Radiology and Biomedical Imaging</t>
+          <t>Quantitative Biosciences Institute (home dept: Medicine)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Weiya Mu</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Assistant Professor</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
+          <t>Terrelea Wong</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>C</t>
@@ -23043,7 +23015,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Radiology faculty; clinical neuroradiology and imaging anatomy, traumatic brain injury research; no ML described.</t>
+          <t>Card has no research text or papers.</t>
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
@@ -23051,7 +23023,7 @@
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/416657849</t>
+          <t>https://profiles.ucsf.edu/terrelea.wong</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -23059,15 +23031,27 @@
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
-        </is>
-      </c>
-      <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr"/>
+          <t>https://qbi.ucsf.edu/investigators</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unspecified: </t>
+        </is>
+      </c>
       <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr"/>
-      <c r="W137" t="inlineStr"/>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Search snippet (unfetched; profile 404s via fetch) indicates volunteer clinical professor in Medicine, not a PI; No research text</t>
+        </is>
+      </c>
       <c r="X137" t="inlineStr"/>
     </row>
     <row r="138">
@@ -23081,12 +23065,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Biomedical Sciences (BMS) PhD program faculty (Wayback 2026-07 copy, pages 0-12 and 26 only)</t>
+          <t>Psychiatry</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Wendy Yue</t>
+          <t>Tianyi Zhang</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -23111,7 +23095,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Spinal ependymal cell proliferation and opioid signalling.</t>
+          <t>Elder financial exploitation in the digital age.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr"/>
@@ -23119,19 +23103,19 @@
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
         <is>
-          <t>https://bms.ucsf.edu/people/wendy-yue-phd</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
+          <t>https://researcherprofiles.org/profile/173787</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Elder Financial Exploitation in the Digital Age (2023)</t>
+        </is>
+      </c>
       <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr">
-        <is>
-          <t>Endogenous opioid signalling regulates spinal ependymal cell proliferation (2024)</t>
-        </is>
-      </c>
+      <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260710111852/https://bms.ucsf.edu/faculty?page=26</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Psychiatry)</t>
         </is>
       </c>
       <c r="R138" t="inlineStr"/>
@@ -23153,22 +23137,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Radiology and Biomedical Imaging</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Xiao Wu</t>
+          <t>Virgina Lee</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -23183,7 +23167,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Interventional radiology; cryoablation cost-effectiveness and radioembolization outcomes.</t>
+          <t>Genetic variants in SNAP25 and OTUD6B in developmental and epileptic disorders.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr"/>
@@ -23191,23 +23175,19 @@
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/115272775</t>
+          <t>https://researcherprofiles.org/profile/31165493</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Cryoablation Versus Breast-Conserving Surgery for Early-Stage, Low-Risk Breast Cancer ≤ 1.5 cm: A Cost-Effectiveness Analysis (2026)</t>
+          <t>Biallelic OTUD6B variants associated with a Kabuki syndrome‐like disorder in three siblings: A clinical report and literature review (2024)</t>
         </is>
       </c>
       <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr">
-        <is>
-          <t>Radioembolization for Colorectal Liver Metastases: Indications and Outcomes (2026) | Transarterial Embolization Versus Manipulation Under Anesthesia and Arthroscopic Capsular Release for Refractory Adhesive Capsulitis-A Cost-Effectiveness Analysis (2026)</t>
-        </is>
-      </c>
+      <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Neurology)</t>
         </is>
       </c>
       <c r="R139" t="inlineStr"/>
@@ -23216,7 +23196,11 @@
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr"/>
       <c r="W139" t="inlineStr"/>
-      <c r="X139" t="inlineStr"/>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -23234,17 +23218,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Xin Cynthia Wu</t>
+          <t>Weiya Mu</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -23259,7 +23243,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Head and neck imaging radiologist; clinical outcome studies with pembrolizumab.</t>
+          <t>Radiology faculty; clinical neuroradiology and imaging anatomy, traumatic brain injury research; no ML described.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr"/>
@@ -23267,19 +23251,11 @@
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/319885332</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>Statin Use Is Associated With Progression-Free Survival for Recurrent/Metastatic Head and Neck Squamous Cell Carcinoma Treated With Pembrolizumab (2026)</t>
-        </is>
-      </c>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>Metastatic Lymph Node Status Is Associated With Progression-Free Survival in Oral Cavity Squamous Cell Carcinoma Treated With Pembrolizumab (2026)</t>
-        </is>
-      </c>
+          <t>https://researcherprofiles.org/profile/416657849</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr">
         <is>
@@ -23292,11 +23268,7 @@
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr"/>
       <c r="W140" t="inlineStr"/>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>associate: confirm promoted 2020+</t>
-        </is>
-      </c>
+      <c r="X140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -23309,22 +23281,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Radiology and Biomedical Imaging</t>
+          <t>Biomedical Sciences (BMS) PhD program faculty (Wayback 2026-07 copy, pages 0-12 and 26 only); Neuroscience Graduate Program (faculty)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Yi Li</t>
+          <t>Wendy Yue</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -23334,12 +23306,12 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>medical-AI</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Clinical neuroradiology; image processing and analysis for the ABCD neuroimaging study.</t>
+          <t>Spinal ependymal cell proliferation and opioid signalling.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr"/>
@@ -23347,19 +23319,19 @@
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/176541</t>
+          <t>https://bms.ucsf.edu/people/wendy-yue-phd</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Chiari malformation type 1 is associated with a smaller fourth ventricle volume - a multi-cohort replication study (2026)</t>
+          <t>Endogenous opioid signalling regulates spinal ependymal cell proliferation (2024)</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
+          <t>https://web.archive.org/web/20260710111852/https://bms.ucsf.edu/faculty?page=26</t>
         </is>
       </c>
       <c r="R141" t="inlineStr"/>
@@ -23368,11 +23340,7 @@
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr"/>
       <c r="W141" t="inlineStr"/>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>associate: confirm promoted 2020+</t>
-        </is>
-      </c>
+      <c r="X141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -23385,16 +23353,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Quantitative Biosciences Institute (home dept: Biochemistry &amp; Biophysics)</t>
+          <t>Radiology and Biomedical Imaging</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Yifan  Cheng</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
+          <t>Xiao Wu</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr">
         <is>
           <t>C</t>
@@ -23407,7 +23383,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Structural biology and cryo-EM.</t>
+          <t>Interventional radiology; cryoablation cost-effectiveness and radioembolization outcomes.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr"/>
@@ -23415,19 +23391,23 @@
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>https://cryoem.ucsf.edu</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
+          <t>https://researcherprofiles.org/profile/115272775</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Cryoablation Versus Breast-Conserving Surgery for Early-Stage, Low-Risk Breast Cancer ≤ 1.5 cm: A Cost-Effectiveness Analysis (2026)</t>
+        </is>
+      </c>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Structural energetics of cold sensitivity (2026) | Antibody reveals conformational latch regulating dimerization in β- and γ-herpesvirus proteases (2026)</t>
+          <t>Radioembolization for Colorectal Liver Metastases: Indications and Outcomes (2026) | Transarterial Embolization Versus Manipulation Under Anesthesia and Arthroscopic Capsular Release for Refractory Adhesive Capsulitis-A Cost-Effectiveness Analysis (2026)</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>https://qbi.ucsf.edu/investigators</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
         </is>
       </c>
       <c r="R142" t="inlineStr"/>
@@ -23454,7 +23434,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Yoo Jin Lee</t>
+          <t>Xin Cynthia Wu</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -23474,12 +23454,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>medical-AI</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Clinical thoracic/cardiac radiology; MRI image quality studies, some AI-assisted segmentation.</t>
+          <t>Head and neck imaging radiologist; clinical outcome studies with pembrolizumab.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr"/>
@@ -23487,16 +23467,20 @@
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/159721860</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr">
-        <is>
-          <t>Determinants of image quality in respiratory triggered free breathing lung MRI at 0.55 T in adults (2026) | AI-Assisted segmentation and volumetric reconstruction of radiographs through multi-angular scintillation imaging (2026)</t>
-        </is>
-      </c>
+          <t>https://researcherprofiles.org/profile/319885332</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Statin Use Is Associated With Progression-Free Survival for Recurrent/Metastatic Head and Neck Squamous Cell Carcinoma Treated With Pembrolizumab (2026)</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Metastatic Lymph Node Status Is Associated With Progression-Free Survival in Oral Cavity Squamous Cell Carcinoma Treated With Pembrolizumab (2026)</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr">
         <is>
           <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
@@ -23520,29 +23504,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>University of California San Francisco</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Neuroscience Graduate Program (faculty)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Bob X. Wang</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Associate Professor of Instruction</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>associate</t>
-        </is>
-      </c>
+          <t>Xin Duan</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
           <t>C</t>
@@ -23555,31 +23531,23 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Biosphere-atmosphere interactions, carbon and hydrological cycles; teaching-track chemistry.</t>
+          <t>Molecular and genetic assembly of neural circuits, optic neuropathy (wet lab)</t>
         </is>
       </c>
       <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>wangx@usf.edu</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/wang.aspx</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/wang.aspx</t>
-        </is>
-      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Cell-intrinsic vulnerability and immune activation cooperate to drive degeneration in a mitochondrial complex I deficiency model of optic neuropathy (2026) | Molecular and cellular dynamics of the developing human neocortex (2025)</t>
+        </is>
+      </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/index.aspx</t>
+          <t>https://neurograd.ucsf.edu/faculty</t>
         </is>
       </c>
       <c r="R144" t="inlineStr"/>
@@ -23588,11 +23556,7 @@
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
       <c r="W144" t="inlineStr"/>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>associate: confirm promoted 2020+</t>
-        </is>
-      </c>
+      <c r="X144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -23600,22 +23564,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>University of California San Francisco</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Radiology and Biomedical Imaging</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Christian Tang</t>
+          <t>Yi Li</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Associate Professor of Instruction</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -23630,52 +23594,40 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>medical-AI</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>No research text or papers on the card.</t>
+          <t>Clinical neuroradiology; image processing and analysis for the ABCD neuroimaging study.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>ctang3@usf.edu</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/index.aspx</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>https://researcherprofiles.org/profile/176541</t>
+        </is>
+      </c>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Chiari malformation type 1 is associated with a smaller fourth ventricle volume - a multi-cohort replication study (2026)</t>
+        </is>
+      </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/index.aspx</t>
-        </is>
-      </c>
-      <c r="R145" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unspecified: </t>
-        </is>
-      </c>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr"/>
+      <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr"/>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>teaching faculty, not a PI; not ML</t>
-        </is>
-      </c>
+      <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
           <t>associate: confirm promoted 2020+</t>
@@ -23688,29 +23640,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>University of California San Francisco</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Quantitative Biosciences Institute (home dept: Biochemistry &amp; Biophysics)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Jin Jia</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Assistant Professor</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
+          <t>Yifan  Cheng</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
           <t>C</t>
@@ -23723,31 +23667,27 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Chemistry department; no research text, presumed chemistry lab.</t>
+          <t>Structural biology and cryo-EM.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>jinjia@usf.edu</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/jia.aspx</t>
-        </is>
-      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/jia.aspx</t>
+          <t>https://cryoem.ucsf.edu</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Structural energetics of cold sensitivity (2026) | Antibody reveals conformational latch regulating dimerization in β- and γ-herpesvirus proteases (2026)</t>
+        </is>
+      </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/index.aspx</t>
+          <t>https://qbi.ucsf.edu/investigators</t>
         </is>
       </c>
       <c r="R146" t="inlineStr"/>
@@ -23764,27 +23704,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>University of California San Francisco</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Molecular Pharmacology and Physiology</t>
+          <t>Radiology and Biomedical Imaging</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Lei Wang</t>
+          <t>Yoo Jin Lee</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -23794,40 +23734,32 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>medical-AI</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Blood pressure and renal function physiology; kidney injury and transplantation mechanisms.</t>
+          <t>Clinical thoracic/cardiac radiology; MRI image quality studies, some AI-assisted segmentation.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>leiwang@usf.edu</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>https://health.usf.edu/medicine/mpp/faculty/leiwang</t>
-        </is>
-      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
-          <t>https://health.usf.edu/medicine/mpp/faculty/leiwang</t>
+          <t>https://researcherprofiles.org/profile/159721860</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Limb Ischemia-Reperfusion Injury in Rats is partially mediated by enhancing Necroptosis via Phosphorylation of RIPK1 and MLKL (2026) | Glomerulus-targeted nanotherapy via collagen IV-α3 binding enhances renal immunoregulation in lupus nephritis (2026)</t>
+          <t>Determinants of image quality in respiratory triggered free breathing lung MRI at 0.55 T in adults (2026) | AI-Assisted segmentation and volumetric reconstruction of radiographs through multi-angular scintillation imaging (2026)</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>https://health.usf.edu/medicine/mpp/faculty/</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
         </is>
       </c>
       <c r="R147" t="inlineStr"/>
@@ -23836,7 +23768,11 @@
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr"/>
       <c r="W147" t="inlineStr"/>
-      <c r="X147" t="inlineStr"/>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -23849,22 +23785,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chemical, Biological and Materials Engineering</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Weizhong Zou</t>
+          <t>Bob X. Wang</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor of Instruction</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -23879,43 +23815,31 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Polymer and materials engineering with multiscale modelling and data-driven tools.</t>
+          <t>Biosphere-atmosphere interactions, carbon and hydrological cycles; teaching-track chemistry.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>wzou@usf.edu</t>
+          <t>wangx@usf.edu</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/engineering/chbme/people/zou.aspx</t>
+          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/wang.aspx</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>https://thezoulab.com/</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>Real-Time Quantification of Molecular-Level Dynamic Behaviors Underpinning Shear Thinning in End-Linked Associative Polymer Networks (2024)</t>
-        </is>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>Toughening and Imparting Deconstructability to 3D-Printed Glassy Thermosets with "Transferinker" Additives (2024)</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>Addition to: "Toughening and Imparting Deconstructability to 3D-Printed Glassy Thermosets with "Transferinker" Additives" (2025)</t>
-        </is>
-      </c>
+          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/wang.aspx</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/engineering/chbme/people/index.aspx</t>
+          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/index.aspx</t>
         </is>
       </c>
       <c r="R148" t="inlineStr"/>
@@ -23924,7 +23848,11 @@
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr"/>
       <c r="W148" t="inlineStr"/>
-      <c r="X148" t="inlineStr"/>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -23942,12 +23870,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Wenqi (Vince) Liu</t>
+          <t>Christian Tang</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Associate Professor of Instruction</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -23967,43 +23895,47 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Host-guest chemistry for sensing, catalysis and separations; functional molecular materials.</t>
+          <t>No research text or papers on the card.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>wenqi@usf.edu</t>
+          <t>ctang3@usf.edu</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>https://nam04.safelinks.protection.outlook.com/?url=http%3A%2F%2Fwww.vincentchemistry.com%2F&amp;data=04%7C01%7Cpaigeromero%40usf.edu%7C27a9b8f622b44829bb3908d96d88e19d%7C741bf7dee2e546df8d6782607df9deaa%7C0%7C0%7C637661256924716608%7CUnknown%7CTWFpbGZsb3d8eyJWIjoiMC4wLjAwMDAiLCJQIjoiV2luMzIiLCJBTiI6Ik1haWwiLCJXVCI6Mn0%3D%7C1000&amp;sdata=mbuJDqqgQC2eHi%2FxUp%2BM4dMT2Zde%2FpwxCJtcyUDXB4g%3D&amp;reserved=0</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>https://nam04.safelinks.protection.outlook.com/?url=http%3A%2F%2Fwww.vincentchemistry.com%2F&amp;data=04%7C01%7Cpaigeromero%40usf.edu%7C27a9b8f622b44829bb3908d96d88e19d%7C741bf7dee2e546df8d6782607df9deaa%7C0%7C0%7C637661256924716608%7CUnknown%7CTWFpbGZsb3d8eyJWIjoiMC4wLjAwMDAiLCJQIjoiV2luMzIiLCJBTiI6Ik1haWwiLCJXVCI6Mn0%3D%7C1000&amp;sdata=mbuJDqqgQC2eHi%2FxUp%2BM4dMT2Zde%2FpwxCJtcyUDXB4g%3D&amp;reserved=0</t>
-        </is>
-      </c>
+          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/index.aspx</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>Mechanically Planar Chiral Molecules by a SuFEx-Auxiliary Approach (2026) | Oxonium-Embedded Benzo[&amp;lt;i&amp;gt;b&amp;lt;/i&amp;gt;]perylene: A Redox-Switchable Closed-Shell π‑Cation, and Its Paramagnetic Charge-Transfer Salt with TCNE&amp;lt;sup&amp;gt;•&amp;lt;/sup&amp;gt; (2026)</t>
-        </is>
-      </c>
+      <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr">
         <is>
           <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/index.aspx</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr"/>
-      <c r="S149" t="inlineStr"/>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unspecified: </t>
+        </is>
+      </c>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr"/>
-      <c r="W149" t="inlineStr"/>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>teaching faculty, not a PI; not ML</t>
+        </is>
+      </c>
       <c r="X149" t="inlineStr">
         <is>
           <t>associate: confirm promoted 2020+</t>
@@ -24021,12 +23953,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Molecular Medicine</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Xuewei Wang</t>
+          <t>Jin Jia</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -24051,23 +23983,23 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Neuroregeneration and neuroprotection; axon regeneration wet-lab biology.</t>
+          <t>Chemistry department; no research text, presumed chemistry lab.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>xueweiwang@usf.edu</t>
+          <t>jinjia@usf.edu</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>https://health.usf.edu/medicine/molecularmedicine/faculty/xueweiwang</t>
+          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/jia.aspx</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>https://cloud.usf.edu/FacultyDirectory/api/get/profile/xueweiwang/document/cv</t>
+          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/jia.aspx</t>
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
@@ -24075,7 +24007,7 @@
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>https://health.usf.edu/medicine/molecularmedicine/faculty/</t>
+          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/index.aspx</t>
         </is>
       </c>
       <c r="R150" t="inlineStr"/>
@@ -24097,12 +24029,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Molecular Pharmacology and Physiology</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Ying Wang</t>
+          <t>Lei Wang</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -24127,31 +24059,35 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Chemistry education research on student affect and learning.</t>
+          <t>Blood pressure and renal function physiology; kidney injury and transplantation mechanisms.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>yingw@usf.edu</t>
+          <t>leiwang@usf.edu</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/ying-wang.aspx</t>
+          <t>https://health.usf.edu/medicine/mpp/faculty/leiwang</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>https://sites.google.com/view/wang-research-group/home</t>
+          <t>https://health.usf.edu/medicine/mpp/faculty/leiwang</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Limb Ischemia-Reperfusion Injury in Rats is partially mediated by enhancing Necroptosis via Phosphorylation of RIPK1 and MLKL (2026) | Glomerulus-targeted nanotherapy via collagen IV-α3 binding enhances renal immunoregulation in lupus nephritis (2026)</t>
+        </is>
+      </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/index.aspx</t>
+          <t>https://health.usf.edu/medicine/mpp/faculty/</t>
         </is>
       </c>
       <c r="R151" t="inlineStr"/>
@@ -24173,22 +24109,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Molecular Pharmacology and Physiology</t>
+          <t>Chemical, Biological and Materials Engineering</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Ying Yang</t>
+          <t>Weizhong Zou</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -24203,35 +24139,43 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Lymphatic vasculature biology and lymphatic valve molecular mechanisms.</t>
+          <t>Polymer and materials engineering with multiscale modelling and data-driven tools.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>yingyang@usf.edu</t>
+          <t>wzou@usf.edu</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>https://health.usf.edu/medicine/mpp/faculty/yingyang</t>
+          <t>https://www.usf.edu/engineering/chbme/people/zou.aspx</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>https://health.usf.edu/medicine/mpp/faculty/yingyang</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
+          <t>https://thezoulab.com/</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Real-Time Quantification of Molecular-Level Dynamic Behaviors Underpinning Shear Thinning in End-Linked Associative Polymer Networks (2024)</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Toughening and Imparting Deconstructability to 3D-Printed Glassy Thermosets with "Transferinker" Additives (2024)</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Lymphatic Malformations With Activating KRAS Mutations Impair Lymphatic Valve Development Through Matrix Metalloproteinases (2026) | Rictor, an mTORC2 Protein, Regulates Murine Lymphatic Valve Formation Through the AKT-FOXO1 Signaling (2024)</t>
+          <t>Addition to: "Toughening and Imparting Deconstructability to 3D-Printed Glassy Thermosets with "Transferinker" Additives" (2025)</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>https://health.usf.edu/medicine/mpp/faculty/</t>
+          <t>https://www.usf.edu/engineering/chbme/people/index.aspx</t>
         </is>
       </c>
       <c r="R152" t="inlineStr"/>
@@ -24240,11 +24184,7 @@
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
       <c r="W152" t="inlineStr"/>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>associate: confirm promoted 2020+</t>
-        </is>
-      </c>
+      <c r="X152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -24257,22 +24197,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Molecular Pharmacology and Physiology</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Yonggang Ma</t>
+          <t>Wenqi (Vince) Liu</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -24287,39 +24227,35 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Immune regulation of heart failure after myocardial infarction; cardiovascular biology.</t>
+          <t>Host-guest chemistry for sensing, catalysis and separations; functional molecular materials.</t>
         </is>
       </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>yma4@usf.edu</t>
+          <t>wenqi@usf.edu</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>https://health.usf.edu/medicine/mpp/faculty/yma4</t>
+          <t>https://nam04.safelinks.protection.outlook.com/?url=http%3A%2F%2Fwww.vincentchemistry.com%2F&amp;data=04%7C01%7Cpaigeromero%40usf.edu%7C27a9b8f622b44829bb3908d96d88e19d%7C741bf7dee2e546df8d6782607df9deaa%7C0%7C0%7C637661256924716608%7CUnknown%7CTWFpbGZsb3d8eyJWIjoiMC4wLjAwMDAiLCJQIjoiV2luMzIiLCJBTiI6Ik1haWwiLCJXVCI6Mn0%3D%7C1000&amp;sdata=mbuJDqqgQC2eHi%2FxUp%2BM4dMT2Zde%2FpwxCJtcyUDXB4g%3D&amp;reserved=0</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>https://health.usf.edu/medicine/mpp/faculty/yma4</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>Glucocorticoids impair T lymphopoiesis after myocardial infarction (2024)</t>
-        </is>
-      </c>
+          <t>https://nam04.safelinks.protection.outlook.com/?url=http%3A%2F%2Fwww.vincentchemistry.com%2F&amp;data=04%7C01%7Cpaigeromero%40usf.edu%7C27a9b8f622b44829bb3908d96d88e19d%7C741bf7dee2e546df8d6782607df9deaa%7C0%7C0%7C637661256924716608%7CUnknown%7CTWFpbGZsb3d8eyJWIjoiMC4wLjAwMDAiLCJQIjoiV2luMzIiLCJBTiI6Ik1haWwiLCJXVCI6Mn0%3D%7C1000&amp;sdata=mbuJDqqgQC2eHi%2FxUp%2BM4dMT2Zde%2FpwxCJtcyUDXB4g%3D&amp;reserved=0</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Aging diminishes thymic output, reduces naive T cells, promotes memory T-cell accumulation, and impairs thymic regeneration (2026) | Lung endothelial cell senescence impairs barrier function and promotes neutrophil adhesion and migration (2025)</t>
+          <t>Mechanically Planar Chiral Molecules by a SuFEx-Auxiliary Approach (2026) | Oxonium-Embedded Benzo[&amp;lt;i&amp;gt;b&amp;lt;/i&amp;gt;]perylene: A Redox-Switchable Closed-Shell π‑Cation, and Its Paramagnetic Charge-Transfer Salt with TCNE&amp;lt;sup&amp;gt;•&amp;lt;/sup&amp;gt; (2026)</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>https://health.usf.edu/medicine/mpp/faculty/</t>
+          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/index.aspx</t>
         </is>
       </c>
       <c r="R153" t="inlineStr"/>
@@ -24328,7 +24264,331 @@
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr"/>
       <c r="W153" t="inlineStr"/>
-      <c r="X153" t="inlineStr"/>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>4</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>University of South Florida</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Molecular Medicine</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Xuewei Wang</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Neuroregeneration and neuroprotection; axon regeneration wet-lab biology.</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>xueweiwang@usf.edu</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>https://health.usf.edu/medicine/molecularmedicine/faculty/xueweiwang</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>https://cloud.usf.edu/FacultyDirectory/api/get/profile/xueweiwang/document/cv</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>https://health.usf.edu/medicine/molecularmedicine/faculty/</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr"/>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr"/>
+      <c r="W154" t="inlineStr"/>
+      <c r="X154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>4</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>University of South Florida</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Ying Wang</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Chemistry education research on student affect and learning.</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>yingw@usf.edu</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/ying-wang.aspx</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/view/wang-research-group/home</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>https://www.usf.edu/arts-sciences/departments/chemistry/faculty/index.aspx</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr"/>
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
+      <c r="W155" t="inlineStr"/>
+      <c r="X155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>4</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>University of South Florida</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Molecular Pharmacology and Physiology</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Ying Yang</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Lymphatic vasculature biology and lymphatic valve molecular mechanisms.</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>yingyang@usf.edu</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>https://health.usf.edu/medicine/mpp/faculty/yingyang</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>https://health.usf.edu/medicine/mpp/faculty/yingyang</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Lymphatic Malformations With Activating KRAS Mutations Impair Lymphatic Valve Development Through Matrix Metalloproteinases (2026) | Rictor, an mTORC2 Protein, Regulates Murine Lymphatic Valve Formation Through the AKT-FOXO1 Signaling (2024)</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>https://health.usf.edu/medicine/mpp/faculty/</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr"/>
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr"/>
+      <c r="W156" t="inlineStr"/>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>4</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>University of South Florida</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Molecular Pharmacology and Physiology</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Yonggang Ma</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Immune regulation of heart failure after myocardial infarction; cardiovascular biology.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>yma4@usf.edu</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>https://health.usf.edu/medicine/mpp/faculty/yma4</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>https://health.usf.edu/medicine/mpp/faculty/yma4</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Glucocorticoids impair T lymphopoiesis after myocardial infarction (2024)</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Aging diminishes thymic output, reduces naive T cells, promotes memory T-cell accumulation, and impairs thymic regeneration (2026) | Lung endothelial cell senescence impairs barrier function and promotes neutrophil adhesion and migration (2025)</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>https://health.usf.edu/medicine/mpp/faculty/</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr"/>
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
+      <c r="W157" t="inlineStr"/>
+      <c r="X157" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24903,7 +25163,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>people 3 | need email 10 | check 17 | dropped C 47</t>
+          <t>people 3 | need email 10 | check 17 | dropped C 51</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -28046,7 +28306,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>done</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -28055,7 +28315,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>99</v>
+      </c>
+      <c r="F79" t="n">
+        <v>99</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -28064,7 +28327,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>403 to our fetch (bot-blocked); not worked around. Program lists ~100 faculty; most are in Profiles depts (Neurology, Psychiatry, Biochem etc.) already rostered</t>
+          <t>bot-check blocked for us; page saved by the applicant in her own browser (data/snapshots/manual/ucsf-neurograd-faculty.pdf); 99 names parsed by code (~100 per catalog); titles from our UCSF Profiles rosters (66/99)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>

--- a/data/export/batch1.xlsx
+++ b/data/export/batch1.xlsx
@@ -567,17 +567,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>University of California San Francisco</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bellini College of AI, Cybersecurity and Computing</t>
+          <t>Bioengineering and Therapeutic Sciences (Profiles dept Bioengineering)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ning Wang</t>
+          <t>Brian Cheung</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -597,57 +597,57 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>trustworthy-ML</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ACL (6) 1</t>
+          <t>ICML 3, Trans. Mach. Learn. Res. 2, WACV 1, NeurIPS 1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AI-type dept: Bellini College of AI, Cybersecurity and Comp</t>
+          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Federated learning, network intrusion detection, adversarial ML, differential privacy, LLMs in cybersecurity.</t>
+          <t>Bioengineering and therapeutic sciences; no research text on card.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ningw@usf.edu</t>
+          <t>bcheung@ucsf.edu</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/ning-wang.aspx</t>
+          <t>https://briancheung.github.io</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://trust-ai-lab.github.io/index.html</t>
+          <t>https://discolab.org/</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Learning from Textual Radiology Reports: A Benchmark Dataset for Coronary CT Angiography</t>
+          <t>Words That Make Language Models Perceive</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>EarlyShield: Early-Stage Screening for Robust Personalized Federated Learning</t>
+          <t>What if Eye...? Computationally Recreating Vision Evolution</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Bioengineering)</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -657,26 +657,26 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Yes: Tasnimul Hossain Tomal joined SPRAI lab as a PhD student. (Aug. 2026; openings link on lab site not read)</t>
+          <t>Yes: Open positions Postdocs, students, and research engineers interested in AI for science.</t>
         </is>
       </c>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Contact Email: bcheung@ucsf.edu</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Agents/reliability and evaluation work connects loosely to trustworthy-AI security; federated medical imaging (Aegis) is the only bio link.</t>
+          <t>Convergent representations across modalities (Platonic Representation Hypothesis) connects to her BioCLIP+EfficientNet representation/evaluation work (arborphy) and probing/interpretability work (interp); AI for scientific discovery fits Bio-AI goal.</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>security-focused ML</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>dossier reader says B: Mostly AI security/privacy rather than core ML; in scope but weaker.; dossier recruiting: quote not on page, re-check</t>
-        </is>
-      </c>
+          <t>Input homepage was a UCSF Profiles page; true lab site is discolab.org; Dept is Bioengineering and Therapeutic Sciences (School of Pharmacy); doctoral program to apply through not stated (check BTS vs BMI); Lab described as 'post AGI' and 'Last updated: Oct 2026': very recently launched</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -684,17 +684,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Psychological &amp; Brain Sciences; Graduate Program for Neuroscience (faculty); Center for Systems Neuroscience</t>
+          <t>Bellini College of AI, Cybersecurity and Computing</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Arthur Lee</t>
+          <t>Ning Wang</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -709,56 +709,62 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NeuroAI</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>trustworthy-ML</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ACL (6) 1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
+          <t>AI-type dept: Bellini College of AI, Cybersecurity and Comp</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Card has no research text or papers.</t>
+          <t>Federated learning, network intrusion detection, adversarial ML, differential privacy, LLMs in cybersecurity.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>artlee@bu.edu</t>
+          <t>ningw@usf.edu</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/psych/profile/arthur-sangil-lee/</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/ning-wang.aspx</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>http://thedecodinglab.com/</t>
+          <t>https://trust-ai-lab.github.io/index.html</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Neural decoders: saving the baby from the bathwater</t>
+          <t>Learning from Textual Radiology Reports: A Benchmark Dataset for Coronary CT Angiography</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Distinguishing deception from its confounds by improving the validity of fMRI-based neural prediction</t>
+          <t>EarlyShield: Early-Stage Screening for Robust Personalized Federated Learning</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/psych/people/faculty/</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -768,28 +774,24 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Yes: We are looking for Ph.D. students interested in our research.</t>
+          <t>Yes: Tasnimul Hossain Tomal joined SPRAI lab as a PhD student. (Aug. 2026; openings link on lab site not read)</t>
         </is>
       </c>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Please feel free to send an email to Arthur (see contact) to let him know to look out for your application.</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>His interest in validating neural decoders (confounds, interpretability) connects to the EEG motor-imagery decoder with run-grouped validation.</t>
+          <t>Agents/reliability and evaluation work connects loosely to trustworthy-AI security; federated medical imaging (Aegis) is the only bio link.</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>psychology department; applications go through Psychology or Neuroscience program, not CS/Stats</t>
+          <t>security-focused ML</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>also listed as Arthur Sangil Lee</t>
+          <t>dossier reader says B: Mostly AI security/privacy rather than core ML; in scope but weaker.; dossier recruiting: quote not on page, re-check</t>
         </is>
       </c>
     </row>
@@ -799,17 +801,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cold Spring Harbor Laboratory</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CSHL Faculty (Research)</t>
+          <t>Psychological &amp; Brain Sciences; Graduate Program for Neuroscience (faculty); Center for Systems Neuroscience</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Helen Hou</t>
+          <t>Arthur Lee</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -832,9 +834,7 @@
           <t>NeuroAI</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
@@ -843,43 +843,39 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Brain-body motor control; ML video analysis and neural encoding from behavior via Gaussian splatting.</t>
+          <t>Card has no research text or papers.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>hou@cshl.edu</t>
+          <t>artlee@bu.edu</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>https://www.cshl.edu/research/faculty-staff/helen-hou/</t>
+          <t>https://www.bu.edu/psych/profile/arthur-sangil-lee/</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://houlab.org</t>
+          <t>http://thedecodinglab.com/</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Cheese3D enables sensitive detection and analysis of whole-face movement in mice</t>
+          <t>Neural decoders: saving the baby from the bathwater</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>A generic noninvasive neuromotor interface for human-computer interaction</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>A case study on the use of end-to-end real-time monitoring to ensure quality of oral solid dosage forms in pharmaceutical development. (2025) | Chemical genetic screens reveal defective lysosomal trafficking as synthetic lethal with NF1 loss (2024)</t>
-        </is>
-      </c>
+          <t>Distinguishing deception from its confounds by improving the validity of fMRI-based neural prediction</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.cshl.edu/research/faculty-staff/</t>
+          <t>https://www.bu.edu/psych/people/faculty/</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -889,24 +885,28 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Yes: We are actively recruiting at all levels, including but not limited to Students, Postdocs, and Research Technicians.</t>
+          <t>Yes: We are looking for Ph.D. students interested in our research.</t>
         </is>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Please get in touch via hou [at] cshl.edu and include your CV/resume and contact information of three references. (IMPORTANT: Please include the term #hou_lab _ candidate somewhere in your message to slip through the spam filter) | *Please contact Helen before application if you are interested in applying to the CSHL or SBU programs and work in our lab.</t>
+          <t>Please feel free to send an email to Arthur (see contact) to let him know to look out for your application.</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Cheese3D (ML video analysis of facial movement) and the CSHL BioAI PhD program fit the applicant's interest in ML for biological/neural data (calcium imaging, EEG decoding).</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr"/>
+          <t>His interest in validating neural decoders (confounds, interpretability) connects to the EEG motor-imagery decoder with run-grouped validation.</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>psychology department; applications go through Psychology or Neuroscience program, not CS/Stats</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dossier start_year: no snapshot, re-check</t>
+          <t>also listed as Arthur Sangil Lee</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Cold Spring Harbor Laboratory</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bellini College of AI, Cybersecurity and Computing</t>
+          <t>CSHL Faculty (Research)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fengchun Qiao</t>
+          <t>Helen Hou</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -941,62 +941,62 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>trustworthy-ML</t>
+          <t>NeuroAI</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ICML 2, CVPR 1, NeurIPS 1, ICLR 1, IEEE Trans. Pattern Anal. Mach. Intell. 1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AI-type dept: Bellini College of AI, Cybersecurity and Comp</t>
+          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Trustworthy ML focused on out-of-distribution generalization, using robust optimization and graph theory.</t>
+          <t>Brain-body motor control; ML video analysis and neural encoding from behavior via Gaussian splatting.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>fengchun@usf.edu</t>
+          <t>hou@cshl.edu</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/fengchun_qiao.aspx</t>
+          <t>https://www.cshl.edu/research/faculty-staff/helen-hou/</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://joffery.github.io/joffery/</t>
+          <t>https://houlab.org</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Structure-informed Risk Minimization for Robust Ensemble Learning</t>
+          <t>Cheese3D enables sensitive detection and analysis of whole-face movement in mice</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>SeafloorAI: A Large-scale Vision-Language Dataset for Seafloor Geological Survey</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
+          <t>A generic noninvasive neuromotor interface for human-computer interaction</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>A case study on the use of end-to-end real-time monitoring to ensure quality of oral solid dosage forms in pharmaceutical development. (2025) | Chemical genetic screens reveal defective lysosomal trafficking as synthetic lethal with NF1 loss (2024)</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
+          <t>https://www.cshl.edu/research/faculty-staff/</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1006,18 +1006,26 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unspecified: </t>
+          <t>Yes: We are actively recruiting at all levels, including but not limited to Students, Postdocs, and Research Technicians.</t>
         </is>
       </c>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Please get in touch via hou [at] cshl.edu and include your CV/resume and contact information of three references. (IMPORTANT: Please include the term #hou_lab _ candidate somewhere in your message to slip through the spam filter) | *Please contact Helen before application if you are interested in applying to the CSHL or SBU programs and work in our lab.</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Arborphy BioCLIP fusion with leakage-aware evaluation connects to OOD generalization / distribution-shift robustness.</t>
+          <t>Cheese3D (ML video analysis of facial movement) and the CSHL BioAI PhD program fit the applicant's interest in ML for biological/neural data (calcium imaging, EEG decoding).</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>dossier start_year: no snapshot, re-check</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1025,22 +1033,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bellini College of AI, Cybersecurity and Computing</t>
+          <t>Mechanical Eng &amp; Materials Science; Center for Computational &amp; Digital Health Innovation</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Guangjing Wang</t>
+          <t>Boyuan Chen</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Assistant Professor in the Thomas Lord Department of Mechanical Engineering and Mate</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1055,53 +1063,57 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>trustworthy-ML</t>
+          <t>core-ML/CV</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ACL (Findings) 1, ACL (1) 1, CVPR 1</t>
+          <t>Trans. Mach. Learn. Res. 4, ICRA 3, CoRL 3, NeurIPS 1, IROS 1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AI-type dept: Bellini College of AI, Cybersecurity and Comp</t>
+          <t>AI-type dept: Mechanical Eng &amp; Materials Science</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Adaptive attacks on audio watermarking and speech spoofing detector benchmarks; also soil sensing system.</t>
+          <t>Robotics: learns realistic lip motions for humanoid face robots; physical AI.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>guangjingwang@usf.edu</t>
+          <t>boyuan.chen@duke.edu</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/guangjing-wang.aspx</t>
+          <t>https://mems.duke.edu/people/boyuan-chen/</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/guangjing-wang.aspx</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>SoilNutri: A Passive Metasurface-based, Low-cost System for Soil Moisture and Nitrogen Monitoring (2026) | Learning to Evade: Adaptive Attacks on Audio Watermarking (2026)</t>
-        </is>
-      </c>
+          <t>http://generalroboticslab.com/</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ORCH: Organizational Principles Enable Collective Intelligence in Embodied AI</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Online Sim-to-Real Adaptation via Closed-Loop System Modeling</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
+          <t>https://mems.duke.edu/people?s=&amp;group=faculty-primary,faculty-secondary</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1116,39 +1128,35 @@
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>multi-agent system with blind cross-model verification connects to his agentic-AI work.</t>
-        </is>
-      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>no personal/lab site found after 2 searches; official page only</t>
+          <t>robotics, little overlap with applicant projects</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>fit based on name-matched papers only: check they are this person's</t>
+          <t>dossier reader says B: Robotics / physical intelligence; AI-for-science pillar is a stretch for Bio-AI goal. Not A.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>University of California San Francisco</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bioengineering and Therapeutic Sciences (Profiles dept Bioengineering)</t>
+          <t>Bellini College of AI, Cybersecurity and Computing</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Brian Cheung</t>
+          <t>Fengchun Qiao</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1168,57 +1176,57 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>trustworthy-ML</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ICML 3, Trans. Mach. Learn. Res. 2, WACV 1, NeurIPS 1</t>
+          <t>ICML 2, CVPR 1, NeurIPS 1, ICLR 1, IEEE Trans. Pattern Anal. Mach. Intell. 1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
+          <t>AI-type dept: Bellini College of AI, Cybersecurity and Comp</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Bioengineering and therapeutic sciences; no research text on card.</t>
+          <t>Trustworthy ML focused on out-of-distribution generalization, using robust optimization and graph theory.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>bcheung@ucsf.edu</t>
+          <t>fengchun@usf.edu</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>https://briancheung.github.io</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/fengchun_qiao.aspx</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://discolab.org/</t>
+          <t>https://joffery.github.io/joffery/</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Words That Make Language Models Perceive</t>
+          <t>Structure-informed Risk Minimization for Robust Ensemble Learning</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>What if Eye...? Computationally Recreating Vision Evolution</t>
+          <t>SeafloorAI: A Large-scale Vision-Language Dataset for Seafloor Geological Survey</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Bioengineering)</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1228,118 +1236,102 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Yes: Open positions Postdocs, students, and research engineers interested in AI for science.</t>
+          <t xml:space="preserve">Unspecified: </t>
         </is>
       </c>
       <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Contact Email: bcheung@ucsf.edu</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Convergent representations across modalities (Platonic Representation Hypothesis) connects to her BioCLIP+EfficientNet representation/evaluation work (arborphy) and probing/interpretability work (interp); AI for scientific discovery fits Bio-AI goal.</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Input homepage was a UCSF Profiles page; true lab site is discolab.org; Dept is Bioengineering and Therapeutic Sciences (School of Pharmacy); doctoral program to apply through not stated (check BTS vs BMI); Lab described as 'post AGI' and 'Last updated: Oct 2026': very recently launched</t>
-        </is>
-      </c>
+          <t>Arborphy BioCLIP fusion with leakage-aware evaluation connects to OOD generalization / distribution-shift robustness.</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Center for Computational &amp; Digital Health Innovation; Biomedical Engineering</t>
+          <t>Bellini College of AI, Cybersecurity and Computing</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pengfei Song</t>
+          <t>Guangjing Wang</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>medical-AI</t>
+          <t>trustworthy-ML</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>IJCAI/ECAI 1</t>
+          <t>ACL (Findings) 1, ACL (1) 1, CVPR 1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
+          <t>AI-type dept: Bellini College of AI, Cybersecurity and Comp</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ultrafast and super-resolution ultrasound imaging, including deep learning applications in ultrasound.</t>
+          <t>Adaptive attacks on audio watermarking and speech spoofing detector benchmarks; also soil sensing system.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>pengfei.song@duke.edu</t>
+          <t>guangjingwang@usf.edu</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>https://comphealth.duke.edu/people/pengfei-song/</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/guangjing-wang.aspx</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://songlab.bme.duke.edu</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Longitudinal Awake Mouse Brain Imaging Using Functional Ultrasound and Functional Ultrasound Localization Microscopy</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Improved Microbubble Tracking for Super-resolution Ultrasound Localization Microscopy Using a Bi-Directional Long Short-term Memory Neural Network</t>
-        </is>
-      </c>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/guangjing-wang.aspx</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Noninvasive whole-brain imaging of glymphatic dynamics (2026) | Near-infrared photochromic miniprotein enables photoacoustic molecular imaging of acute inflammation and intracellular antigens (2026)</t>
+          <t>SoilNutri: A Passive Metasurface-based, Low-cost System for Soil Moisture and Nitrogen Monitoring (2026) | Learning to Evade: Adaptive Attacks on Audio Watermarking (2026)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://comphealth.duke.edu/our-team/?rendered_page=5</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1349,24 +1341,24 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Yes: We are always looking for new members to join our lab. Please email Prof. Song ( pengfei.song@duke.edu ) if you are interested!</t>
+          <t xml:space="preserve">Unspecified: </t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>His neuroimaging and neural-network-based microbubble tracking connect to my self-supervised calcium-imaging denoising (calcium).</t>
+          <t>multi-agent system with blind cross-model verification connects to his agentic-AI work.</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>primarily ultrasound imaging, DL is secondary</t>
+          <t>no personal/lab site found after 2 searches; official page only</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+</t>
+          <t>fit based on name-matched papers only: check they are this person's</t>
         </is>
       </c>
     </row>
@@ -1376,17 +1368,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>University of California San Francisco</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bakar Computational Health Sciences Institute</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Irene Chen</t>
+          <t>Xiaomin Lin</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1406,57 +1398,61 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>medical-AI</t>
+          <t>core-ML/CV</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ICRA 4, IROS 3, WACV (Workshops) 1, AAAI 1, ECCV (65) 1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
+          <t>AI-type dept: Electrical Engineering</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Machine learning methods for improving and equalizing clinical care; auditing algorithmic bias.</t>
+          <t>Robotics, perception and edge AI for underwater and agricultural autonomy; deep learning rhino detection.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>iychen@berkeley.edu</t>
+          <t>xlin2@usf.edu</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>https://irenechen.net</t>
+          <t>https://www.usf.edu/engineering/ece/faculty-staff/lin-xiaomin.aspx</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://irenechen.net</t>
+          <t>https://xiaominlin.github.io/</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Falsifying Sparse Autoencoder Reasoning Features in Language Models.</t>
+          <t>WaterGen</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Aggregated Individual Reporting for Post-Deployment Evaluation.</t>
+          <t>RAZOR</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Investigating CAR-T Treatment Access for Multiple Myeloma Patients Using Real-World Evidence (2026) | The MI-CLAIM-GEN checklist for generative artificial intelligence in health (2025)</t>
+          <t>Automated rhinoceros detection in satellite imagery using deep learning (2025) | A Kinodynamic Model for Dubins-Based Trajectory Planning in Precision Oyster Harvesting (2025)</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://bakarinstitute.ucsf.edu/people-at-bakar</t>
+          <t>https://www.usf.edu/engineering/ece/faculty-staff/index.aspx</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1466,21 +1462,21 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Yes: The Chen Lab is looking for 1-2 PhD students starting Fall 2027.</t>
+          <t>Yes: I am actively recruiting PhD students to join my lab starting Spring 2027 and Fall 2027.</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Apply through the Computational Precision Health or EECS (AI-H) admissions portals. | Unfortunately due to volume, we cannot respond to all emails about PhD admissions, but I do read every email I receive. | (1) core ML methods particularly around data quality or evaluation, or (2) developing AI methods to improve healthcare including modeling clinical/health data.</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Her SAE-feature falsification and evaluation work matches the applicant's LLM circuit-tracing/probing project (null causal conclusions with sham controls) and leakage-aware evaluation work.</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr"/>
+          <t xml:space="preserve">Please read my Research Statement (PDF) before applying. | Competitive applicants typically hold an MS in a related field and have at least one top-tier publication. | Prospective students (not currently at USF) — fill out this application form . Please send an email to me as well, with your CV, transcripts, and a brief statement of your research interests and career goals. Tell me which of my papers or directions interest you and why. | You wrote the email yourself: Prospective Student - Bulls </t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>site requires AI-disclosure tag (subject 'Prospective Student - Bulls 3Q') for AI-drafted emails; expects &gt;=1 top-tier publication (applicant has none); paper titles are only short names on homepage news (WaterGen ECCV 2026, RAZOR CVPR 2026 Findings)</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1489,27 +1485,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Computational Biomedicine; Bioinformatics Program</t>
+          <t>Electrical &amp; Computer Engineering</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Chao Zhang</t>
+          <t>Neil Gong</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Assistant Professor of Medicine</t>
+          <t>Associate Professor of Electrical and Computer Engineering</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1523,45 +1519,57 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NeurIPS 3, ICLR 2, ACL (1) 1, ACL (Findings) 1, EMNLP 1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
+          <t>AI-type dept: Electrical &amp; Computer Engineering</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Computational biomedicine; single-cell data integration methods such as CellDiffusion plus aging omics.</t>
+          <t>Zero-shot autonomous microscopy for scalable characterization of 2D materials.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>chz2009@bu.edu</t>
+          <t>neil.gong@duke.edu</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>https://www.bumc.bu.edu/compbiomed/people/faculty/</t>
+          <t>https://ece.duke.edu/people/neil-gong/</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>http://class.bu.edu/~chz2009/</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+          <t>https://people.duke.edu/~zg70/index.html</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>A Critical Evaluation of Defenses against Prompt Injection Attacks</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Fingerprinting LLMs via Prompt Injection</t>
+        </is>
+      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Environmental and genetic risk factors of depression converge on neuronal dysfunction driven by changes in cholesterol homeostasis (2026) | Calorie Restriction Attenuates Transcriptional Aging Signatures in White Matter Oligodendrocytes and Immune Cells of the Monkey Brain (2026)</t>
+          <t>Zero-Shot Autonomous Microscopy for Scalable and Intelligent Characterization of 2D Materials (2025)</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://www.bumc.bu.edu/compbiomed/people/faculty/</t>
+          <t>https://ece.duke.edu/faculty</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1571,20 +1579,24 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Yes: PhD in Computational Biology, Computer Science, Data Science, Bioinformatics, Biostatistics, Mathematics or other related quantitative areas.</t>
+          <t>Yes: I am looking for postdocs, Ph.D. students, master's students, and undergraduate researchers. If you are interested in pursuing a Ph.D., please submit your application to Duke ECE.</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>His work on evaluating prompt-injection defenses and secure agentic AI connects to my multi-agent system with verification and trust gating (agents).</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Lab site publications list shows no 2024-2026 papers (latest 2022); site looks dated; profiles.bu.edu page failed to fetch (SSL), so title/CellDiffusion claim not verified from it; Email not verbatim on any fetched page</t>
+          <t>first-pass summary describes different work (microscopy of 2D materials); possibly wrong person/mismatch; warns he receives many emails and may not respond</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>fit based on name-matched papers only: check they are this person's</t>
+          <t>associate: confirm promoted 2020+; fit based on name-matched papers only: check they are this person's</t>
         </is>
       </c>
     </row>
@@ -1594,85 +1606,87 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bioinformatics Program; Biomedical Genetics</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Xiaoling Zhang</t>
+          <t>Danyang Zhuo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Associate Professor of Medicine and Biostatistics Section of Biomedical Genetics  / School of Medicine</t>
+          <t>Hamelsky Family Assistant Professor of Computer Science</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stats-methods</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>core-ML/CV</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NeurIPS 2, AAAI 1, UAI 1, AISTATS 1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
+          <t>AI-type dept: Computer Science</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Methods for epidemiology, EHR, genetics and functional genomics data; Alzheimer genetics.</t>
+          <t>Machine learning systems and datacenter/cloud computing.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>zhangxl@bu.edu</t>
+          <t>danyang.zhuo@duke.edu</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>https://sites.bu.edu/zhanglab/</t>
+          <t>https://scholars.duke.edu/person/danyang.zhuo</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>https://sites.bu.edu/zhanglab/</t>
+          <t>https://danyangzhuo.com/</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Alzheimer’s Disease Risk Prediction from Clinical and Social Determinants of Health: A Machine Learning Cohort Study in UK Biobank</t>
+          <t>DecodeShare: Tracing the Shared Pathways of LLM Decode-Time Decisions.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>A multi-ancestry polygenic risk score for Alzheimer disease is associated with cognitive decline, hippocampal atrophy and neuropathological hallmarks in diverse populations</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Blood PCSK9 Impacts Alzheimer's Disease Risk in an &amp;lt;i&amp;gt;APOE&amp;lt;/i&amp;gt; Genotype-Dependent Manner: A Prospective Cohort Study (2026) | Corrigendum to 'Circulating C-reactive protein influences polygenic risk of inflammatory genes expressed in brain endothelia for Alzheimer's disease' Neurobiology of Disease 219 (2026) Article Number 107257 (2026)</t>
-        </is>
-      </c>
+          <t>Phantora: Maximizing Code Reuse in Simulation-based Machine Learning System Performance Estimation.</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/bioinformatics/people/faculty/</t>
+          <t>https://users.cs.duke.edu/people/faculty</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1682,7 +1696,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Yes: We are always looking for talented and self-motivated graduate students and post-doc fellows interested in Bioinformatics/Computational Biology, Statistic Genetics, Functional Genomics</t>
+          <t>Yes: I am always looking for new PhD students. Please apply to Duke CS if you are interested in working with me!</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -1690,12 +1704,12 @@
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Associate Professor; promotion year not found, may not be recent; Applied genetic epidemiology; ML is secondary</t>
+          <t>systems, not ML methods; site email differs from input email</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+; dossier reader says C: Statistical genetics/Alzheimer genomics; recruiting is open but little deep-ML overlap and no honest project hook.</t>
+          <t>dossier reader says C: Networking and GPU systems; no overlap with applicant's stats/Bio-AI background. Downgraded A-&gt;C. Note site email is dan</t>
         </is>
       </c>
     </row>
@@ -1710,74 +1724,78 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Duke Discovery AI; Biomedical Engineering; Biostatistics &amp; Bioinformatics (SOM); CBB program; University Program in Genetics &amp; Genomics</t>
+          <t>Statistical Science; Duke Institute for Brain Sciences (network faculty)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Yi Zhang</t>
+          <t>Simon Mak</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Assistant Professor of Neurosurgery, Biostatistics &amp; Bioinformatics, Biomedical Engineering</t>
+          <t>Associate Professor of Statistical Science</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>AI-for-science</t>
+          <t>stats-methods</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>KDD 2, AAAI 1, AISTATS 1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AI-type dept: Biostatistics &amp; Bioinformatics (SOM)</t>
+          <t>AI-type dept: Statistical Science</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Develops ML methods for single-cell genomics and spatial transcriptomics in tumors.</t>
+          <t>Gaussian process surrogate modeling for computer experiments and sensitivity analysis.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>yi.zhang@duke.edu</t>
+          <t>sm769@duke.edu</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>https://scholars.duke.edu/person/yi.zhang</t>
+          <t>https://scholars.duke.edu/person/SimonTszFung.Mak</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>http://yi-zhang-compbio-lab.github.io/</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>STHD: probabilistic cell typing of single Spots in whole Transcriptome spatial data with High Definition” BioRxiv Preprint (2024). Genome Biology (2025)</t>
-        </is>
-      </c>
+          <t>https://sites.google.com/view/simonmak/</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Isotonic surrogate modeling for computer experiments with many input variables (2026) | Fast multitask Gaussian processes, with application to surrogate modeling of the quark-gluon plasma (2026)</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://discoveryai.duke.edu/our-team-2/</t>
+          <t>https://stat.duke.edu/people/faculty</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1787,20 +1805,24 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Yes: We are recruiting Postdocs, Duke students, and researchers .</t>
+          <t>Yes: If you are interested in joining our research group, please send a CV and transcript to sm769[at]duke.edu, with a description of your research background &amp; interests.</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Her ML methods for high-resolution spatial transcriptomics are close to the representation-learning-on-imaging-like-data theme of my calcium-imaging work (calcium).</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr"/>
+          <t>His interpretable, science-guided statistical models connect to my Bayesian latent-variable modeling of the FlyWire connectome (flywire).</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>associate; promotion year not found; no papers list on site (CV/Scholar only)</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dossier reader says A: Directly ML for biological data (single-cell, spatial, pathology); recruiting students via CBB/Biostat/UPGG. Upgraded B-</t>
+          <t>associate: confirm promoted 2020+; fit based on name-matched papers only: check they are this person's; dossier reader says B: Strong stats/ML for science, but applications are physics/engineering, not biology; associate, start year unknown. A-&gt;B.</t>
         </is>
       </c>
     </row>
@@ -1810,87 +1832,83 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Icahn School of Medicine at Mount Sinai</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Genetics and Genomic Sciences; PhD Biomedical Sciences: Artificial Intelligence training area</t>
+          <t>Electrical &amp; Computer Engineering</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Kuan-Lin Huang</t>
+          <t>Tingjun Chen</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASSOCIATE PROFESSOR</t>
+          <t>Nortel Networks Assistant Professor of Electrical and Computer Engineering</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>AI-for-science</t>
+          <t>core-ML/CV</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ICRA 2, IROS 1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
+          <t>AI-type dept: Electrical &amp; Computer Engineering</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Computational cancer genomics and proteomics; genetic dependency and precision oncology.</t>
+          <t>Disaggregated machine learning via in-physics computing at radio frequency.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>kuan-lin.huang@mssm.edu</t>
+          <t>tingjun.chen@duke.edu</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/kuan-lin-huang</t>
+          <t>https://ece.duke.edu/people/tingjun-chen/</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>https://labs.icahn.mssm.edu/kuanhuanglab/join/</t>
+          <t>https://tingjunchen.com/</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Mutation impact on mRNA versus protein expression across human cancers.</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>A clinical benchmark of public self-supervised pathology foundation models.</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Expression-driven genetic dependency reveals targets for precision oncology (2026) | KEAP1 loss-of-function suppresses immunogenic ferroptosis and limits PD-1 blockade efficacy through an NRF2-FSP1 pathway (2026)</t>
-        </is>
-      </c>
+          <t>Disaggregated machine learning via in-physics computing at radio frequency (2026)</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470001513038352&amp;selectedFilter=department&amp;tab=faculty&amp;start=50</t>
+          <t>https://ece.duke.edu/faculty</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1900,28 +1918,22 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Yes: We welcome inquiries from Ph.D. &amp; Master students of the Graduate School of Biomedical Sciences at the Icahn School of Medicine at Mount Sinai (ISMMS)</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>We welcome inquiries from Ph.D. &amp; Master students of the Graduate School of Biomedical Sciences at the Icahn School of Medicine at Mount Sinai (ISMMS) | please send Dr. Kuan-lin Huang your GitHub with code samples and a paragraph describing your interests in our work. | We focus on computational works</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>The pathology foundation-model benchmark connects to arborphy (stress-testing BioCLIP-based foundation-model fusion with a leakage-aware protocol).</t>
-        </is>
-      </c>
+          <t>Yes: I am always looking for motivated B.S., M.S., Ph.D. students and Postdocs to join my group at Duke ECE. If interested, email me your CV, transcript, and a brief note on your research interests.</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>PhD inquiries explicitly framed for students already in Mount Sinai GSBS; apply via GSBS, then rotate; start_year not found (associate)</t>
+          <t>not actually ML-focused</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+</t>
+          <t>dossier reader says C: Wireless/optical networking hardware; ML is peripheral. A-&gt;C.</t>
         </is>
       </c>
     </row>
@@ -1931,22 +1943,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Icahn School of Medicine at Mount Sinai</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Diagnostic, Molecular and Interventional Radiology; BMEII core + AI; PhD Biomedical Sciences: Artificial Intelligence training area</t>
+          <t>Center for Computational &amp; Digital Health Innovation; Biomedical Engineering</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Xiang Xu</t>
+          <t>Pengfei Song</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASSOCIATE PROFESSOR</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1964,8 +1976,14 @@
           <t>medical-AI</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>IJCAI/ECAI 1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
@@ -1973,39 +1991,43 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>MRI and NMR method development (CEST imaging); hybrid self-supervised learning for MRI reconstruction and denoising.</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>self-supervised denoising of calcium imaging</t>
-        </is>
-      </c>
+          <t>Ultrafast and super-resolution ultrasound imaging, including deep learning applications in ultrasound.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>xiang.xu@mssm.edu</t>
+          <t>pengfei.song@duke.edu</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/xiang-xu</t>
+          <t>https://comphealth.duke.edu/people/pengfei-song/</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>https://labs.icahn.mssm.edu/xiang-xu-lab/</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+          <t>https://songlab.bme.duke.edu</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Longitudinal Awake Mouse Brain Imaging Using Functional Ultrasound and Functional Ultrasound Localization Microscopy</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Improved Microbubble Tracking for Super-resolution Ultrasound Localization Microscopy Using a Bi-Directional Long Short-term Memory Neural Network</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Dynamic glucose-enhanced MRI in brain tumors (2026) | Hybrid learning: a combination of self-supervised and supervised learning for joint MRI reconstruction and denoising in low-field MRI (2026)</t>
+          <t>Noninvasive whole-brain imaging of glymphatic dynamics (2026) | Near-infrared photochromic miniprotein enables photoacoustic molecular imaging of acute inflammation and intracellular antigens (2026)</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470074622153001&amp;selectedFilter=department&amp;tab=faculty&amp;start=220</t>
+          <t>https://comphealth.duke.edu/our-team/?rendered_page=5</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2015,24 +2037,24 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Yes: We are always looking for graduate students and post-doc fellows.</t>
+          <t>Yes: We are always looking for new members to join our lab. Please email Prof. Song ( pengfei.song@duke.edu ) if you are interested!</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Interested candidates should send their CV to xiang.xu@mssm.edu.</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>His neuroimaging and neural-network-based microbubble tracking connect to my self-supervised calcium-imaging denoising (calcium).</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>MRI physics/chemistry methods; no ML on lab site; publications page lists nothing 2024-26</t>
+          <t>primarily ultrasound imaging, DL is secondary</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+; dossier reader says C: Lab is NMR/MRI (CEST) methods development; no machine learning stated on site.</t>
+          <t>associate: confirm promoted 2020+</t>
         </is>
       </c>
     </row>
@@ -2047,35 +2069,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Biological and Medical Informatics (BMI) PhD program core+affiliate faculty (Wayback 2026-05 copy); Neurology</t>
+          <t>Bakar Computational Health Sciences Institute</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Jingjing Li</t>
+          <t>Irene Chen</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Associate Professor, Neurology</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>AI-for-science</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>medical-AI</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
@@ -2084,35 +2108,43 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Single-cell multiome and proteome atlases of developing brain; deep learning on personal genomes.</t>
+          <t>Machine learning methods for improving and equalizing clinical care; auditing algorithmic bias.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>jingjing.li@ucsf.edu</t>
+          <t>iychen@berkeley.edu</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>https://www.complexdisease.org/</t>
+          <t>https://irenechen.net</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>https://www.complexdisease.org/</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+          <t>https://irenechen.net</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Falsifying Sparse Autoencoder Reasoning Features in Language Models.</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Aggregated Individual Reporting for Post-Deployment Evaluation.</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Single-cell proteomic landscape of the developing human brain (2026) | Single-cell spatiotemporal dissection of the human maternal-fetal interface (2026)</t>
+          <t>Investigating CAR-T Treatment Access for Multiple Myeloma Patients Using Real-World Evidence (2026) | The MI-CLAIM-GEN checklist for generative artificial intelligence in health (2025)</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260517152053/https://bmi.ucsf.edu/people/faculty</t>
+          <t>https://bakarinstitute.ucsf.edu/people-at-bakar</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2122,30 +2154,22 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Yes: Postdocs and graduate students in computational and experimental biology.</t>
+          <t>Yes: The Chen Lab is looking for 1-2 PhD students starting Fall 2027.</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Send a CV, a short note on your interests, and three references to jingjing.li@ucsf.edu</t>
+          <t>Apply through the Computational Precision Health or EECS (AI-H) admissions portals. | Unfortunately due to volume, we cannot respond to all emails about PhD admissions, but I do read every email I receive. | (1) core ML methods particularly around data quality or evaluation, or (2) developing AI methods to improve healthcare including modeling clinical/health data.</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Calcium-imaging/self-supervised denoising and FlyWire latent-type work connect to single-cell atlases and deep learning on genomes.</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>papers list is JS-collapsed ('Show all papers'); only venue/year tags seen (Nature 2025, Nat Biotech 2026), no titles</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>associate: confirm promoted 2020+; dossier recruiting: no snapshot, re-check</t>
-        </is>
-      </c>
+          <t>Her SAE-feature falsification and evaluation work matches the applicant's LLM circuit-tracing/probing project (null causal conclusions with sham controls) and leakage-aware evaluation work.</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2153,22 +2177,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mechanical Eng &amp; Materials Science; Center for Computational &amp; Digital Health Innovation</t>
+          <t>Computational Biomedicine; Bioinformatics Program</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Boyuan Chen</t>
+          <t>Chao Zhang</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Assistant Professor in the Thomas Lord Department of Mechanical Engineering and Mate</t>
+          <t>Assistant Professor of Medicine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2178,62 +2202,54 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>core-ML/CV</t>
+          <t>AI-for-science</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Trans. Mach. Learn. Res. 4, ICRA 3, CoRL 3, NeurIPS 1, IROS 1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AI-type dept: Mechanical Eng &amp; Materials Science</t>
+          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Robotics: learns realistic lip motions for humanoid face robots; physical AI.</t>
+          <t>Computational biomedicine; single-cell data integration methods such as CellDiffusion plus aging omics.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>boyuan.chen@duke.edu</t>
+          <t>chz2009@bu.edu</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>https://mems.duke.edu/people/boyuan-chen/</t>
+          <t>https://www.bumc.bu.edu/compbiomed/people/faculty/</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>http://generalroboticslab.com/</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>ORCH: Organizational Principles Enable Collective Intelligence in Embodied AI</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Online Sim-to-Real Adaptation via Closed-Loop System Modeling</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr"/>
+          <t>http://class.bu.edu/~chz2009/</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Environmental and genetic risk factors of depression converge on neuronal dysfunction driven by changes in cholesterol homeostasis (2026) | Calorie Restriction Attenuates Transcriptional Aging Signatures in White Matter Oligodendrocytes and Immune Cells of the Monkey Brain (2026)</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://mems.duke.edu/people?s=&amp;group=faculty-primary,faculty-secondary</t>
+          <t>https://www.bumc.bu.edu/compbiomed/people/faculty/</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2243,7 +2259,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unspecified: </t>
+          <t>Yes: PhD in Computational Biology, Computer Science, Data Science, Bioinformatics, Biostatistics, Mathematics or other related quantitative areas.</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
@@ -2251,12 +2267,12 @@
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>robotics, little overlap with applicant projects</t>
+          <t>Lab site publications list shows no 2024-2026 papers (latest 2022); site looks dated; profiles.bu.edu page failed to fetch (SSL), so title/CellDiffusion claim not verified from it; Email not verbatim on any fetched page</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>dossier reader says B: Robotics / physical intelligence; AI-for-science pillar is a stretch for Bio-AI goal. Not A.</t>
+          <t>fit based on name-matched papers only: check they are this person's</t>
         </is>
       </c>
     </row>
@@ -2266,27 +2282,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Duke AI Health (Faculty Affiliates); Biostatistics &amp; Bioinformatics (SOM); CBB program</t>
+          <t>Bioinformatics Program; Biomedical Genetics</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chuan Hong</t>
+          <t>Xiaoling Zhang</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biostatistics &amp; Bioinformatics</t>
+          <t>Associate Professor of Medicine and Biostatistics Section of Biomedical Genetics  / School of Medicine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2296,49 +2312,55 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>medical-AI</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>NeurIPS 1</t>
-        </is>
-      </c>
+          <t>stats-methods</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AI-type dept: Biostatistics &amp; Bioinformatics (SOM)</t>
+          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ML and LLMs on EHR data: representation learning, LLM screening, cardiovascular risk.</t>
+          <t>Methods for epidemiology, EHR, genetics and functional genomics data; Alzheimer genetics.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>chuan.hong@duke.edu</t>
+          <t>zhangxl@bu.edu</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/profile/chuan-hong</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+          <t>https://sites.bu.edu/zhanglab/</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>https://sites.bu.edu/zhanglab/</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Alzheimer’s Disease Risk Prediction from Clinical and Social Determinants of Health: A Machine Learning Cohort Study in UK Biobank</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>A multi-ancestry polygenic risk score for Alzheimer disease is associated with cognitive decline, hippocampal atrophy and neuropathological hallmarks in diverse populations</t>
+        </is>
+      </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Representation learning to advance multi-institutional studies with electronic health record data from US and France (2026) | Leveraging LLMs for Title and Abstract Screening for Systematic Review: A Cost-effective Dynamic Few-shot Learning Approach (2026)</t>
+          <t>Blood PCSK9 Impacts Alzheimer's Disease Risk in an &amp;lt;i&amp;gt;APOE&amp;lt;/i&amp;gt; Genotype-Dependent Manner: A Prospective Cohort Study (2026) | Corrigendum to 'Circulating C-reactive protein influences polygenic risk of inflammatory genes expressed in brain endothelia for Alzheimer's disease' Neurobiology of Disease 219 (2026) Article Number 107257 (2026)</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://aihealth.duke.edu/people/</t>
+          <t>https://www.bu.edu/bioinformatics/people/faculty/</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2348,22 +2370,20 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unspecified: </t>
-        </is>
-      </c>
-      <c r="W17" t="n">
-        <v>2022</v>
-      </c>
+          <t>Yes: We are always looking for talented and self-motivated graduate students and post-doc fellows interested in Bioinformatics/Computational Biology, Statistic Genetics, Functional Genomics</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>no lab site or research text fetched; themes unverified</t>
+          <t>Associate Professor; promotion year not found, may not be recent; Applied genetic epidemiology; ML is secondary</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>fit based on name-matched papers only: check they are this person's</t>
+          <t>associate: confirm promoted 2020+; dossier reader says C: Statistical genetics/Alzheimer genomics; recruiting is open but little deep-ML overlap and no honest project hook.</t>
         </is>
       </c>
     </row>
@@ -2378,22 +2398,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mathematics; Duke Discovery AI; Biostatistics &amp; Bioinformatics (SOM); CBB program</t>
+          <t>Duke Discovery AI; Biomedical Engineering; Biostatistics &amp; Bioinformatics (SOM); CBB program; University Program in Genetics &amp; Genomics</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Jichun Xie</t>
+          <t>Yi Zhang</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Associate Professor of Biostatistics &amp; Bioinformatics</t>
+          <t>Assistant Professor of Neurosurgery, Biostatistics &amp; Bioinformatics, Biomedical Engineering</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2407,57 +2427,45 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>J. Mach. Learn. Res. 1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AI-type dept: Mathematics</t>
+          <t>AI-type dept: Biostatistics &amp; Bioinformatics (SOM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Sequence-to-function models, cell annotation and rare-variant association methods for genomics.</t>
+          <t>Develops ML methods for single-cell genomics and spatial transcriptomics in tumors.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>jichun.xie@duke.edu</t>
+          <t>yi.zhang@duke.edu</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>https://scholars.duke.edu/person/jichun.xie</t>
+          <t>https://scholars.duke.edu/person/yi.zhang</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://jichunxie.github.io/</t>
+          <t>http://yi-zhang-compbio-lab.github.io/</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Single-cell and spatial detection of senescent cells using DeepScence. Cell Genomics (2025)</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>B-Lightning: Using bait genes for marker gene hunting in single-cell data with complex heterogeneity. Briefings in Bioinformatics (2025)</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>B-Lightning: using bait genes for marker gene hunting in single-cell data with complex heterogeneity (2024) | Single-cell landscape analysis unravels molecular programming of the human B cell compartment in chronic GVHD (2023)</t>
-        </is>
-      </c>
+          <t>STHD: probabilistic cell typing of single Spots in whole Transcriptome spatial data with High Definition” BioRxiv Preprint (2024). Genome Biology (2025)</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://math.duke.edu/people/faculty</t>
+          <t>https://discoveryai.duke.edu/our-team-2/</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2467,24 +2475,20 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unspecified: </t>
+          <t>Yes: We are recruiting Postdocs, Duke students, and researchers .</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Her theme of combining classical statistical models with AI models for reliability and interpretability connects to my leakage-aware evaluation of fusion models (arborphy).</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>news last dated Jun 2024</t>
-        </is>
-      </c>
+          <t>Her ML methods for high-resolution spatial transcriptomics are close to the representation-learning-on-imaging-like-data theme of my calcium-imaging work (calcium).</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+</t>
+          <t>dossier reader says A: Directly ML for biological data (single-cell, spatial, pathology); recruiting students via CBB/Biostat/UPGG. Upgraded B-</t>
         </is>
       </c>
     </row>
@@ -2494,27 +2498,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Icahn School of Medicine at Mount Sinai</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Biostatistics &amp; Bioinformatics (SOM); CBB program; Duke Discovery AI</t>
+          <t>Genetics and Genomic Sciences; PhD Biomedical Sciences: Artificial Intelligence training area</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Zhicheng Ji</t>
+          <t>Kuan-Lin Huang</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biostatistics &amp; Bioinformatics</t>
+          <t>ASSOCIATE PROFESSOR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2528,57 +2532,53 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>CVPR Workshops 1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AI-type dept: Biostatistics &amp; Bioinformatics (SOM)</t>
+          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cell-state TWAS, temporal expression modeling and LLM-based single-cell preprocessing.</t>
+          <t>Computational cancer genomics and proteomics; genetic dependency and precision oncology.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>zhicheng.ji@duke.edu</t>
+          <t>kuan-lin.huang@mssm.edu</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/profile/zhicheng-ji</t>
+          <t>https://profiles.icahn.mssm.edu/kuan-lin-huang</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>https://zji90.github.io/</t>
+          <t>https://labs.icahn.mssm.edu/kuanhuanglab/join/</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Zhuang H, Ji Z* . PreTSA: computationally efficient modeling of temporal and spatial gene expression patterns. 2026. Genome Biology</t>
+          <t>Mutation impact on mRNA versus protein expression across human cancers.</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Vispro improves imaging analysis for Visium spatial transcriptomics. 2025. Genome Biology</t>
+          <t>A clinical benchmark of public self-supervised pathology foundation models.</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Transcriptome-wide association studies at cell-state level using single-cell eQTL data (2026) | PreTSA: computationally efficient modeling of temporal and spatial gene expression patterns (2026)</t>
+          <t>Expression-driven genetic dependency reveals targets for precision oncology (2026) | KEAP1 loss-of-function suppresses immunogenic ferroptosis and limits PD-1 blockade efficacy through an NRF2-FSP1 pathway (2026)</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/people/faculty?page=3</t>
+          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470001513038352&amp;selectedFilter=department&amp;tab=faculty&amp;start=50</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2588,22 +2588,28 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Unspecified: PhD Students : Huimin Wang, Haotian Zhuang, Xingyuan Zhang, Pengyu Li</t>
-        </is>
-      </c>
-      <c r="W19" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X19" t="inlineStr"/>
+          <t>Yes: We welcome inquiries from Ph.D. &amp; Master students of the Graduate School of Biomedical Sciences at the Icahn School of Medicine at Mount Sinai (ISMMS)</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>We welcome inquiries from Ph.D. &amp; Master students of the Graduate School of Biomedical Sciences at the Icahn School of Medicine at Mount Sinai (ISMMS) | please send Dr. Kuan-lin Huang your GitHub with code samples and a paragraph describing your interests in our work. | We focus on computational works</t>
+        </is>
+      </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>His AI methods for biomedical images and LLM evaluation connect to my calcium-imaging denoising and my evaluation-focused work (calcium).</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr"/>
+          <t>The pathology foundation-model benchmark connects to arborphy (stress-testing BioCLIP-based foundation-model fusion with a leakage-aware protocol).</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>PhD inquiries explicitly framed for students already in Mount Sinai GSBS; apply via GSBS, then rotate; start_year not found (associate)</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>fit based on name-matched papers only: check they are this person's; dossier reader says A: Bio-AI: deep learning, LLMs, spatial transcriptomics/imaging; has PhD students. Upgraded B-&gt;A. Programs listed are only ; also listed as Jason Ji</t>
+          <t>associate: confirm promoted 2020+</t>
         </is>
       </c>
     </row>
@@ -2618,22 +2624,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Windreich AI and Human Health; Neuroscience</t>
+          <t>Diagnostic, Molecular and Interventional Radiology; BMEII core + AI; PhD Biomedical Sciences: Artificial Intelligence training area</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Baihan Lin</t>
+          <t>Xiang Xu</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ASSISTANT PROFESSOR | Artificial Intelligence and Human Health</t>
+          <t>ASSOCIATE PROFESSOR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2646,14 +2652,8 @@
           <t>medical-AI</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>IJCAI 1</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
@@ -2661,35 +2661,39 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>AI and human health; speech acoustic analysis to screen cognitive impairment; mania speech; AI governance in consumer health.</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>MRI and NMR method development (CEST imaging); hybrid self-supervised learning for MRI reconstruction and denoising.</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>self-supervised denoising of calcium imaging</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>baihan.lin@mssm.edu</t>
+          <t>xiang.xu@mssm.edu</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>https://icahn.mssm.edu/profiles/baihan-lin</t>
+          <t>https://profiles.icahn.mssm.edu/xiang-xu</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>https://www.bytesofminds.com/</t>
+          <t>https://labs.icahn.mssm.edu/xiang-xu-lab/</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Acoustic Analysis of Primary Care Patient-Clinician Conversations to Screen for Cognitive Impairment (2026) | Temporal elements of speech in mania.  (2026)</t>
+          <t>Dynamic glucose-enhanced MRI in brain tumors (2026) | Hybrid learning: a combination of self-supervised and supervised learning for joint MRI reconstruction and denoising in low-field MRI (2026)</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://icahn.mssm.edu/about/artificial-intelligence/faculty</t>
+          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470074622153001&amp;selectedFilter=department&amp;tab=faculty&amp;start=220</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2699,28 +2703,24 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Unspecified: If you want to work with us, or on something adjacent, get in touch.</t>
+          <t>Yes: We are always looking for graduate students and post-doc fellows.</t>
         </is>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
-          <t>If you want to work with us, or on something adjacent, get in touch.</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>EEG motor-imagery decoder project connects to the lab's brain-computer-interface theme.</t>
-        </is>
-      </c>
+          <t>Interested candidates should send their CV to xiang.xu@mssm.edu.</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>no papers list fetched (publications page not retrieved); search snippet mentions earlier open-position postings via baihan.lin@mssm.edu (not fetched)</t>
+          <t>MRI physics/chemistry methods; no ML on lab site; publications page lists nothing 2024-26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>fit based on name-matched papers only: check they are this person's</t>
+          <t>associate: confirm promoted 2020+; dossier reader says C: Lab is NMR/MRI (CEST) methods development; no machine learning stated on site.</t>
         </is>
       </c>
     </row>
@@ -2730,27 +2730,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>University of California San Francisco</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bioinformatics Program; Biomedical Genetics</t>
+          <t>Biological and Medical Informatics (BMI) PhD program core+affiliate faculty (Wayback 2026-05 copy); Neurology</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lei Hou</t>
+          <t>Jingjing Li</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Assistant Professor, Biomedical Genetics /  School of Medicine</t>
+          <t>Associate Professor, Neurology</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2772,35 +2772,35 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Systems genomics and regulatory genomics for brain-related disease biomarkers.</t>
+          <t>Single-cell multiome and proteome atlases of developing brain; deep learning on personal genomes.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>leihou@bu.edu</t>
+          <t>jingjing.li@ucsf.edu</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>https://hougroup.xyz/</t>
+          <t>https://www.complexdisease.org/</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://hougroup.xyz/</t>
+          <t>https://www.complexdisease.org/</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Genotype epigenome phenotype integration reveals peripheral immune contributions to type I bipolar disorder (2026) | Peripheral vascular function, including endothelium-dependent measures, and dementia risk: The Framingham Heart Study (2026)</t>
+          <t>Single-cell proteomic landscape of the developing human brain (2026) | Single-cell spatiotemporal dissection of the human maternal-fetal interface (2026)</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/bioinformatics/people/faculty/</t>
+          <t>https://web.archive.org/web/20260517152053/https://bmi.ucsf.edu/people/faculty</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2810,20 +2810,28 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Unspecified: We are hiring postdocs, interns, and data analysts!</t>
+          <t>Yes: Postdocs and graduate students in computational and experimental biology.</t>
         </is>
       </c>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Send a CV, a short note on your interests, and three references to jingjing.li@ucsf.edu</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Calcium-imaging/self-supervised denoising and FlyWire latent-type work connect to single-cell atlases and deep learning on genomes.</t>
+        </is>
+      </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>No 2024-2026 papers on lab publications page (latest 2023); Site hiring postdocs/interns/analysts only; no PhD recruiting stated; Mostly genomics/genetics, light ML</t>
+          <t>papers list is JS-collapsed ('Show all papers'); only venue/year tags seen (Nature 2025, Nat Biotech 2026), no titles</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>dossier reader says C: Genetics-focused lab with no stated PhD recruiting and no honest project link.</t>
+          <t>associate: confirm promoted 2020+; dossier recruiting: no snapshot, re-check</t>
         </is>
       </c>
     </row>
@@ -2833,79 +2841,87 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Center for Computational &amp; Digital Health Innovation; Biomedical Engineering; Medical Physics (PhD program) - Neurosurgery</t>
+          <t>Faculty of Computing &amp; Data Sciences</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Dan Ma</t>
+          <t>Boqing Gong</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor, Department of Computer Science; Faculty Fellow, Faculty of Computing &amp; Data Sciences</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>medical-AI</t>
+          <t>core-ML/CV</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>CVPR 7, ICCV 6, ICLR 5, ICML 3, NeurIPS 3, Trans. Mach. Learn. Res. 2, ECCV (89) 1, ECCV (70) 1, EMNLP 1, IEEE Trans. Pa</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
+          <t>AI-type dept: Faculty of Computing &amp; Data Sciences</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Quantitative MRI acquisition, reconstruction and AI-based image analysis for clinical translation.</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
+          <t>Computer vision and ML research on generalization, efficiency and visual analytics.</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>BioCLIP/EfficientNet fusion</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>dan.ma@duke.edu</t>
+          <t>bgong@bu.edu</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>https://comphealth.duke.edu/people/dan-ma/</t>
+          <t>https://www.bu.edu/cds-faculty/profile/boqing-gong/</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://neurosurgery.duke.edu/ma-lab</t>
+          <t>https://boqinggong.github.io/</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Enhancing Study Design and Analysis of MR Imaging Markers Through Measurement Error Modeling (2026) | Surfaced-based detection of focal cortical dysplasia using magnetic resonance fingerprinting and machine learning (2026)</t>
+          <t>AdverIN: Monotonic adversarial intensity attack for domain generalization in medical image segmentation (2026)</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://comphealth.duke.edu/our-team/?rendered_page=3</t>
+          <t>https://www.bu.edu/cds-faculty/culture-community/faculty-staff-directory/?num=2</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2915,26 +2931,22 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unspecified: </t>
+          <t>Unspecified: Assistant Professor Boston University</t>
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Her AI-based MRI reconstruction and image analysis connects to my calcium-imaging denoising work (calcium).</t>
+          <t>His foundation-model and generalization work relates to the Arborphy BioCLIP fusion/evaluation project.</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>no 2024-26 papers verified on lab page</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>associate: confirm promoted 2020+</t>
-        </is>
-      </c>
+          <t>Title conflict: CDS profile says Assistant Professor; College of Engineering profile says Professor (Computer Science); Publications page only lists to 2022, so no verified 2024-2026 papers; Part-time research scientist at Google</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2942,22 +2954,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Icahn School of Medicine at Mount Sinai</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Genetics and Genomic Sciences; Pharmacological Sciences; PhD Biomedical Sciences: Artificial Intelligence training area</t>
+          <t>Statistical Science</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Sifan Liu</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ASSISTANT PROFESSOR</t>
+          <t>Assistant Professor of Statistical Science</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2967,48 +2979,66 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>AI-for-science</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>stats-methods</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ICLR 3, NeurIPS 1, EMNLP (Findings) 1, J. Mach. Learn. Res. 1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
+          <t>AI-type dept: Statistical Science</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Biophysics, computer simulation, drug design, protein folding, structural biology; AI-in-medicine training area.</t>
+          <t>Sampling algorithms and MCMC with diffusion paths for Bayesian inference and generative modeling.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>wei.wang@mssm.edu</t>
+          <t>sifan.liu@duke.edu</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/wei-wang</t>
+          <t>https://scholars.duke.edu/person/sifan.liu</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/wei-wang</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+          <t>https://liusf15.github.io/</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Weak Diffusion Priors Can Still Achieve Strong Inverse-Problem Performance Jing Jia, Wei Yuan, Sifan Liu, Liyue Shen, Guanyang Wang ICML 2026, spotlight</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Antithetic Noise in Diffusion Models Jing Jia, Sifan Liu, Bowen Song, Wei Yuan, Liyue Shen, Guanyang Wang ICLR 2026</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>A Novel Uncertainty Analysis Method for Bonner Sphere Based on Local Correlation of Response Matrix (2026) | Towards Understanding Camera Motions in Any Video (2025)</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470001513038352&amp;selectedFilter=department&amp;tab=faculty&amp;start=130</t>
+          <t>https://stat.duke.edu/people/faculty</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3018,15 +3048,19 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unspecified: </t>
+          <t>Unspecified: If you are interested in my research, feel free to get in touch!</t>
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Her Bayesian sampling and inference work connects to my Bayesian stochastic block model fitting on the FlyWire connectome (flywire).</t>
+        </is>
+      </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>no lab site found; official profile only; no recruiting info</t>
+          <t>joined Duke after Flatiron (2024-2025) per site; start year not stated</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr"/>
@@ -3037,22 +3071,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Icahn School of Medicine at Mount Sinai</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Windreich AI and Human Health; Diagnostic, Molecular and Interventional Radiology; BMEII core + AI; PhD Biomedical Sciences: Artificial Intelligence training area</t>
+          <t>Duke AI Health (Faculty Affiliates); Biostatistics &amp; Bioinformatics (SOM); CBB program</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Xueyan Mei</t>
+          <t>Chuan Hong</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ASSISTANT PROFESSOR | Diagnostic, Molecular and Interventional Radiology</t>
+          <t>Assistant Professor of Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3070,52 +3104,46 @@
           <t>medical-AI</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>NeurIPS 1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
+          <t>AI-type dept: Biostatistics &amp; Bioinformatics (SOM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Deep learning in cardiovascular imaging and detection of AI-generated radiographs by radiologists.</t>
+          <t>ML and LLMs on EHR data: representation learning, LLM screening, cardiovascular risk.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>xueyan.mei@mssm.edu</t>
+          <t>chuan.hong@duke.edu</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>https://icahn.mssm.edu/profiles/xueyan-mei</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>https://icahn.mssm.edu/profiles/xueyan-mei</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Timing and Pattern of Extraosseous Dissemination Are Key Determinants of Survival in Multiple Myeloma (2026)</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Retinal imaging and supervised learning predict hospitalizations and kidney and heart-lung damage in sickle cell disease (2026)</t>
-        </is>
-      </c>
+          <t>https://biostat.duke.edu/profile/chuan-hong</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>The Rise of Deepfake Medical Imaging: Radiologists' Diagnostic Accuracy in Detecting ChatGPT-generated Radiographs (2026) | AI and Deep Learning in Cardiovascular Imaging: From Risk Stratification to Precision Phenotyping (2026)</t>
+          <t>Representation learning to advance multi-institutional studies with electronic health record data from US and France (2026) | Leveraging LLMs for Title and Abstract Screening for Systematic Review: A Cost-effective Dynamic Few-shot Learning Approach (2026)</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://icahn.mssm.edu/about/artificial-intelligence/faculty</t>
+          <t>https://aihealth.duke.edu/people/</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3128,107 +3156,113 @@
           <t xml:space="preserve">Unspecified: </t>
         </is>
       </c>
-      <c r="W24" t="inlineStr"/>
+      <c r="W24" t="n">
+        <v>2022</v>
+      </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>no personal/lab site found (4 searches/fetches); official profile only</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr"/>
+          <t>no lab site or research text fetched; themes unverified</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>fit based on name-matched papers only: check they are this person's</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Mathematics; Duke Discovery AI; Biostatistics &amp; Bioinformatics (SOM); CBB program</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Xiaomin Lin</t>
+          <t>Jichun Xie</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor of Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>core-ML/CV</t>
+          <t>AI-for-science</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>ICRA 4, IROS 3, WACV (Workshops) 1, AAAI 1, ECCV (65) 1</t>
+          <t>J. Mach. Learn. Res. 1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>AI-type dept: Electrical Engineering</t>
+          <t>AI-type dept: Mathematics</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Robotics, perception and edge AI for underwater and agricultural autonomy; deep learning rhino detection.</t>
+          <t>Sequence-to-function models, cell annotation and rare-variant association methods for genomics.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>xlin2@usf.edu</t>
+          <t>jichun.xie@duke.edu</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/engineering/ece/faculty-staff/lin-xiaomin.aspx</t>
+          <t>https://scholars.duke.edu/person/jichun.xie</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://xiaominlin.github.io/</t>
+          <t>https://jichunxie.github.io/</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>WaterGen</t>
+          <t>Single-cell and spatial detection of senescent cells using DeepScence. Cell Genomics (2025)</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>RAZOR</t>
+          <t>B-Lightning: Using bait genes for marker gene hunting in single-cell data with complex heterogeneity. Briefings in Bioinformatics (2025)</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Automated rhinoceros detection in satellite imagery using deep learning (2025) | A Kinodynamic Model for Dubins-Based Trajectory Planning in Precision Oyster Harvesting (2025)</t>
+          <t>B-Lightning: using bait genes for marker gene hunting in single-cell data with complex heterogeneity (2024) | Single-cell landscape analysis unravels molecular programming of the human B cell compartment in chronic GVHD (2023)</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/engineering/ece/faculty-staff/index.aspx</t>
+          <t>https://math.duke.edu/people/faculty</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3238,26 +3272,30 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Yes: I am actively recruiting PhD students to join my lab starting Spring 2027 and Fall 2027.</t>
+          <t xml:space="preserve">Unspecified: </t>
         </is>
       </c>
       <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Please read my Research Statement (PDF) before applying. | Competitive applicants typically hold an MS in a related field and have at least one top-tier publication. | Prospective students (not currently at USF) — fill out this application form . Please send an email to me as well, with your CV, transcripts, and a brief statement of your research interests and career goals. Tell me which of my papers or directions interest you and why. | You wrote the email yourself: Prospective Student - Bulls </t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Her theme of combining classical statistical models with AI models for reliability and interpretability connects to my leakage-aware evaluation of fusion models (arborphy).</t>
+        </is>
+      </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>site requires AI-disclosure tag (subject 'Prospective Student - Bulls 3Q') for AI-drafted emails; expects &gt;=1 top-tier publication (applicant has none); paper titles are only short names on homepage news (WaterGen ECCV 2026, RAZOR CVPR 2026 Findings)</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr"/>
+          <t>news last dated Jun 2024</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3266,22 +3304,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Electrical &amp; Computer Engineering</t>
+          <t>Biostatistics &amp; Bioinformatics (SOM); CBB program; Duke Discovery AI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Neil Gong</t>
+          <t>Zhicheng Ji</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Associate Professor of Electrical and Computer Engineering</t>
+          <t>Assistant Professor of Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3295,57 +3333,57 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>NeurIPS 3, ICLR 2, ACL (1) 1, ACL (Findings) 1, EMNLP 1</t>
+          <t>CVPR Workshops 1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>AI-type dept: Electrical &amp; Computer Engineering</t>
+          <t>AI-type dept: Biostatistics &amp; Bioinformatics (SOM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Zero-shot autonomous microscopy for scalable characterization of 2D materials.</t>
+          <t>Cell-state TWAS, temporal expression modeling and LLM-based single-cell preprocessing.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>neil.gong@duke.edu</t>
+          <t>zhicheng.ji@duke.edu</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>https://ece.duke.edu/people/neil-gong/</t>
+          <t>https://biostat.duke.edu/profile/zhicheng-ji</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://people.duke.edu/~zg70/index.html</t>
+          <t>https://zji90.github.io/</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>A Critical Evaluation of Defenses against Prompt Injection Attacks</t>
+          <t>Zhuang H, Ji Z* . PreTSA: computationally efficient modeling of temporal and spatial gene expression patterns. 2026. Genome Biology</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Fingerprinting LLMs via Prompt Injection</t>
+          <t>Vispro improves imaging analysis for Visium spatial transcriptomics. 2025. Genome Biology</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Zero-Shot Autonomous Microscopy for Scalable and Intelligent Characterization of 2D Materials (2025)</t>
+          <t>Transcriptome-wide association studies at cell-state level using single-cell eQTL data (2026) | PreTSA: computationally efficient modeling of temporal and spatial gene expression patterns (2026)</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://ece.duke.edu/faculty</t>
+          <t>https://biostat.duke.edu/people/faculty?page=3</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3355,49 +3393,47 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Yes: I am looking for postdocs, Ph.D. students, master's students, and undergraduate researchers. If you are interested in pursuing a Ph.D., please submit your application to Duke ECE.</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr"/>
+          <t>Unspecified: PhD Students : Huimin Wang, Haotian Zhuang, Xingyuan Zhang, Pengyu Li</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>2020</v>
+      </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>His work on evaluating prompt-injection defenses and secure agentic AI connects to my multi-agent system with verification and trust gating (agents).</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>first-pass summary describes different work (microscopy of 2D materials); possibly wrong person/mismatch; warns he receives many emails and may not respond</t>
-        </is>
-      </c>
+          <t>His AI methods for biomedical images and LLM evaluation connect to my calcium-imaging denoising and my evaluation-focused work (calcium).</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+; fit based on name-matched papers only: check they are this person's</t>
+          <t>fit based on name-matched papers only: check they are this person's; dossier reader says A: Bio-AI: deep learning, LLMs, spatial transcriptomics/imaging; has PhD students. Upgraded B-&gt;A. Programs listed are only ; also listed as Jason Ji</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Icahn School of Medicine at Mount Sinai</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Windreich AI and Human Health; Neuroscience</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Danyang Zhuo</t>
+          <t>Baihan Lin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hamelsky Family Assistant Professor of Computer Science</t>
+          <t>ASSISTANT PROFESSOR | Artificial Intelligence and Human Health</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3407,62 +3443,58 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>core-ML/CV</t>
+          <t>medical-AI</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>NeurIPS 2, AAAI 1, UAI 1, AISTATS 1</t>
+          <t>IJCAI 1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>AI-type dept: Computer Science</t>
+          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Machine learning systems and datacenter/cloud computing.</t>
+          <t>AI and human health; speech acoustic analysis to screen cognitive impairment; mania speech; AI governance in consumer health.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>danyang.zhuo@duke.edu</t>
+          <t>baihan.lin@mssm.edu</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>https://scholars.duke.edu/person/danyang.zhuo</t>
+          <t>https://icahn.mssm.edu/profiles/baihan-lin</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>https://danyangzhuo.com/</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>DecodeShare: Tracing the Shared Pathways of LLM Decode-Time Decisions.</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Phantora: Maximizing Code Reuse in Simulation-based Machine Learning System Performance Estimation.</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
+          <t>https://www.bytesofminds.com/</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Acoustic Analysis of Primary Care Patient-Clinician Conversations to Screen for Cognitive Impairment (2026) | Temporal elements of speech in mania.  (2026)</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>https://users.cs.duke.edu/people/faculty</t>
+          <t>https://icahn.mssm.edu/about/artificial-intelligence/faculty</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3472,106 +3504,108 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Yes: I am always looking for new PhD students. Please apply to Duke CS if you are interested in working with me!</t>
+          <t>Unspecified: If you want to work with us, or on something adjacent, get in touch.</t>
         </is>
       </c>
       <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>If you want to work with us, or on something adjacent, get in touch.</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>EEG motor-imagery decoder project connects to the lab's brain-computer-interface theme.</t>
+        </is>
+      </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>systems, not ML methods; site email differs from input email</t>
+          <t>no papers list fetched (publications page not retrieved); search snippet mentions earlier open-position postings via baihan.lin@mssm.edu (not fetched)</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>dossier reader says C: Networking and GPU systems; no overlap with applicant's stats/Bio-AI background. Downgraded A-&gt;C. Note site email is dan</t>
+          <t>fit based on name-matched papers only: check they are this person's</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Statistical Science; Duke Institute for Brain Sciences (network faculty)</t>
+          <t>Bioinformatics Program; Biomedical Genetics</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Simon Mak</t>
+          <t>Lei Hou</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Associate Professor of Statistical Science</t>
+          <t>Assistant Professor, Biomedical Genetics /  School of Medicine</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stats-methods</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>KDD 2, AAAI 1, AISTATS 1</t>
-        </is>
-      </c>
+          <t>AI-for-science</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>AI-type dept: Statistical Science</t>
+          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Gaussian process surrogate modeling for computer experiments and sensitivity analysis.</t>
+          <t>Systems genomics and regulatory genomics for brain-related disease biomarkers.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>sm769@duke.edu</t>
+          <t>leihou@bu.edu</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>https://scholars.duke.edu/person/SimonTszFung.Mak</t>
+          <t>https://hougroup.xyz/</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>https://sites.google.com/view/simonmak/</t>
+          <t>https://hougroup.xyz/</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Isotonic surrogate modeling for computer experiments with many input variables (2026) | Fast multitask Gaussian processes, with application to surrogate modeling of the quark-gluon plasma (2026)</t>
+          <t>Genotype epigenome phenotype integration reveals peripheral immune contributions to type I bipolar disorder (2026) | Peripheral vascular function, including endothelium-dependent measures, and dementia risk: The Framingham Heart Study (2026)</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://stat.duke.edu/people/faculty</t>
+          <t>https://www.bu.edu/bioinformatics/people/faculty/</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3581,30 +3615,26 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Yes: If you are interested in joining our research group, please send a CV and transcript to sm769[at]duke.edu, with a description of your research background &amp; interests.</t>
+          <t>Unspecified: We are hiring postdocs, interns, and data analysts!</t>
         </is>
       </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>His interpretable, science-guided statistical models connect to my Bayesian latent-variable modeling of the FlyWire connectome (flywire).</t>
-        </is>
-      </c>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>associate; promotion year not found; no papers list on site (CV/Scholar only)</t>
+          <t>No 2024-2026 papers on lab publications page (latest 2023); Site hiring postdocs/interns/analysts only; no PhD recruiting stated; Mostly genomics/genetics, light ML</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+; fit based on name-matched papers only: check they are this person's; dossier reader says B: Strong stats/ML for science, but applications are physics/engineering, not biology; associate, start year unknown. A-&gt;B.</t>
+          <t>dossier reader says C: Genetics-focused lab with no stated PhD recruiting and no honest project link.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3613,78 +3643,74 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Electrical &amp; Computer Engineering</t>
+          <t>Center for Computational &amp; Digital Health Innovation; Biomedical Engineering; Medical Physics (PhD program) - Neurosurgery</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tingjun Chen</t>
+          <t>Dan Ma</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nortel Networks Assistant Professor of Electrical and Computer Engineering</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>core-ML/CV</t>
+          <t>medical-AI</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>ICRA 2, IROS 1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>AI-type dept: Electrical &amp; Computer Engineering</t>
+          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Disaggregated machine learning via in-physics computing at radio frequency.</t>
+          <t>Quantitative MRI acquisition, reconstruction and AI-based image analysis for clinical translation.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>tingjun.chen@duke.edu</t>
+          <t>dan.ma@duke.edu</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>https://ece.duke.edu/people/tingjun-chen/</t>
+          <t>https://comphealth.duke.edu/people/dan-ma/</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>https://tingjunchen.com/</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Disaggregated machine learning via in-physics computing at radio frequency (2026)</t>
-        </is>
-      </c>
+          <t>https://neurosurgery.duke.edu/ma-lab</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Enhancing Study Design and Analysis of MR Imaging Markers Through Measurement Error Modeling (2026) | Surfaced-based detection of focal cortical dysplasia using magnetic resonance fingerprinting and machine learning (2026)</t>
+        </is>
+      </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://ece.duke.edu/faculty</t>
+          <t>https://comphealth.duke.edu/our-team/?rendered_page=3</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3694,47 +3720,49 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Yes: I am always looking for motivated B.S., M.S., Ph.D. students and Postdocs to join my group at Duke ECE. If interested, email me your CV, transcript, and a brief note on your research interests.</t>
-        </is>
-      </c>
-      <c r="W29" t="n">
-        <v>2021</v>
-      </c>
+          <t xml:space="preserve">Unspecified: </t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Her AI-based MRI reconstruction and image analysis connects to my calcium-imaging denoising work (calcium).</t>
+        </is>
+      </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>not actually ML-focused</t>
+          <t>no 2024-26 papers verified on lab page</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>dossier reader says C: Wireless/optical networking hardware; ML is peripheral. A-&gt;C.</t>
+          <t>associate: confirm promoted 2020+</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>Icahn School of Medicine at Mount Sinai</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Electrical &amp; Computer Engineering</t>
+          <t>Genetics and Genomic Sciences; Pharmacological Sciences; PhD Biomedical Sciences: Artificial Intelligence training area</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Yigong Hu</t>
+          <t>Wei Wang</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Assistant Professor (ECE)</t>
+          <t>ASSISTANT PROFESSOR</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3744,62 +3772,48 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>core-ML/CV</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>NeurIPS 2</t>
-        </is>
-      </c>
+          <t>AI-for-science</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>AI-type dept: Electrical &amp; Computer Engineering</t>
+          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Reliable, fast systems from machine learning systems to cloud platforms.</t>
+          <t>Biophysics, computer simulation, drug design, protein folding, structural biology; AI-in-medicine training area.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>yigongh@bu.edu</t>
+          <t>wei.wang@mssm.edu</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/eng/profile/yigong-hu-phd/</t>
+          <t>https://profiles.icahn.mssm.edu/wei-wang</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>https://yigonghu.github.io/</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Magneton: Optimizing Energy Efficiency of ML Systems via Differential Energy Debugging</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>An Agentic Framework for Triaging Incidents in Production Cloud Infrastructure</t>
-        </is>
-      </c>
+          <t>https://profiles.icahn.mssm.edu/wei-wang</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/eng/academics/departments-and-divisions/biomedical-engineering/people/?department=electrical-computer-engineering&amp;affiliation=primary-affiliated-faculty&amp;layout=list&amp;num=1</t>
+          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470001513038352&amp;selectedFilter=department&amp;tab=faculty&amp;start=130</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3809,47 +3823,41 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Yes: I’m currently looking for self-motivated students (undergraduate, master’s, and PhD) and interns who are passionate about building systems.</t>
-        </is>
-      </c>
-      <c r="W30" t="n">
-        <v>2025</v>
-      </c>
+          <t xml:space="preserve">Unspecified: </t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>Systems research (OSDI/SOSP), not ML methods</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>dossier reader says C: Computer systems lab; ML only as a systems target. Corrected from A.</t>
-        </is>
-      </c>
+          <t>no lab site found; official profile only; no recruiting info</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Icahn School of Medicine at Mount Sinai</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bellini College of AI, Cybersecurity and Computing</t>
+          <t>Windreich AI and Human Health; Diagnostic, Molecular and Interventional Radiology; BMEII core + AI; PhD Biomedical Sciences: Artificial Intelligence training area</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Yi Sheng</t>
+          <t>Xueyan Mei</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>ASSISTANT PROFESSOR | Diagnostic, Molecular and Interventional Radiology</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3867,54 +3875,52 @@
           <t>medical-AI</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>AAAI 1, MICCAI (7) 1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>AI-type dept: Bellini College of AI, Cybersecurity and Comp</t>
+          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Energy-efficient AI systems on edge devices for medical image computing applications.</t>
+          <t>Deep learning in cardiovascular imaging and detection of AI-generated radiographs by radiologists.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>sheng1@usf.edu</t>
+          <t>xueyan.mei@mssm.edu</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/yi_sheng.aspx</t>
+          <t>https://icahn.mssm.edu/profiles/xueyan-mei</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>https://eaho-research-lab.github.io/Homepage/</t>
+          <t>https://icahn.mssm.edu/profiles/xueyan-mei</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>APS-USCT: Ultrasound Computed Tomography on Sparse Data via AI-Physic Synergy</t>
+          <t>Timing and Pattern of Extraosseous Dissemination Are Key Determinants of Survival in Multiple Myeloma (2026)</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Data-Algorithm-Architecture Co-Optimization for Fair Neural Networks on Skin Lesion Dataset</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr"/>
+          <t>Retinal imaging and supervised learning predict hospitalizations and kidney and heart-lung damage in sickle cell disease (2026)</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>The Rise of Deepfake Medical Imaging: Radiologists' Diagnostic Accuracy in Detecting ChatGPT-generated Radiographs (2026) | AI and Deep Learning in Cardiovascular Imaging: From Risk Stratification to Precision Phenotyping (2026)</t>
+        </is>
+      </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
+          <t>https://icahn.mssm.edu/about/artificial-intelligence/faculty</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3924,21 +3930,17 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Yes: We are recruiting self-motivated PhD students with strong backgrounds in machine learning, computer systems, or related areas. Funding is available for strong candidates.</t>
+          <t xml:space="preserve">Unspecified: </t>
         </is>
       </c>
       <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Apply through the USF CSE Graduate Admissions portal and mention Dr. Yi Sheng in your statement of purpose. Feel free to email with your CV and a brief research statement before applying. | We try to respond to all inquiries within one week.</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>Her work on fairness evaluation of medical AI (skin lesion) connects to the arborphy leakage-aware, multi-seed evaluation of a fusion model.</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>no personal/lab site found (4 searches/fetches); official profile only</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -3947,22 +3949,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Biostatistics &amp; Bioinformatics (SOM)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ed Chien</t>
+          <t>Pan Xu</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Assistant Professor of Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3972,58 +3974,66 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>core-ML/CV</t>
+          <t>medical-AI</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>NeurIPS 5, ICML 4, Trans. Mach. Learn. Res. 4, ICLR 3, AISTATS 2, AAAI 1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>AI-type dept: Computer Science</t>
+          <t>AI-type dept: Biostatistics &amp; Bioinformatics (SOM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Differential geometry and topology for graphics; machine learning applications of optimal transport.</t>
+          <t>Reinforcement learning for decision support in ECMO management.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>edchien@bu.edu</t>
+          <t>pan.xu@duke.edu</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/cs/profiles/edchien/</t>
+          <t>https://biostat.duke.edu/profile/pan-xu</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>https://cs-people.bu.edu/edchien/</t>
+          <t>https://panxulab.github.io/</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Partially Observed Trajectory Inference using Optimal Transport and a Dynamics Prior</t>
+          <t>Extremely Sparse Supervision Incentivizes Reasoning Ability</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Faraday Cage Estimation of Normals for Point Clouds and Ribbon Sketches</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
+          <t>Decoupled Marginal Sharpening for Training-Free Inference-Time Scaling</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>rECMOmender: Reinforcement Learning for Decision Support in Venovenous Extracorporeal Membrane Oxygenation Management (2026)</t>
+        </is>
+      </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/cs/people/faculty/</t>
+          <t>https://biostat.duke.edu/people/faculty?page=6</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4033,24 +4043,24 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Yes: I am looking for a PhD student or postdoc to work on projects associated with the NSF CAREER grant that I received recently</t>
+          <t xml:space="preserve">Yes: I am always happy to collaborate with highly motivated and self-driven students who are genuinely interested in our research. Before contacting me, please take the time to carefully read at least one </t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>Doctoral students should apply to BU's doctoral program and potential postdocs should reach out to me via email. | Please reach out if you are interested!</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>His 'Extremely Sparse Supervision' paper runs on-policy distillation experiments on the Qwen3 family, which touches the applicant's Qwen3 probing/steering interp work (evaluation-focused, not a causal claim).</t>
+        </is>
+      </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>mostly geometry processing / graphics / fabrication, little ML; funded slot is for computational knitting</t>
+          <t>site requires reading a lab paper and a specific 5-8 sentence note (CV + which paper/why/background) before he replies; start year not stated; original panxu-ai.github.io redirects to panxulab.github.io</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>dossier reader says B: Mainly geometry processing and computational fabrication; ML limited to applied optimal transport (one ICLR 2025 paper).</t>
+          <t>dossier reader says A: Upgraded B-&gt;A: ML-core (RL, LLMs, data-efficient learning), tenure-track assistant professor with healthcare application</t>
         </is>
       </c>
     </row>
@@ -4065,17 +4075,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faculty of Computing &amp; Data Sciences</t>
+          <t>Electrical &amp; Computer Engineering</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Xuezhou (Jack) Zhang</t>
+          <t>Yigong Hu</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Assistant Professor of Computing &amp; Data Sciences</t>
+          <t>Assistant Professor (ECE)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4093,48 +4103,54 @@
           <t>core-ML/CV</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>NeurIPS 2</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>AI-type dept: Faculty of Computing &amp; Data Sciences</t>
+          <t>AI-type dept: Electrical &amp; Computer Engineering</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Develops machine learning algorithms with theoretical and empirical performance guarantees.</t>
+          <t>Reliable, fast systems from machine learning systems to cloud platforms.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>xuezhouz@bu.edu</t>
+          <t>yigongh@bu.edu</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/cds-faculty/profile/xuezhou-jack-zhang/</t>
+          <t>https://www.bu.edu/eng/profile/yigong-hu-phd/</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>https://zhangxz1123.github.io/</t>
+          <t>https://yigonghu.github.io/</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Accelerating RL for LLM Reasoning with Optimal Advantage Regression.</t>
+          <t>Magneton: Optimizing Energy Efficiency of ML Systems via Differential Energy Debugging</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Avoiding exp(R max ) scaling in RLHF through Preference-based Exploration.</t>
+          <t>An Agentic Framework for Triaging Incidents in Production Cloud Infrastructure</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/cds-faculty/culture-community/faculty-staff-directory/?num=4</t>
+          <t>https://www.bu.edu/eng/academics/departments-and-divisions/biomedical-engineering/people/?department=electrical-computer-engineering&amp;affiliation=primary-affiliated-faculty&amp;layout=list&amp;num=1</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4144,20 +4160,22 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Yes: I am in constant lookout for self-motivated Ph.D. students with a strong mathematical and/or programming background .</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr"/>
+          <t>Yes: I’m currently looking for self-motivated students (undergraduate, master’s, and PhD) and interns who are passionate about building systems.</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>2025</v>
+      </c>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>RL/learning-theory focus; weak connection to applicant's projects; Slow to respond to unsolicited email</t>
+          <t>Systems research (OSDI/SOSP), not ML methods</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>dossier reader says B: Young, openly recruiting, rigorous ML theory/RL for LLMs, but little Bio-AI overlap and no honest project hook.</t>
+          <t>dossier reader says C: Computer systems lab; ML only as a systems target. Corrected from A.</t>
         </is>
       </c>
     </row>
@@ -4167,22 +4185,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mechanical Eng &amp; Materials Science</t>
+          <t>Bellini College of AI, Cybersecurity and Computing</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Xianyi Cheng</t>
+          <t>Yi Sheng</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Assistant Professor in the Thomas Lord Department of Mechanical Engineering and Materials Science</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4192,48 +4210,62 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>core-ML/CV</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>medical-AI</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>AAAI 1, MICCAI (7) 1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>AI-type dept: Mechanical Eng &amp; Materials Science</t>
+          <t>AI-type dept: Bellini College of AI, Cybersecurity and Comp</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Robot dexterity lab: generalizable, transferable robot manipulation skills, contact mechanics, interactive perception.</t>
+          <t>Energy-efficient AI systems on edge devices for medical image computing applications.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>xianyi.cheng@duke.edu</t>
+          <t>sheng1@usf.edu</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>https://mems.duke.edu/people/xianyi-cheng/</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/yi_sheng.aspx</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://xianyicheng.github.io/</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+          <t>https://eaho-research-lab.github.io/Homepage/</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>APS-USCT: Ultrasound Computed Tomography on Sparse Data via AI-Physic Synergy</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Data-Algorithm-Architecture Co-Optimization for Fair Neural Networks on Skin Lesion Dataset</t>
+        </is>
+      </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://mems.duke.edu/people?s=&amp;group=faculty-primary,faculty-secondary</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4243,22 +4275,22 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Yes: Interested in joining the DexLab? Fill out this form and send me a brief email to let me know your interest.</t>
+          <t>Yes: We are recruiting self-motivated PhD students with strong backgrounds in machine learning, computer systems, or related areas. Funding is available for strong candidates.</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>robotics hardware, not ML methods; lab publications/join pages 404 on fetch</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>dossier reader says C: Robot manipulation/mechanics; little overlap. A-&gt;C.</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Apply through the USF CSE Graduate Admissions portal and mention Dr. Yi Sheng in your statement of purpose. Feel free to email with your CV and a brief research statement before applying. | We try to respond to all inquiries within one week.</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Her work on fairness evaluation of medical AI (skin lesion) connects to the arborphy leakage-aware, multi-seed evaluation of a fusion model.</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4266,17 +4298,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bellini College of AI, Cybersecurity and Computing</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Jiajun Huang</t>
+          <t>Ed Chien</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4305,40 +4337,44 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>AI-type dept: Bellini College of AI, Cybersecurity and Comp</t>
+          <t>AI-type dept: Computer Science</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Efficient high-performance systems for large-scale AI; GPU compression and collective communication.</t>
+          <t>Differential geometry and topology for graphics; machine learning applications of optimal transport.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>jiajunhuang@usf.edu</t>
+          <t>edchien@bu.edu</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/jiajun_huang.aspx</t>
+          <t>https://www.bu.edu/cs/profiles/edchien/</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>https://jiajunhuang1999.github.io</t>
+          <t>https://cs-people.bu.edu/edchien/</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>OCTANE: Breaking the Neighbor-List Bottleneck in GPU Molecular Dynamics</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
+          <t>Partially Observed Trajectory Inference using Optimal Transport and a Dynamics Prior</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Faraday Cage Estimation of Normals for Point Clouds and Ribbon Sketches</t>
+        </is>
+      </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
+          <t>https://www.bu.edu/cs/people/faculty/</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4348,24 +4384,24 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Yes: is recruiting 2-4 Ph.D. students for Spring 2027 and Fall 2027</t>
+          <t>Yes: I am looking for a PhD student or postdoc to work on projects associated with the NSF CAREER grant that I received recently</t>
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
-          <t>How to Apply: Email Subject: PhD Application [Spring 2027 / Fall 2027] [Your Name] (please indicate your intended start semester) | Email Content: Self-introduction (including research experience &amp; interests) Resume (CV) Academic transcripts Additional materials (optional, e.g., TOEFL/GRE scores, if available) Combine all documents into a single PDF Send your application to jiajunhuang@usf.edu | Click here for more details before reaching out via email.</t>
+          <t>Doctoral students should apply to BU's doctoral program and potential postdocs should reach out to me via email. | Please reach out if you are interested!</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>HPC/systems focus; little overlap with applicant's projects</t>
+          <t>mostly geometry processing / graphics / fabrication, little ML; funded slot is for computational knitting</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>dossier contact_prefs: no snapshot, re-check</t>
+          <t>dossier reader says B: Mainly geometry processing and computational fabrication; ML limited to applied optimal transport (one ICLR 2025 paper).</t>
         </is>
       </c>
     </row>
@@ -4375,22 +4411,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mechanical and Aerospace Engineering</t>
+          <t>Faculty of Computing &amp; Data Sciences</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Xiaoyu Liu</t>
+          <t>Xuezhou (Jack) Zhang</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Assistant Professor of Computing &amp; Data Sciences</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4412,44 +4448,44 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>AI-type dept: Mechanical and Aerospace Engineering</t>
+          <t>AI-type dept: Faculty of Computing &amp; Data Sciences</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Machine learning and mathematical methods for human-robot teaming in space missions.</t>
+          <t>Develops machine learning algorithms with theoretical and empirical performance guarantees.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>xiaoyuliu@usf.edu</t>
+          <t>xuezhouz@bu.edu</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>https://xiaoyuliu-space.github.io/</t>
+          <t>https://www.bu.edu/cds-faculty/profile/xuezhou-jack-zhang/</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>https://xiaoyuliu-space.github.io/</t>
+          <t>https://zhangxz1123.github.io/</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Reinforcement Learning-Based Framework to Support Multi-Agent Teaming in Space Missions</t>
+          <t>Accelerating RL for LLM Reasoning with Optimal Advantage Regression.</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Computational Framework for Assessing Mission Outcomes with Humans and Robots</t>
+          <t>Avoiding exp(R max ) scaling in RLHF through Preference-based Exploration.</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/engineering/mae/people/index.aspx</t>
+          <t>https://www.bu.edu/cds-faculty/culture-community/faculty-staff-directory/?num=4</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4459,28 +4495,20 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Yes: I am currently recruiting Ph.D. and M.S. students starting in Fall 2027/Spring 2028.</t>
+          <t>Yes: I am in constant lookout for self-motivated Ph.D. students with a strong mathematical and/or programming background .</t>
         </is>
       </c>
       <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>If you are interested in machine learning/multi-agent teaming/space mission planning, send me an email at xiaoyuliu@usf.edu!</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Multi-agent system with trust levels loosely connects to multi-agent teaming.</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>application domain is aerospace; ML is applied RL/modeling</t>
+          <t>RL/learning-theory focus; weak connection to applicant's projects; Slow to respond to unsolicited email</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>dossier reader says B: Applied RL for human-robot teaming in MAE; far from Bio-AI but explicitly recruiting for Fall 2027.</t>
+          <t>dossier reader says B: Young, openly recruiting, rigorous ML theory/RL for LLMs, but little Bio-AI overlap and no honest project hook.</t>
         </is>
       </c>
     </row>
@@ -4490,27 +4518,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Mechanical Eng &amp; Materials Science</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Zhuo Lu</t>
+          <t>Xianyi Cheng</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor in the Thomas Lord Department of Mechanical Engineering and Materials Science</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4520,51 +4548,43 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>core-ML/CV</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>AI-type dept: Electrical Engineering</t>
+          <t>AI-type dept: Mechanical Eng &amp; Materials Science</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Communication, network and security theory, with recent work on AI for security and security for AI.</t>
+          <t>Robot dexterity lab: generalizable, transferable robot manipulation skills, contact mechanics, interactive perception.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>zhuolu@usf.edu</t>
+          <t>xianyi.cheng@duke.edu</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/engineering/ece/faculty-staff/zhuo-lu-anchor-page.aspx</t>
+          <t>https://mems.duke.edu/people/xianyi-cheng/</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>https://csalab.site</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>VOID: Backdoor Injection through Knowledge Vacuity in Federated Unlearning</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>ScrambleMark: Zero-Query Watermark-Agnostic Black-Box Evasion of Modern Speech Watermarking</t>
-        </is>
-      </c>
+          <t>https://xianyicheng.github.io/</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/engineering/ece/faculty-staff/index.aspx</t>
+          <t>https://mems.duke.edu/people?s=&amp;group=faculty-primary,faculty-secondary</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4574,24 +4594,20 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Yes: We are always looking for self-motivated PhD students: computer, engineering, or mathematical background</t>
+          <t>Yes: Interested in joining the DexLab? Fill out this form and send me a brief email to let me know your interest.</t>
         </is>
       </c>
       <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>PhD Admission to the Department Details can be found here . GRE scores can be optional. Good research/project backgrounds help a lot.</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>senior (associate) and security/wireless focus; not a young-faculty target; start year not found</t>
+          <t>robotics hardware, not ML methods; lab publications/join pages 404 on fetch</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+; dossier reader says C: Primarily communications/network security with ML security on the side; associate with unknown promotion date.</t>
+          <t>dossier reader says C: Robot manipulation/mechanics; little overlap. A-&gt;C.</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4627,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Shichen Zhang</t>
+          <t>Jiajun Huang</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4626,7 +4642,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4645,40 +4661,32 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Intelligent wireless systems joining communication, sensing and AI; radar-based sensing.</t>
+          <t>Efficient high-performance systems for large-scale AI; GPU compression and collective communication.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>szhang1@usf.edu</t>
+          <t>jiajunhuang@usf.edu</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/shichen_zhang.aspx</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/jiajun_huang.aspx</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>https://sczhang6.github.io/</t>
+          <t>https://jiajunhuang1999.github.io</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>RadEye: Tracking Eye Motion Using FMCW Radar</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>RadSee: See Your Handwriting Through Walls Using 6GHz FMCW Radar</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>RadSee: See Your Handwriting Through Walls Using FMCW Radar (2025) | Anti-Jamming 5G Millimeter-Wave Communication via Joint Analog and Digital Beamforming: A Bayesian Optimization Approach (2025)</t>
-        </is>
-      </c>
+          <t>OCTANE: Breaking the Neighbor-List Bottleneck in GPU Molecular Dynamics</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
           <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
@@ -4691,28 +4699,24 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Yes: I am actively seeking self-motivated Ph.D. students to join my group in Spring/Fall 2027.</t>
+          <t>Yes: is recruiting 2-4 Ph.D. students for Spring 2027 and Fall 2027</t>
         </is>
       </c>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr">
         <is>
-          <t>If you are interested, please fill out the Prospective Ph.D. Student Survey and feel free to email me at szhang1 [at] usf.edu with the following materials: your CV, transcripts (B.S. and M.S.), any published papers (if applicable), TOEFL/IELTS scores, and any other supplementary materials that help me learn more about you. | A strong background in wireless sensing , wireless networking , and deep learning is highly desirable.</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>EEG motor-imagery decoding (signal processing + deep learning) loosely connects to RF/biosignal sensing.</t>
-        </is>
-      </c>
+          <t>How to Apply: Email Subject: PhD Application [Spring 2027 / Fall 2027] [Your Name] (please indicate your intended start semester) | Email Content: Self-introduction (including research experience &amp; interests) Resume (CV) Academic transcripts Additional materials (optional, e.g., TOEFL/GRE scores, if available) Combine all documents into a single PDF Send your application to jiajunhuang@usf.edu | Click here for more details before reaching out via email.</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>wireless systems background expected</t>
+          <t>HPC/systems focus; little overlap with applicant's projects</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>dossier reader says C: Wireless/RF sensing; ML is a tool, requested background (wireless networking) does not match; no honest hook.; dossier recruiting: quote not on page, re-check</t>
+          <t>dossier contact_prefs: no snapshot, re-check</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4731,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bellini College of AI, Cybersecurity and Computing</t>
+          <t>Mechanical and Aerospace Engineering</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Yili Ren</t>
+          <t>Xiaoyu Liu</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4747,7 +4751,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4755,50 +4759,48 @@
           <t>core-ML/CV</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>AI-type dept: Bellini College of AI, Cybersecurity and Comp</t>
+          <t>AI-type dept: Mechanical and Aerospace Engineering</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Mobile and wireless sensing for IoT and smart home; AI/LLM plus mobile computing.</t>
+          <t>Machine learning and mathematical methods for human-robot teaming in space missions.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>yiliren@usf.edu</t>
+          <t>xiaoyuliu@usf.edu</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/yili-ren.aspx</t>
+          <t>https://xiaoyuliu-space.github.io/</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>https://yiliren.github.io/</t>
+          <t>https://xiaoyuliu-space.github.io/</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>MURAL-Fi: Multi-User Respiration Authentication Leveraging WiFi</t>
+          <t>Reinforcement Learning-Based Framework to Support Multi-Agent Teaming in Space Missions</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>SpaceBeat: Identity-aware Multi-person Vital Signs Monitoring Using Commodity WiFi</t>
+          <t>Computational Framework for Assessing Mission Outcomes with Humans and Robots</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
+          <t>https://www.usf.edu/engineering/mae/people/index.aspx</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4808,26 +4810,30 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Yes: I am looking for self-motivated Ph.D. students to join my group.</t>
+          <t>Yes: I am currently recruiting Ph.D. and M.S. students starting in Fall 2027/Spring 2028.</t>
         </is>
       </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Candidates with research experiences in wireless sensing, network/mobile systems, signal processing, machine learning, and cybersecurity will be given favorable consideration. If you are interested, please feel free to send me an email with your CV, transcripts, TOEFL scores, and any other relevant materials that you believe would support your application.</t>
+          <t>If you are interested in machine learning/multi-agent teaming/space mission planning, send me an email at xiaoyuliu@usf.edu!</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>Vital-sign/respiration sensing and signal processing loosely relate to the EEG motor-imagery decoder (biomedical time series).</t>
+          <t>Multi-agent system with trust levels loosely connects to multi-agent teaming.</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>email on site is obfuscated [at] form; value de-obfuscated</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr"/>
+          <t>application domain is aerospace; ML is applied RL/modeling</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>dossier reader says B: Applied RL for human-robot teaming in MAE; far from Bio-AI but explicitly recruiting for Fall 2027.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4835,27 +4841,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faculty of Computing &amp; Data Sciences</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Boqing Gong</t>
+          <t>Zhuo Lu</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Assistant Professor, Department of Computer Science; Faculty Fellow, Faculty of Computing &amp; Data Sciences</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4865,57 +4871,51 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>core-ML/CV</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>30</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>CVPR 7, ICCV 6, ICLR 5, ICML 3, NeurIPS 3, Trans. Mach. Learn. Res. 2, ECCV (89) 1, ECCV (70) 1, EMNLP 1, IEEE Trans. Pa</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>AI-type dept: Faculty of Computing &amp; Data Sciences</t>
+          <t>AI-type dept: Electrical Engineering</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Computer vision and ML research on generalization, efficiency and visual analytics.</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>BioCLIP/EfficientNet fusion</t>
-        </is>
-      </c>
+          <t>Communication, network and security theory, with recent work on AI for security and security for AI.</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>bgong@bu.edu</t>
+          <t>zhuolu@usf.edu</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/cds-faculty/profile/boqing-gong/</t>
+          <t>https://www.usf.edu/engineering/ece/faculty-staff/zhuo-lu-anchor-page.aspx</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>https://boqinggong.github.io/</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>AdverIN: Monotonic adversarial intensity attack for domain generalization in medical image segmentation (2026)</t>
-        </is>
-      </c>
+          <t>https://csalab.site</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>VOID: Backdoor Injection through Knowledge Vacuity in Federated Unlearning</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>ScrambleMark: Zero-Query Watermark-Agnostic Black-Box Evasion of Modern Speech Watermarking</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/cds-faculty/culture-community/faculty-staff-directory/?num=2</t>
+          <t>https://www.usf.edu/engineering/ece/faculty-staff/index.aspx</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4925,22 +4925,26 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Unspecified: Assistant Professor Boston University</t>
+          <t>Yes: We are always looking for self-motivated PhD students: computer, engineering, or mathematical background</t>
         </is>
       </c>
       <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>His foundation-model and generalization work relates to the Arborphy BioCLIP fusion/evaluation project.</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>PhD Admission to the Department Details can be found here . GRE scores can be optional. Good research/project backgrounds help a lot.</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>Title conflict: CDS profile says Assistant Professor; College of Engineering profile says Professor (Computer Science); Publications page only lists to 2022, so no verified 2024-2026 papers; Part-time research scientist at Google</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr"/>
+          <t>senior (associate) and security/wireless focus; not a young-faculty target; start year not found</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+; dossier reader says C: Primarily communications/network security with ML security on the side; associate with unknown promotion date.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4948,22 +4952,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Statistical Science</t>
+          <t>Bellini College of AI, Cybersecurity and Computing</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sifan Liu</t>
+          <t>Shichen Zhang</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Assistant Professor of Statistical Science</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4973,66 +4977,62 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stats-methods</t>
+          <t>core-ML/CV</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>ICLR 3, NeurIPS 1, EMNLP (Findings) 1, J. Mach. Learn. Res. 1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>AI-type dept: Statistical Science</t>
+          <t>AI-type dept: Bellini College of AI, Cybersecurity and Comp</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Sampling algorithms and MCMC with diffusion paths for Bayesian inference and generative modeling.</t>
+          <t>Intelligent wireless systems joining communication, sensing and AI; radar-based sensing.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>sifan.liu@duke.edu</t>
+          <t>szhang1@usf.edu</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>https://scholars.duke.edu/person/sifan.liu</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/shichen_zhang.aspx</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>https://liusf15.github.io/</t>
+          <t>https://sczhang6.github.io/</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Weak Diffusion Priors Can Still Achieve Strong Inverse-Problem Performance Jing Jia, Wei Yuan, Sifan Liu, Liyue Shen, Guanyang Wang ICML 2026, spotlight</t>
+          <t>RadEye: Tracking Eye Motion Using FMCW Radar</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Antithetic Noise in Diffusion Models Jing Jia, Sifan Liu, Bowen Song, Wei Yuan, Liyue Shen, Guanyang Wang ICLR 2026</t>
+          <t>RadSee: See Your Handwriting Through Walls Using 6GHz FMCW Radar</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>A Novel Uncertainty Analysis Method for Bonner Sphere Based on Local Correlation of Response Matrix (2026) | Towards Understanding Camera Motions in Any Video (2025)</t>
+          <t>RadSee: See Your Handwriting Through Walls Using FMCW Radar (2025) | Anti-Jamming 5G Millimeter-Wave Communication via Joint Analog and Digital Beamforming: A Bayesian Optimization Approach (2025)</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://stat.duke.edu/people/faculty</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5042,22 +5042,30 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Unspecified: If you are interested in my research, feel free to get in touch!</t>
+          <t>Yes: I am actively seeking self-motivated Ph.D. students to join my group in Spring/Fall 2027.</t>
         </is>
       </c>
       <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>If you are interested, please fill out the Prospective Ph.D. Student Survey and feel free to email me at szhang1 [at] usf.edu with the following materials: your CV, transcripts (B.S. and M.S.), any published papers (if applicable), TOEFL/IELTS scores, and any other supplementary materials that help me learn more about you. | A strong background in wireless sensing , wireless networking , and deep learning is highly desirable.</t>
+        </is>
+      </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>Her Bayesian sampling and inference work connects to my Bayesian stochastic block model fitting on the FlyWire connectome (flywire).</t>
+          <t>EEG motor-imagery decoding (signal processing + deep learning) loosely connects to RF/biosignal sensing.</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>joined Duke after Flatiron (2024-2025) per site; start year not stated</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr"/>
+          <t>wireless systems background expected</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>dossier reader says C: Wireless/RF sensing; ML is a tool, requested background (wireless networking) does not match; no honest hook.; dossier recruiting: quote not on page, re-check</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5070,12 +5078,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mathematics and Statistics</t>
+          <t>Bellini College of AI, Cybersecurity and Computing</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Jie Min</t>
+          <t>Yili Ren</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5095,49 +5103,53 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stats-methods</t>
+          <t>core-ML/CV</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>WACV 1, CVPR 1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>AI-type dept: Mathematics and Statistics</t>
+          <t>AI-type dept: Bellini College of AI, Cybersecurity and Comp</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No research text on card; Mathematics and Statistics department only.</t>
+          <t>Mobile and wireless sensing for IoT and smart home; AI/LLM plus mobile computing.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>jiem@usf.edu</t>
+          <t>yiliren@usf.edu</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/arts-sciences/departments/mathematics-statistics/people/faculty/jie-min.aspx</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/yili-ren.aspx</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/arts-sciences/departments/mathematics-statistics/people/faculty/jie-min.aspx</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
+          <t>https://yiliren.github.io/</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>MURAL-Fi: Multi-User Respiration Authentication Leveraging WiFi</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>SpaceBeat: Identity-aware Multi-person Vital Signs Monitoring Using Commodity WiFi</t>
+        </is>
+      </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/arts-sciences/departments/mathematics-statistics/people/faculty/index.aspx</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5147,15 +5159,23 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unspecified: </t>
+          <t>Yes: I am looking for self-motivated Ph.D. students to join my group.</t>
         </is>
       </c>
       <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Candidates with research experiences in wireless sensing, network/mobile systems, signal processing, machine learning, and cybersecurity will be given favorable consideration. If you are interested, please feel free to send me an email with your CV, transcripts, TOEFL scores, and any other relevant materials that you believe would support your application.</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Vital-sign/respiration sensing and signal processing loosely relate to the EEG motor-imagery decoder (biomedical time series).</t>
+        </is>
+      </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>no lab/personal site found</t>
+          <t>email on site is obfuscated [at] form; value de-obfuscated</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr"/>
@@ -5166,65 +5186,71 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Faculty of Computing &amp; Data Sciences</t>
+          <t>Mathematics and Statistics</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DK Lee</t>
+          <t>Jie Min</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kelli Questrom Associate Professor of Information Systems + Computing &amp; Data Sciences</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>core-ML/CV</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>stats-methods</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>WACV 1, CVPR 1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>AI-type dept: Faculty of Computing &amp; Data Sciences</t>
+          <t>AI-type dept: Mathematics and Statistics</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Economic impact of AI and textual data in e-commerce; text extraction and understanding.</t>
+          <t>No research text on card; Mathematics and Statistics department only.</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>dokyun@bu.edu</t>
+          <t>jiem@usf.edu</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/cds-faculty/profile/dk-lee/</t>
+          <t>https://www.usf.edu/arts-sciences/departments/mathematics-statistics/people/faculty/jie-min.aspx</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>http://www.dkbitlab.com/</t>
+          <t>https://www.usf.edu/arts-sciences/departments/mathematics-statistics/people/faculty/jie-min.aspx</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr"/>
@@ -5232,7 +5258,7 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/cds-faculty/culture-community/faculty-staff-directory/?num=2</t>
+          <t>https://www.usf.edu/arts-sciences/departments/mathematics-statistics/people/faculty/index.aspx</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5242,7 +5268,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Unspecified: Doctoral Students Zhaoqi Cheng Zhaoqi Cheng is an Information Systems PhD student at Boston University, Questrom School of Business.</t>
+          <t xml:space="preserve">Unspecified: </t>
         </is>
       </c>
       <c r="W43" t="inlineStr"/>
@@ -5250,14 +5276,10 @@
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>Business school information systems / marketing, not ML methods or biology; Lab page dated (2023 meeting)</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>associate: confirm promoted 2020+; dossier reader says C: Business/e-commerce text analytics. Corrected from A.</t>
-        </is>
-      </c>
+          <t>no lab/personal site found</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5270,17 +5292,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Electrical &amp; Computer Engineering</t>
+          <t>Faculty of Computing &amp; Data Sciences</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wei-Lun (Harry) Chao</t>
+          <t>DK Lee</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Associate Professor (ECE)</t>
+          <t>Kelli Questrom Associate Professor of Information Systems + Computing &amp; Data Sciences</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5302,48 +5324,36 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>AI-type dept: Electrical &amp; Computer Engineering</t>
+          <t>AI-type dept: Faculty of Computing &amp; Data Sciences</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>ML and computer vision for recognition, autonomous driving, imageomics and healthcare.</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>BioCLIP/EfficientNet fusion</t>
-        </is>
-      </c>
+          <t>Economic impact of AI and textual data in e-commerce; text extraction and understanding.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>chao209@bu.edu</t>
+          <t>dokyun@bu.edu</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/eng/profile/wei-lun-chao-phd/</t>
+          <t>https://www.bu.edu/cds-faculty/profile/dk-lee/</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>https://sites.google.com/view/wei-lun-harry-chao</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>BioCAP: Exploiting Synthetic Captions Beyond Labels in Biological Foundation Models.</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>TaxaAdapter: Scaling Fine-grained Species Image Generation To the Tree of Life.</t>
-        </is>
-      </c>
+          <t>http://www.dkbitlab.com/</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/eng/academics/departments-and-divisions/biomedical-engineering/people/?department=electrical-computer-engineering&amp;affiliation=primary-affiliated-faculty&amp;layout=list&amp;num=1</t>
+          <t>https://www.bu.edu/cds-faculty/culture-community/faculty-staff-directory/?num=2</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5353,24 +5363,20 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Unspecified: Opening TBA</t>
+          <t>Unspecified: Doctoral Students Zhaoqi Cheng Zhaoqi Cheng is an Information Systems PhD student at Boston University, Questrom School of Business.</t>
         </is>
       </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>His Imageomics biological foundation-model papers (BioCAP, camera-trap species recognition) connect directly to the Arborphy BioCLIP plant-recognition and leakage-aware evaluation project.</t>
-        </is>
-      </c>
+      <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>Tenured Associate Professor (previously at Ohio State); BU start year not stated on fetched pages, so 'recent associate' unverified; Opening page says only 'TBA'</t>
+          <t>Business school information systems / marketing, not ML methods or biology; Lab page dated (2023 meeting)</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+</t>
+          <t>associate: confirm promoted 2020+; dossier reader says C: Business/e-commerce text analytics. Corrected from A.</t>
         </is>
       </c>
     </row>
@@ -5380,27 +5386,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mathematics and Statistics</t>
+          <t>Electrical &amp; Computer Engineering</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Jiaqi Gu</t>
+          <t>Wei-Lun (Harry) Chao</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor (ECE)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5410,55 +5416,55 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stats-methods</t>
+          <t>core-ML/CV</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>AI-type dept: Mathematics and Statistics</t>
+          <t>AI-type dept: Electrical &amp; Computer Engineering</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Knockoff-based inference for genetic association studies and gene expression analysis.</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
+          <t>ML and computer vision for recognition, autonomous driving, imageomics and healthcare.</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>BioCLIP/EfficientNet fusion</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>jiaqigu@usf.edu</t>
+          <t>chao209@bu.edu</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/arts-sciences/departments/mathematics-statistics/people/faculty/jiaqi-gu.aspx</t>
+          <t>https://www.bu.edu/eng/profile/wei-lun-chao-phd/</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>https://sites.google.com/view/jiaqigu</t>
+          <t>https://sites.google.com/view/wei-lun-harry-chao</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Bayesian Knockoff Filter for Controlling False Discovery Rate</t>
+          <t>BioCAP: Exploiting Synthetic Captions Beyond Labels in Biological Foundation Models.</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Distilling Direct Effects via Conditional Differential Gene Expression Analysis</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>Robust Inference With Ghostknockoffs in Genome-Wide Association Studies With Sample Relatedness (2026) | Refining genetic discoveries of group knockoffs via a feature-level filter (2026)</t>
-        </is>
-      </c>
+          <t>TaxaAdapter: Scaling Fine-grained Species Image Generation To the Tree of Life.</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/arts-sciences/departments/mathematics-statistics/people/faculty/index.aspx</t>
+          <t>https://www.bu.edu/eng/academics/departments-and-divisions/biomedical-engineering/people/?department=electrical-computer-engineering&amp;affiliation=primary-affiliated-faculty&amp;layout=list&amp;num=1</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5468,20 +5474,24 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unspecified: </t>
+          <t>Unspecified: Opening TBA</t>
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>BSBM/statistical-modeling background connects to knockoff / gene-regulatory-network inference.</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr"/>
+          <t>His Imageomics biological foundation-model papers (BioCAP, camera-trap species recognition) connect directly to the Arborphy BioCLIP plant-recognition and leakage-aware evaluation project.</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Tenured Associate Professor (previously at Ohio State); BU start year not stated on fetched pages, so 'recent associate' unverified; Opening page says only 'TBA'</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>fit based on name-matched papers only: check they are this person's; dossier start_year: quote not on page, re-check</t>
+          <t>associate: confirm promoted 2020+</t>
         </is>
       </c>
     </row>
@@ -5491,22 +5501,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Electrical &amp; Computer Engineering</t>
+          <t>Mathematics and Statistics</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Chuanfei Dong</t>
+          <t>Jiaqi Gu</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Assistant Professor (Astronomy, ECE)</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5516,54 +5526,60 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>AI-for-science</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
+          <t>stats-methods</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>AI-type dept: Electrical &amp; Computer Engineering</t>
+          <t>AI-type dept: Mathematics and Statistics</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Space plasma physics of Mars and magnetosphere; paper on machine-learning closure for fluid modeling.</t>
+          <t>Knockoff-based inference for genetic association studies and gene expression analysis.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>dcfy@bu.edu</t>
+          <t>jiaqigu@usf.edu</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/eng/profile/chuanfei-dong-phd/</t>
+          <t>https://www.usf.edu/arts-sciences/departments/mathematics-statistics/people/faculty/jiaqi-gu.aspx</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>https://sites.google.com/site/chuanfeidong</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+          <t>https://sites.google.com/view/jiaqigu</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Bayesian Knockoff Filter for Controlling False Discovery Rate</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Distilling Direct Effects via Conditional Differential Gene Expression Analysis</t>
+        </is>
+      </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Widespread plasma jets in the Martian magnetosheath revealed by dual-spacecraft observations (2026) | Simultaneous Mars-orbit observations reveal Kelvin-Helmholtz instability-driven bulk atmospheric ion escape (2026)</t>
+          <t>Robust Inference With Ghostknockoffs in Genome-Wide Association Studies With Sample Relatedness (2026) | Refining genetic discoveries of group knockoffs via a feature-level filter (2026)</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/eng/academics/departments-and-divisions/biomedical-engineering/people/?department=electrical-computer-engineering&amp;affiliation=primary-affiliated-faculty&amp;layout=list&amp;num=1</t>
+          <t>https://www.usf.edu/arts-sciences/departments/mathematics-statistics/people/faculty/index.aspx</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5573,22 +5589,20 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Unspecified: To apply for Ph.D. in Astronomy at Boston University, please click here .</t>
-        </is>
-      </c>
-      <c r="W46" t="n">
-        <v>2023</v>
-      </c>
+          <t xml:space="preserve">Unspecified: </t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>Space plasma physics; ML is a side area; Moving: IBM Einstein Fellowship at IAS (2026) listed on profile; could be on leave</t>
-        </is>
-      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>BSBM/statistical-modeling background connects to knockoff / gene-regulatory-network inference.</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>dossier reader says C: Primarily space physics; AI4Science side topic only.</t>
+          <t>fit based on name-matched papers only: check they are this person's; dossier start_year: quote not on page, re-check</t>
         </is>
       </c>
     </row>
@@ -5598,27 +5612,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Biostatistics &amp; Bioinformatics (SOM)</t>
+          <t>Electrical &amp; Computer Engineering</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Hwanhee Hong</t>
+          <t>Chuanfei Dong</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Associate Professor of Biostatistics &amp; Bioinformatics</t>
+          <t>Assistant Professor (Astronomy, ECE)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5628,7 +5642,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stats-methods</t>
+          <t>AI-for-science</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -5637,40 +5651,40 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>AI-type dept: Biostatistics &amp; Bioinformatics (SOM)</t>
+          <t>AI-type dept: Electrical &amp; Computer Engineering</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Biostatistician: Bayesian reanalysis, heterogeneity of treatment effect, comparative effectiveness in cardiology trials.</t>
+          <t>Space plasma physics of Mars and magnetosphere; paper on machine-learning closure for fluid modeling.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>hwanhee.hong@duke.edu</t>
+          <t>dcfy@bu.edu</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/profile/hwanhee-hong</t>
+          <t>https://www.bu.edu/eng/profile/chuanfei-dong-phd/</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/profile/hwanhee-hong</t>
+          <t>https://sites.google.com/site/chuanfeidong</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Single-Ventricle Disease: Long-Term Outcomes and Global Morbidity in the Single Ventricle Reconstruction Trial (2026) | Heterogeneity of Treatment Effect of DOACs vs Warfarin in Atrial Fibrillation (2026)</t>
+          <t>Widespread plasma jets in the Martian magnetosheath revealed by dual-spacecraft observations (2026) | Simultaneous Mars-orbit observations reveal Kelvin-Helmholtz instability-driven bulk atmospheric ion escape (2026)</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/people/faculty?page=2</t>
+          <t>https://www.bu.edu/eng/academics/departments-and-divisions/biomedical-engineering/people/?department=electrical-computer-engineering&amp;affiliation=primary-affiliated-faculty&amp;layout=list&amp;num=1</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5680,7 +5694,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unspecified: </t>
+          <t>Unspecified: To apply for Ph.D. in Astronomy at Boston University, please click here .</t>
         </is>
       </c>
       <c r="W47" t="n">
@@ -5690,12 +5704,12 @@
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>not ML; no lab site</t>
+          <t>Space plasma physics; ML is a side area; Moving: IBM Einstein Fellowship at IAS (2026) listed on profile; could be on leave</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+; dossier reader says C: Clinical-trial/comparative-effectiveness biostatistics; not ML. Associate since 2023. B-&gt;C. No personal lab site found (</t>
+          <t>dossier reader says C: Primarily space physics; AI4Science side topic only.</t>
         </is>
       </c>
     </row>
@@ -5710,22 +5724,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Electrical &amp; Computer Engineering</t>
+          <t>Biostatistics &amp; Bioinformatics (SOM)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Xiang Cheng</t>
+          <t>Hwanhee Hong</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Assistant Professor in the Department of Electrical and Computer Engineering</t>
+          <t>Associate Professor of Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5735,47 +5749,49 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>core-ML/CV</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>stats-methods</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>AI-type dept: Electrical &amp; Computer Engineering</t>
+          <t>AI-type dept: Biostatistics &amp; Bioinformatics (SOM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No research text; ECE assistant professor, teaches Practical Machine Learning.</t>
+          <t>Biostatistician: Bayesian reanalysis, heterogeneity of treatment effect, comparative effectiveness in cardiology trials.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>xiang.cheng@duke.edu</t>
+          <t>hwanhee.hong@duke.edu</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>https://ece.duke.edu/people/xiang-cheng/</t>
+          <t>https://biostat.duke.edu/profile/hwanhee-hong</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>https://ece.duke.edu/people/xiang-cheng/</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Sun X, Cheng X. Calibrated LRT Guidance for Offline Diffusion Policies . In: Proceedings of the International Joint Conference on Autonomous Agents and Multiagent Systems Aamas. 2026.</t>
-        </is>
-      </c>
+          <t>https://biostat.duke.edu/profile/hwanhee-hong</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Single-Ventricle Disease: Long-Term Outcomes and Global Morbidity in the Single Ventricle Reconstruction Trial (2026) | Heterogeneity of Treatment Effect of DOACs vs Warfarin in Atrial Fibrillation (2026)</t>
+        </is>
+      </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>https://ece.duke.edu/faculty</t>
+          <t>https://biostat.duke.edu/people/faculty?page=2</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5788,15 +5804,21 @@
           <t xml:space="preserve">Unspecified: </t>
         </is>
       </c>
-      <c r="W48" t="inlineStr"/>
+      <c r="W48" t="n">
+        <v>2023</v>
+      </c>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>no lab site found (search returned only a Simons Institute student profile, not verified as same person's current page); recruiting info not found; start year not found (PhD Berkeley 2020)</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr"/>
+          <t>not ML; no lab site</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+; dossier reader says C: Clinical-trial/comparative-effectiveness biostatistics; not ML. Associate since 2023. B-&gt;C. No personal lab site found (</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5809,22 +5831,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Biostatistics &amp; Bioinformatics (SOM)</t>
+          <t>Electrical &amp; Computer Engineering</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Yuan Wu</t>
+          <t>Xiang Cheng</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Associate Professor in Biostatistics &amp; Bioinformatics</t>
+          <t>Assistant Professor in the Department of Electrical and Computer Engineering</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5834,47 +5856,47 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stats-methods</t>
+          <t>core-ML/CV</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>AI-type dept: Biostatistics &amp; Bioinformatics (SOM)</t>
+          <t>AI-type dept: Electrical &amp; Computer Engineering</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Biostatistics methods: group sequential sample size, propensity score variance estimation.</t>
+          <t>No research text; ECE assistant professor, teaches Practical Machine Learning.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>yuan.wu@duke.edu</t>
+          <t>xiang.cheng@duke.edu</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/profile/yuan-wu</t>
+          <t>https://ece.duke.edu/people/xiang-cheng/</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/profile/yuan-wu</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr"/>
+          <t>https://ece.duke.edu/people/xiang-cheng/</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Sun X, Cheng X. Calibrated LRT Guidance for Offline Diffusion Policies . In: Proceedings of the International Joint Conference on Autonomous Agents and Multiagent Systems Aamas. 2026.</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>Group Sequential Sample Size for Comparing Two Survival Probabilities at a Specific Time Point (2026) | Symptom management and transitioning to engagement with post-treatment care for adolescent and young adult cancer survivors (AYA STEPS): Study protocol (2026)</t>
-        </is>
-      </c>
+      <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/people/faculty?page=6</t>
+          <t>https://ece.duke.edu/faculty</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5892,14 +5914,10 @@
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>no lab/personal site found (1 search); official profile has no research text; associate professor; promotion year not found</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>associate: confirm promoted 2020+</t>
-        </is>
-      </c>
+          <t>no lab site found (search returned only a Simons Institute student profile, not verified as same person's current page); recruiting info not found; start year not found (PhD Berkeley 2020)</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5907,27 +5925,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Icahn School of Medicine at Mount Sinai</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Genetics and Genomic Sciences</t>
+          <t>Biostatistics &amp; Bioinformatics (SOM)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Donghoon Lee</t>
+          <t>Yuan Wu</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ASSISTANT PROFESSOR</t>
+          <t>Associate Professor in Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5940,54 +5958,44 @@
           <t>stats-methods</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
+          <t>AI-type dept: Biostatistics &amp; Bioinformatics (SOM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Computational psychiatric genomics; new methods for single-nucleus data, e.g. Dreamlet differential expression.</t>
+          <t>Biostatistics methods: group sequential sample size, propensity score variance estimation.</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>donghoon.lee@mssm.edu</t>
+          <t>yuan.wu@duke.edu</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/donghoon-lee</t>
+          <t>https://biostat.duke.edu/profile/yuan-wu</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>https://profiles.icahn.mssm.edu/donghoon-lee</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Efficient differential expression analysis of large-scale single-cell transcriptomics data using Dreamlet (2026)</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>SECmeres outperform extracellular vesicles as potential blood RNA biomarkers for Alzheimer's disease (2026)</t>
-        </is>
-      </c>
+          <t>https://biostat.duke.edu/profile/yuan-wu</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Single-nucleus atlas of cell-type specific genetic regulation in the human brain (2026) | Lifespan single-cell transcriptomic atlas of the human prefrontal cortex (2026)</t>
+          <t>Group Sequential Sample Size for Comparing Two Survival Probabilities at a Specific Time Point (2026) | Symptom management and transitioning to engagement with post-treatment care for adolescent and young adult cancer survivors (AYA STEPS): Study protocol (2026)</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470001513038352&amp;selectedFilter=department&amp;tab=faculty&amp;start=70</t>
+          <t>https://biostat.duke.edu/people/faculty?page=6</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -6005,10 +6013,14 @@
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>no personal/lab site found; official profile only</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr"/>
+          <t>no lab/personal site found (1 search); official profile has no research text; associate professor; promotion year not found</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6016,22 +6028,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Icahn School of Medicine at Mount Sinai</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Civil and Environmental Engineering</t>
+          <t>Genetics and Genomic Sciences</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Hao Zhou</t>
+          <t>Donghoon Lee</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Assistant Professor - Transportation</t>
+          <t>ASSISTANT PROFESSOR</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6046,7 +6058,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>stats-methods</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -6060,31 +6072,43 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Roster says traffic operation and AI for mobility; research text describes turbulent flow simulation; conflicting.</t>
+          <t>Computational psychiatric genomics; new methods for single-nucleus data, e.g. Dreamlet differential expression.</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>haozhou1@usf.edu</t>
+          <t>donghoon.lee@mssm.edu</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/engineering/cee/faculty-staff/index.aspx</t>
+          <t>https://profiles.icahn.mssm.edu/donghoon-lee</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>https://engineers.usf.edu/kalfredo</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
+          <t>https://profiles.icahn.mssm.edu/donghoon-lee</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Efficient differential expression analysis of large-scale single-cell transcriptomics data using Dreamlet (2026)</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>SECmeres outperform extracellular vesicles as potential blood RNA biomarkers for Alzheimer's disease (2026)</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Single-nucleus atlas of cell-type specific genetic regulation in the human brain (2026) | Lifespan single-cell transcriptomic atlas of the human prefrontal cortex (2026)</t>
+        </is>
+      </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/engineering/cee/faculty-staff/index.aspx</t>
+          <t>https://faculty.icahn.mssm.edu/results?departmentId=0000072470001513038352&amp;selectedFilter=department&amp;tab=faculty&amp;start=70</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6102,14 +6126,10 @@
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>Given homepage engineers.usf.edu/kalfredo is a different person (Alfredo, drinking water) - wrong homepage; No personal/lab site found (3 searches)</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>also listed as Jingran Sun</t>
-        </is>
-      </c>
+          <t>no personal/lab site found; official profile only</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6122,17 +6142,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mechanical and Aerospace Engineering</t>
+          <t>Civil and Environmental Engineering</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wenbin Mao</t>
+          <t>Hao Zhou</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Assistant Professor - Transportation</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6147,7 +6167,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>medical-AI</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -6156,40 +6176,36 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>AI-type dept: Mechanical and Aerospace Engineering</t>
+          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Cardiac and vascular biomechanics modelling with deep learning and physics-informed neural networks.</t>
+          <t>Roster says traffic operation and AI for mobility; research text describes turbulent flow simulation; conflicting.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>wmao@usf.edu</t>
+          <t>haozhou1@usf.edu</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/engineering/mae/people/index.aspx</t>
+          <t>https://www.usf.edu/engineering/cee/faculty-staff/index.aspx</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>http://bfbsm.eng.usf.edu/</t>
+          <t>https://engineers.usf.edu/kalfredo</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>Identification of in vivo constitutive parameters of thoracic aortic aneurysms based on the unified-fiber-distribution model (2026) | A Deep Learning Model for the Identification of Active Contraction Properties of the Myocardium Using Limited Clinical Metrics (2026)</t>
-        </is>
-      </c>
+      <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/engineering/mae/people/index.aspx</t>
+          <t>https://www.usf.edu/engineering/cee/faculty-staff/index.aspx</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6207,37 +6223,37 @@
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>lab site http://bfbsm.eng.usf.edu/ is a one-line page that does not name the PI or USF, so not accepted as lab_site; no join/contact info found; WebSearch found only 2019-20 PhD ads</t>
+          <t>Given homepage engineers.usf.edu/kalfredo is a different person (Alfredo, drinking water) - wrong homepage; No personal/lab site found (3 searches)</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>fit based on name-matched papers only: check they are this person's</t>
+          <t>also listed as Jingran Sun</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Biostatistics &amp; Bioinformatics (SOM)</t>
+          <t>Mechanical and Aerospace Engineering</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Pan Xu</t>
+          <t>Wenbin Mao</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biostatistics &amp; Bioinformatics</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6256,57 +6272,45 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>NeurIPS 5, ICML 4, Trans. Mach. Learn. Res. 4, ICLR 3, AISTATS 2, AAAI 1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>AI-type dept: Biostatistics &amp; Bioinformatics (SOM)</t>
+          <t>AI-type dept: Mechanical and Aerospace Engineering</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Reinforcement learning for decision support in ECMO management.</t>
+          <t>Cardiac and vascular biomechanics modelling with deep learning and physics-informed neural networks.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>pan.xu@duke.edu</t>
+          <t>wmao@usf.edu</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/profile/pan-xu</t>
+          <t>https://www.usf.edu/engineering/mae/people/index.aspx</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>https://panxulab.github.io/</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Extremely Sparse Supervision Incentivizes Reasoning Ability</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>Decoupled Marginal Sharpening for Training-Free Inference-Time Scaling</t>
-        </is>
-      </c>
+          <t>http://bfbsm.eng.usf.edu/</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
-          <t>rECMOmender: Reinforcement Learning for Decision Support in Venovenous Extracorporeal Membrane Oxygenation Management (2026)</t>
+          <t>Identification of in vivo constitutive parameters of thoracic aortic aneurysms based on the unified-fiber-distribution model (2026) | A Deep Learning Model for the Identification of Active Contraction Properties of the Myocardium Using Limited Clinical Metrics (2026)</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/people/faculty?page=6</t>
+          <t>https://www.usf.edu/engineering/mae/people/index.aspx</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6316,24 +6320,20 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes: I am always happy to collaborate with highly motivated and self-driven students who are genuinely interested in our research. Before contacting me, please take the time to carefully read at least one </t>
+          <t xml:space="preserve">Unspecified: </t>
         </is>
       </c>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>His 'Extremely Sparse Supervision' paper runs on-policy distillation experiments on the Qwen3 family, which touches the applicant's Qwen3 probing/steering interp work (evaluation-focused, not a causal claim).</t>
-        </is>
-      </c>
+      <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>site requires reading a lab paper and a specific 5-8 sentence note (CV + which paper/why/background) before he replies; start year not stated; original panxu-ai.github.io redirects to panxulab.github.io</t>
+          <t>lab site http://bfbsm.eng.usf.edu/ is a one-line page that does not name the PI or USF, so not accepted as lab_site; no join/contact info found; WebSearch found only 2019-20 PhD ads</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>dossier reader says A: Upgraded B-&gt;A: ML-core (RL, LLMs, data-efficient learning), tenure-track assistant professor with healthcare application</t>
+          <t>fit based on name-matched papers only: check they are this person's</t>
         </is>
       </c>
     </row>
@@ -8216,27 +8216,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of California San Francisco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Biostatistics &amp; Bioinformatics (SOM)</t>
+          <t>Radiology and Biomedical Imaging</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Zhiguo Li</t>
+          <t>Kang Wang</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Associate Professor of Biostatistics &amp; Bioinformatics</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8246,39 +8246,53 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stats-methods</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>medical-AI</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ICCV 3, MICCAI (18) 2, MICCAI (7) 1, MICCAI (13) 1, MICCAI (5) 1, NeurIPS 1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AI-type dept: Biostatistics &amp; Bioinformatics (SOM)</t>
+          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Survival analysis methods: win ratio under non-proportional hazards versus restricted mean survival.</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>Develops anatomy-aware vision-language AI for CT detection of metastatic colorectal cancer.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>BioCLIP/EfficientNet fusion (CV)</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/profile/zhiguo-li</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+          <t>https://researcherprofiles.org/profile/523574019</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Zero-Shot Large Language Model-Powered Data Curation for Pancreatic Cyst Surveillance: Promise, Progress, and the Path to Practice (2026)</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Win Ratio as an Effect Size Measure Under Non-Proportional Hazards: A Comparison With Difference in Restricted Mean Survival (2026)</t>
+          <t>Imaging Evaluation for Steatotic Liver Disease (2026) | Diagnostic performance of CT/MRI LI-RADS radiation treatment response algorithm v2024 for Y-90 radioembolization (2026)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://biostat.duke.edu/people/faculty?page=3</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -8296,42 +8310,38 @@
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>no email on official page (input also None); no lab site found; official profile has no research text; associate professor; promotion year not found</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>associate: confirm promoted 2020+; dossier reader says C: Downgraded B-&gt;C: survival-analysis methods (win ratio/RMST), no ML link, no site or recruiting evidence found.</t>
-        </is>
-      </c>
+          <t>no lab site; radiology.ucsf.edu 403 (not bypassed); web-search summary (not fetched page) says AI-based quantitative liver MRI, vision-language models for abdominal oncology, NIH R01 2025-2029</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>University of California San Francisco</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Radiology and Biomedical Imaging</t>
+          <t>Biostatistics &amp; Bioinformatics (SOM)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kang Wang</t>
+          <t>Zhiguo Li</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor of Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8341,53 +8351,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>medical-AI</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>9</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ICCV 3, MICCAI (18) 2, MICCAI (7) 1, MICCAI (13) 1, MICCAI (5) 1, NeurIPS 1</t>
-        </is>
-      </c>
+          <t>stats-methods</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
+          <t>AI-type dept: Biostatistics &amp; Bioinformatics (SOM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Develops anatomy-aware vision-language AI for CT detection of metastatic colorectal cancer.</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>BioCLIP/EfficientNet fusion (CV)</t>
-        </is>
-      </c>
+          <t>Survival analysis methods: win ratio under non-proportional hazards versus restricted mean survival.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://researcherprofiles.org/profile/523574019</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Zero-Shot Large Language Model-Powered Data Curation for Pancreatic Cyst Surveillance: Promise, Progress, and the Path to Practice (2026)</t>
-        </is>
-      </c>
+          <t>https://biostat.duke.edu/profile/zhiguo-li</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Imaging Evaluation for Steatotic Liver Disease (2026) | Diagnostic performance of CT/MRI LI-RADS radiation treatment response algorithm v2024 for Y-90 radioembolization (2026)</t>
+          <t>Win Ratio as an Effect Size Measure Under Non-Proportional Hazards: A Comparison With Difference in Restricted Mean Survival (2026)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Radiology)</t>
+          <t>https://biostat.duke.edu/people/faculty?page=3</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -8405,10 +8401,14 @@
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>no lab site; radiology.ucsf.edu 403 (not bypassed); web-search summary (not fetched page) says AI-based quantitative liver MRI, vision-language models for abdominal oncology, NIH R01 2025-2029</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr"/>
+          <t>no email on official page (input also None); no lab site found; official profile has no research text; associate professor; promotion year not found</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+; dossier reader says C: Downgraded B-&gt;C: survival-analysis methods (win ratio/RMST), no ML link, no site or recruiting evidence found.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -9905,88 +9905,90 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>University of California San Francisco</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Biological and Medical Informatics (BMI) PhD program core+affiliate faculty (Wayback 2026-05 copy)</t>
+          <t>Electrical &amp; Computer Engineering; Systems Engineering</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Julian Hong</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>Wenchao Li</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Associate Professor (ECE, SE Appointed)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>medical-AI</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NeurIPS 3, AAAI 1, ICMLA 1, ICML 1, ICRA 1, NAACL (Findings) 1, ICLR 1, EMNLP (Findings) 1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
+          <t>AI-type dept: Electrical &amp; Computer Engineering</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Develops, validates and evaluates computational tools, including RAG and LLMs, for the cancer clinic.</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>multi-agent LLM systems</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+          <t>Dependable Computing Laboratory; no ML content on card.</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>wenchao@bu.edu</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>https://www.bu.edu/eng/profile/wenchao-li-ph-d/</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://honglab.ucsf.edu/</t>
+          <t>https://www.bu.edu/eng/profile/wenchao-li-ph-d/</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Retrieval-Augmented Generation in Oncology: Promises, Pitfalls, and Early Applications (2026) | Impact of Radionecrosis and Local Recurrence on Overall Survival After Stereotactic Radiosurgery for Brain Metastases (2026)</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260517152053/https://bmi.ucsf.edu/people/faculty</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unspecified: </t>
-        </is>
-      </c>
+          <t>https://www.bu.edu/eng/academics/departments-and-divisions/biomedical-engineering/people/?department=electrical-computer-engineering&amp;affiliation=primary-affiliated-faculty&amp;layout=list&amp;num=1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>official profile links honglab.ucsf.edu but it returned 403 (not bypassed); not read; promoted to Associate Professor 2024 per search summary</t>
-        </is>
-      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>fit based on name-matched papers only: check they are this person's</t>
+          <t>associate: confirm promoted 2020+</t>
         </is>
       </c>
     </row>
@@ -10006,7 +10008,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>William Chen</t>
+          <t>Julian Hong</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -10030,22 +10032,26 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Uses AI and computer vision in digital pathology to find prostate cancer biomarkers.</t>
+          <t>Develops, validates and evaluates computational tools, including RAG and LLMs, for the cancer clinic.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>BioCLIP/EfficientNet fusion (CV)</t>
+          <t>multi-agent LLM systems</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>https://honglab.ucsf.edu/</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Incidental meningiomas have favorable clinical outcomes across molecular classification systems (2026) | IL6 Supports Development of an Immunosuppressive Microenvironment and Resistance to Therapy in Glioblastoma (2026)</t>
+          <t>Retrieval-Augmented Generation in Oncology: Promises, Pitfalls, and Early Applications (2026) | Impact of Radionecrosis and Local Recurrence on Overall Survival After Stereotactic Radiosurgery for Brain Metastases (2026)</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -10068,7 +10074,7 @@
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>wchenlab.ucsf.edu returned 403 (not bypassed); search: Will S. Chen, Asst Prof Radiation Oncology (2025), computational/genomics/spatial biomarkers; identity of 'William Chen' vs 'Will S. Chen' plausible but not confirmed from a fetched page</t>
+          <t>official profile links honglab.ucsf.edu but it returned 403 (not bypassed); not read; promoted to Associate Professor 2024 per search summary</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -10083,32 +10089,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Icahn School of Medicine at Mount Sinai</t>
+          <t>University of California San Francisco</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Windreich AI and Human Health; Genetics and Genomic Sciences; Neuroscience</t>
+          <t>Biological and Medical Informatics (BMI) PhD program core+affiliate faculty (Wayback 2026-05 copy)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Jason Liu</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ASSISTANT PROFESSOR | Artificial Intelligence and Human Health</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
+          <t>William Chen</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -10125,31 +10123,27 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>(no research evidence saved) Appointed in AI and Human Health, with psychiatry, neuroscience and genomics; no research text.</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>jason.liu@mssm.edu</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>https://icahn.mssm.edu/profiles/jason-liu</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>https://icahn.mssm.edu/profiles/jason-liu</t>
-        </is>
-      </c>
+          <t>Uses AI and computer vision in digital pathology to find prostate cancer biomarkers.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>BioCLIP/EfficientNet fusion (CV)</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Incidental meningiomas have favorable clinical outcomes across molecular classification systems (2026) | IL6 Supports Development of an Immunosuppressive Microenvironment and Resistance to Therapy in Glioblastoma (2026)</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://icahn.mssm.edu/about/artificial-intelligence/faculty</t>
+          <t>https://web.archive.org/web/20260517152053/https://bmi.ucsf.edu/people/faculty</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -10167,10 +10161,14 @@
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>only the Icahn profile fetched: title lines only, no research text; email jason.liu@mssm.edu from input not re-verified (profile shows 'email' link only); no lab site found by search</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr"/>
+          <t>wchenlab.ucsf.edu returned 403 (not bypassed); search: Will S. Chen, Asst Prof Radiation Oncology (2025), computational/genomics/spatial biomarkers; identity of 'William Chen' vs 'Will S. Chen' plausible but not confirmed from a fetched page</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>fit based on name-matched papers only: check they are this person's</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -10178,22 +10176,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>University of California San Francisco</t>
+          <t>Icahn School of Medicine at Mount Sinai</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Biological and Medical Informatics (BMI) PhD program core+affiliate faculty (Wayback 2026-05 copy); Biomedical Sciences (BMS) PhD program faculty (Wayback 2026-07 copy, pages 0-12 and 26 only)</t>
+          <t>Windreich AI and Human Health; Genetics and Genomic Sciences; Neuroscience</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jimmie Ye</t>
+          <t>Jason Liu</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Assistant Professor, Epidemiology &amp; Biostatistics</t>
+          <t>ASSISTANT PROFESSOR | Artificial Intelligence and Human Health</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -10208,7 +10206,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>medical-AI</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -10220,19 +10218,31 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No research text or papers on the card.</t>
+          <t>(no research evidence saved) Appointed in AI and Human Health, with psychiatry, neuroscience and genomics; no research text.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>jason.liu@mssm.edu</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>https://icahn.mssm.edu/profiles/jason-liu</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>https://icahn.mssm.edu/profiles/jason-liu</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260517152053/https://bmi.ucsf.edu/people/faculty</t>
+          <t>https://icahn.mssm.edu/about/artificial-intelligence/faculty</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -10250,14 +10260,10 @@
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>UCSF profile lists title 'Professor, Medicine': not young faculty; yelab.ucsf.edu fetch failed (proxy 502)</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>appointment in Epidemiology &amp; Biostatistics (excluded dept): your call; dossier reader says C: Full Professor, outside young-faculty scope; statistical-genomics immunology lab.</t>
-        </is>
-      </c>
+          <t>only the Icahn profile fetched: title lines only, no research text; email jason.liu@mssm.edu from input not re-verified (profile shows 'email' link only); no lab site found by search</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -10270,17 +10276,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Biological and Medical Informatics (BMI) PhD program core+affiliate faculty (Wayback 2026-05 copy)</t>
+          <t>Biological and Medical Informatics (BMI) PhD program core+affiliate faculty (Wayback 2026-05 copy); Biomedical Sciences (BMS) PhD program faculty (Wayback 2026-07 copy, pages 0-12 and 26 only)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>John Liu</t>
+          <t>Jimmie Ye</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Assistant Professor, Neurological Surgery</t>
+          <t>Assistant Professor, Epidemiology &amp; Biostatistics</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -10307,17 +10313,13 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>(no research evidence saved) Functional genomics to find therapeutic targets and treatment-resistance pathways in brain tumors.</t>
+          <t>No research text or papers on the card.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>https://liulab.ucsf.edu/</t>
-        </is>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
@@ -10341,47 +10343,47 @@
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>lab site not fetchable (403); not ML (brain tumor genomics)</t>
+          <t>UCSF profile lists title 'Professor, Medicine': not young faculty; yelab.ucsf.edu fetch failed (proxy 502)</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dossier reader says C: Lab site liulab.ucsf.edu returned 403 to fetch (not bypassed); search snippets show brain-tumor functional genomics, wet</t>
+          <t>appointment in Epidemiology &amp; Biostatistics (excluded dept): your call; dossier reader says C: Full Professor, outside young-faculty scope; statistical-genomics immunology lab.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>University of California San Francisco</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Electrical &amp; Computer Engineering; Systems Engineering</t>
+          <t>Biological and Medical Informatics (BMI) PhD program core+affiliate faculty (Wayback 2026-05 copy)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wenchao Li</t>
+          <t>John Liu</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Associate Professor (ECE, SE Appointed)</t>
+          <t>Assistant Professor, Neurological Surgery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>?</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -10389,38 +10391,24 @@
           <t>other</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>NeurIPS 3, AAAI 1, ICMLA 1, ICML 1, ICRA 1, NAACL (Findings) 1, ICLR 1, EMNLP (Findings) 1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AI-type dept: Electrical &amp; Computer Engineering</t>
+          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Dependable Computing Laboratory; no ML content on card.</t>
+          <t>(no research evidence saved) Functional genomics to find therapeutic targets and treatment-resistance pathways in brain tumors.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>wenchao@bu.edu</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>https://www.bu.edu/eng/profile/wenchao-li-ph-d/</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/eng/profile/wenchao-li-ph-d/</t>
+          <t>https://liulab.ucsf.edu/</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -10428,18 +10416,30 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/eng/academics/departments-and-divisions/biomedical-engineering/people/?department=electrical-computer-engineering&amp;affiliation=primary-affiliated-faculty&amp;layout=list&amp;num=1</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+          <t>https://web.archive.org/web/20260517152053/https://bmi.ucsf.edu/people/faculty</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unspecified: </t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>lab site not fetchable (403); not ML (brain tumor genomics)</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>associate: confirm promoted 2020+</t>
+          <t>dossier reader says C: Lab site liulab.ucsf.edu returned 403 to fetch (not bypassed); search snippets show brain-tumor functional genomics, wet</t>
         </is>
       </c>
     </row>

--- a/data/export/batch1.xlsx
+++ b/data/export/batch1.xlsx
@@ -567,87 +567,91 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>University of California San Francisco</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bioengineering and Therapeutic Sciences (Profiles dept Bioengineering)</t>
+          <t>Electrical &amp; Computer Engineering</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Brian Cheung</t>
+          <t>Neil Gong</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor of Electrical and Computer Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>assistant</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>trustworthy-ML</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ICML 3, Trans. Mach. Learn. Res. 2, WACV 1, NeurIPS 1</t>
+          <t>NeurIPS 3, ICLR 2, ACL (1) 1, ACL (Findings) 1, EMNLP 1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
+          <t>AI-type dept: Electrical &amp; Computer Engineering</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Bioengineering and therapeutic sciences; no research text on card.</t>
+          <t>Zero-shot autonomous microscopy for scalable characterization of 2D materials.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>bcheung@ucsf.edu</t>
+          <t>neil.gong@duke.edu</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>https://briancheung.github.io</t>
+          <t>https://ece.duke.edu/people/neil-gong/</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://discolab.org/</t>
+          <t>https://people.duke.edu/~zg70/index.html</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Words That Make Language Models Perceive</t>
+          <t>A Critical Evaluation of Defenses against Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>What if Eye...? Computationally Recreating Vision Evolution</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
+          <t>Fingerprinting LLMs via Prompt Injection</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Zero-Shot Autonomous Microscopy for Scalable and Intelligent Characterization of 2D Materials (2025)</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://profiles.ucsf.edu/search/advanced (Department=Bioengineering)</t>
+          <t>https://ece.duke.edu/faculty</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -657,26 +661,26 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Yes: Open positions Postdocs, students, and research engineers interested in AI for science.</t>
+          <t>Yes: I am looking for postdocs, Ph.D. students, master's students, and undergraduate researchers. If you are interested in pursuing a Ph.D., please submit your application to Duke ECE.</t>
         </is>
       </c>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Contact Email: bcheung@ucsf.edu</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Convergent representations across modalities (Platonic Representation Hypothesis) connects to her BioCLIP+EfficientNet representation/evaluation work (arborphy) and probing/interpretability work (interp); AI for scientific discovery fits Bio-AI goal.</t>
+          <t>His work on evaluating prompt-injection defenses and secure agentic AI connects to my multi-agent system with verification and trust gating (agents).</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Input homepage was a UCSF Profiles page; true lab site is discolab.org; Dept is Bioengineering and Therapeutic Sciences (School of Pharmacy); doctoral program to apply through not stated (check BTS vs BMI); Lab described as 'post AGI' and 'Last updated: Oct 2026': very recently launched</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+          <t>first-pass summary describes different work (microscopy of 2D materials); possibly wrong person/mismatch; warns he receives many emails and may not respond</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>associate: confirm promoted 2020+; fit based on name-matched papers only: check they are this person's</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -684,17 +688,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>University of California San Francisco</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bellini College of AI, Cybersecurity and Computing</t>
+          <t>Bioengineering and Therapeutic Sciences (Profiles dept Bioengineering)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ning Wang</t>
+          <t>Brian Cheung</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -714,57 +718,57 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>trustworthy-ML</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ACL (6) 1</t>
+          <t>ICML 3, Trans. Mach. Learn. Res. 2, WACV 1, NeurIPS 1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AI-type dept: Bellini College of AI, Cybersecurity and Comp</t>
+          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Federated learning, network intrusion detection, adversarial ML, differential privacy, LLMs in cybersecurity.</t>
+          <t>Bioengineering and therapeutic sciences; no research text on card.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ningw@usf.edu</t>
+          <t>bcheung@ucsf.edu</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/ning-wang.aspx</t>
+          <t>https://briancheung.github.io</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://trust-ai-lab.github.io/index.html</t>
+          <t>https://discolab.org/</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Learning from Textual Radiology Reports: A Benchmark Dataset for Coronary CT Angiography</t>
+          <t>Words That Make Language Models Perceive</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>EarlyShield: Early-Stage Screening for Robust Personalized Federated Learning</t>
+          <t>What if Eye...? Computationally Recreating Vision Evolution</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
+          <t>https://profiles.ucsf.edu/search/advanced (Department=Bioengineering)</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -774,26 +778,26 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Yes: Tasnimul Hossain Tomal joined SPRAI lab as a PhD student. (Aug. 2026; openings link on lab site not read)</t>
+          <t>Yes: Open positions Postdocs, students, and research engineers interested in AI for science.</t>
         </is>
       </c>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Contact Email: bcheung@ucsf.edu</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Agents/reliability and evaluation work connects loosely to trustworthy-AI security; federated medical imaging (Aegis) is the only bio link.</t>
+          <t>Convergent representations across modalities (Platonic Representation Hypothesis) connects to her BioCLIP+EfficientNet representation/evaluation work (arborphy) and probing/interpretability work (interp); AI for scientific discovery fits Bio-AI goal.</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>security-focused ML</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>dossier reader says B: Mostly AI security/privacy rather than core ML; in scope but weaker.; dossier recruiting: quote not on page, re-check</t>
-        </is>
-      </c>
+          <t>Input homepage was a UCSF Profiles page; true lab site is discolab.org; Dept is Bioengineering and Therapeutic Sciences (School of Pharmacy); doctoral program to apply through not stated (check BTS vs BMI); Lab described as 'post AGI' and 'Last updated: Oct 2026': very recently launched</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -801,17 +805,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Psychological &amp; Brain Sciences; Graduate Program for Neuroscience (faculty); Center for Systems Neuroscience</t>
+          <t>Bellini College of AI, Cybersecurity and Computing</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Arthur Lee</t>
+          <t>Ning Wang</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -826,56 +830,62 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NeuroAI</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>trustworthy-ML</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ACL (6) 1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
+          <t>AI-type dept: Bellini College of AI, Cybersecurity and Comp</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Card has no research text or papers.</t>
+          <t>Federated learning, network intrusion detection, adversarial ML, differential privacy, LLMs in cybersecurity.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>artlee@bu.edu</t>
+          <t>ningw@usf.edu</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/psych/profile/arthur-sangil-lee/</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/ning-wang.aspx</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>http://thedecodinglab.com/</t>
+          <t>https://trust-ai-lab.github.io/index.html</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Neural decoders: saving the baby from the bathwater</t>
+          <t>Learning from Textual Radiology Reports: A Benchmark Dataset for Coronary CT Angiography</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Distinguishing deception from its confounds by improving the validity of fMRI-based neural prediction</t>
+          <t>EarlyShield: Early-Stage Screening for Robust Personalized Federated Learning</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/psych/people/faculty/</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -885,28 +895,24 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Yes: We are looking for Ph.D. students interested in our research.</t>
+          <t>Yes: Tasnimul Hossain Tomal joined SPRAI lab as a PhD student. (Aug. 2026; openings link on lab site not read)</t>
         </is>
       </c>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Please feel free to send an email to Arthur (see contact) to let him know to look out for your application.</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>His interest in validating neural decoders (confounds, interpretability) connects to the EEG motor-imagery decoder with run-grouped validation.</t>
+          <t>Agents/reliability and evaluation work connects loosely to trustworthy-AI security; federated medical imaging (Aegis) is the only bio link.</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>psychology department; applications go through Psychology or Neuroscience program, not CS/Stats</t>
+          <t>security-focused ML</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>also listed as Arthur Sangil Lee</t>
+          <t>dossier reader says B: Mostly AI security/privacy rather than core ML; in scope but weaker.; dossier recruiting: quote not on page, re-check</t>
         </is>
       </c>
     </row>
@@ -916,17 +922,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cold Spring Harbor Laboratory</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CSHL Faculty (Research)</t>
+          <t>Psychological &amp; Brain Sciences; Graduate Program for Neuroscience (faculty); Center for Systems Neuroscience</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Helen Hou</t>
+          <t>Arthur Lee</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -949,9 +955,7 @@
           <t>NeuroAI</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
@@ -960,43 +964,39 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Brain-body motor control; ML video analysis and neural encoding from behavior via Gaussian splatting.</t>
+          <t>Card has no research text or papers.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>hou@cshl.edu</t>
+          <t>artlee@bu.edu</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>https://www.cshl.edu/research/faculty-staff/helen-hou/</t>
+          <t>https://www.bu.edu/psych/profile/arthur-sangil-lee/</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://houlab.org</t>
+          <t>http://thedecodinglab.com/</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Cheese3D enables sensitive detection and analysis of whole-face movement in mice</t>
+          <t>Neural decoders: saving the baby from the bathwater</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>A generic noninvasive neuromotor interface for human-computer interaction</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>A case study on the use of end-to-end real-time monitoring to ensure quality of oral solid dosage forms in pharmaceutical development. (2025) | Chemical genetic screens reveal defective lysosomal trafficking as synthetic lethal with NF1 loss (2024)</t>
-        </is>
-      </c>
+          <t>Distinguishing deception from its confounds by improving the validity of fMRI-based neural prediction</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.cshl.edu/research/faculty-staff/</t>
+          <t>https://www.bu.edu/psych/people/faculty/</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1006,24 +1006,28 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Yes: We are actively recruiting at all levels, including but not limited to Students, Postdocs, and Research Technicians.</t>
+          <t>Yes: We are looking for Ph.D. students interested in our research.</t>
         </is>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Please get in touch via hou [at] cshl.edu and include your CV/resume and contact information of three references. (IMPORTANT: Please include the term #hou_lab _ candidate somewhere in your message to slip through the spam filter) | *Please contact Helen before application if you are interested in applying to the CSHL or SBU programs and work in our lab.</t>
+          <t>Please feel free to send an email to Arthur (see contact) to let him know to look out for your application.</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Cheese3D (ML video analysis of facial movement) and the CSHL BioAI PhD program fit the applicant's interest in ML for biological/neural data (calcium imaging, EEG decoding).</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr"/>
+          <t>His interest in validating neural decoders (confounds, interpretability) connects to the EEG motor-imagery decoder with run-grouped validation.</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>psychology department; applications go through Psychology or Neuroscience program, not CS/Stats</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dossier start_year: no snapshot, re-check</t>
+          <t>also listed as Arthur Sangil Lee</t>
         </is>
       </c>
     </row>
@@ -1033,22 +1037,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Cold Spring Harbor Laboratory</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mechanical Eng &amp; Materials Science; Center for Computational &amp; Digital Health Innovation</t>
+          <t>CSHL Faculty (Research)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Boyuan Chen</t>
+          <t>Helen Hou</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Assistant Professor in the Thomas Lord Department of Mechanical Engineering and Mate</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1058,62 +1062,62 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>core-ML/CV</t>
+          <t>NeuroAI</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Trans. Mach. Learn. Res. 4, ICRA 3, CoRL 3, NeurIPS 1, IROS 1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AI-type dept: Mechanical Eng &amp; Materials Science</t>
+          <t>check which PhD program can admit (not a CS/Stat/DS dept)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Robotics: learns realistic lip motions for humanoid face robots; physical AI.</t>
+          <t>Brain-body motor control; ML video analysis and neural encoding from behavior via Gaussian splatting.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>boyuan.chen@duke.edu</t>
+          <t>hou@cshl.edu</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>https://mems.duke.edu/people/boyuan-chen/</t>
+          <t>https://www.cshl.edu/research/faculty-staff/helen-hou/</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>http://generalroboticslab.com/</t>
+          <t>https://houlab.org</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ORCH: Organizational Principles Enable Collective Intelligence in Embodied AI</t>
+          <t>Cheese3D enables sensitive detection and analysis of whole-face movement in mice</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Online Sim-to-Real Adaptation via Closed-Loop System Modeling</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
+          <t>A generic noninvasive neuromotor interface for human-computer interaction</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>A case study on the use of end-to-end real-time monitoring to ensure quality of oral solid dosage forms in pharmaceutical development. (2025) | Chemical genetic screens reveal defective lysosomal trafficking as synthetic lethal with NF1 loss (2024)</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://mems.duke.edu/people?s=&amp;group=faculty-primary,faculty-secondary</t>
+          <t>https://www.cshl.edu/research/faculty-staff/</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1123,20 +1127,24 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unspecified: </t>
+          <t>Yes: We are actively recruiting at all levels, including but not limited to Students, Postdocs, and Research Technicians.</t>
         </is>
       </c>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>robotics, little overlap with applicant projects</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Please get in touch via hou [at] cshl.edu and include your CV/resume and contact information of three references. (IMPORTANT: Please include the term #hou_lab _ candidate somewhere in your message to slip through the spam filter) | *Please contact Helen before application if you are interested in applying to the CSHL or SBU programs and work in our lab.</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Cheese3D (ML video analysis of facial movement) and the CSHL BioAI PhD program fit the applicant's interest in ML for biological/neural data (calcium imaging, EEG decoding).</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dossier reader says B: Robotics / physical intelligence; AI-for-science pillar is a stretch for Bio-AI goal. Not A.</t>
+          <t>dossier start_year: no snapshot, re-check</t>
         </is>
       </c>
     </row>
@@ -1146,22 +1154,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bellini College of AI, Cybersecurity and Computing</t>
+          <t>Mechanical Eng &amp; Materials Science; Center for Computational &amp; Digital Health Innovation</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fengchun Qiao</t>
+          <t>Boyuan Chen</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Assistant Professor in the Thomas Lord Department of Mechanical Engineering and Mate</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1176,57 +1184,57 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>trustworthy-ML</t>
+          <t>core-ML/CV</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ICML 2, CVPR 1, NeurIPS 1, ICLR 1, IEEE Trans. Pattern Anal. Mach. Intell. 1</t>
+          <t>Trans. Mach. Learn. Res. 4, ICRA 3, CoRL 3, NeurIPS 1, IROS 1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AI-type dept: Bellini College of AI, Cybersecurity and Comp</t>
+          <t>AI-type dept: Mechanical Eng &amp; Materials Science</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Trustworthy ML focused on out-of-distribution generalization, using robust optimization and graph theory.</t>
+          <t>Robotics: learns realistic lip motions for humanoid face robots; physical AI.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>fengchun@usf.edu</t>
+          <t>boyuan.chen@duke.edu</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/fengchun_qiao.aspx</t>
+          <t>https://mems.duke.edu/people/boyuan-chen/</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://joffery.github.io/joffery/</t>
+          <t>http://generalroboticslab.com/</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Structure-informed Risk Minimization for Robust Ensemble Learning</t>
+          <t>ORCH: Organizational Principles Enable Collective Intelligence in Embodied AI</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>SeafloorAI: A Large-scale Vision-Language Dataset for Seafloor Geological Survey</t>
+          <t>Online Sim-to-Real Adaptation via Closed-Loop System Modeling</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
+          <t>https://mems.duke.edu/people?s=&amp;group=faculty-primary,faculty-secondary</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1241,13 +1249,17 @@
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Arborphy BioCLIP fusion with leakage-aware evaluation connects to OOD generalization / distribution-shift robustness.</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>robotics, little overlap with applicant projects</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dossier reader says B: Robotics / physical intelligence; AI-for-science pillar is a stretch for Bio-AI goal. Not A.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1265,7 +1277,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Guangjing Wang</t>
+          <t>Fengchun Qiao</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1289,11 +1301,11 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ACL (Findings) 1, ACL (1) 1, CVPR 1</t>
+          <t>ICML 2, CVPR 1, NeurIPS 1, ICLR 1, IEEE Trans. Pattern Anal. Mach. Intell. 1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1303,32 +1315,36 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Adaptive attacks on audio watermarking and speech spoofing detector benchmarks; also soil sensing system.</t>
+          <t>Trustworthy ML focused on out-of-distribution generalization, using robust optimization and graph theory.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>guangjingwang@usf.edu</t>
+          <t>fengchun@usf.edu</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/guangjing-wang.aspx</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/fengchun_qiao.aspx</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/guangjing-wang.aspx</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>SoilNutri: A Passive Metasurface-based, Low-cost System for Soil Moisture and Nitrogen Monitoring (2026) | Learning to Evade: Adaptive Attacks on Audio Watermarking (2026)</t>
-        </is>
-      </c>
+          <t>https://joffery.github.io/joffery/</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Structure-informed Risk Minimization for Robust Ensemble Learning</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>SeafloorAI: A Large-scale Vision-Language Dataset for Seafloor Geological Survey</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
           <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
@@ -1348,23 +1364,15 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>multi-agent system with blind cross-model verification connects to his agentic-AI work.</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>no personal/lab site found after 2 searches; official page only</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>fit based on name-matched papers only: check they are this person's</t>
-        </is>
-      </c>
+          <t>Arborphy BioCLIP fusion with leakage-aware evaluation connects to OOD generalization / distribution-shift robustness.</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1373,12 +1381,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Bellini College of AI, Cybersecurity and Computing</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Xiaomin Lin</t>
+          <t>Guangjing Wang</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1398,61 +1406,53 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>core-ML/CV</t>
+          <t>trustworthy-ML</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ICRA 4, IROS 3, WACV (Workshops) 1, AAAI 1, ECCV (65) 1</t>
+          <t>ACL (Findings) 1, ACL (1) 1, CVPR 1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AI-type dept: Electrical Engineering</t>
+          <t>AI-type dept: Bellini College of AI, Cybersecurity and Comp</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Robotics, perception and edge AI for underwater and agricultural autonomy; deep learning rhino detection.</t>
+          <t>Adaptive attacks on audio watermarking and speech spoofing detector benchmarks; also soil sensing system.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>xlin2@usf.edu</t>
+          <t>guangjingwang@usf.edu</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/engineering/ece/faculty-staff/lin-xiaomin.aspx</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/guangjing-wang.aspx</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://xiaominlin.github.io/</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>WaterGen</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>RAZOR</t>
-        </is>
-      </c>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/guangjing-wang.aspx</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Automated rhinoceros detection in satellite imagery using deep learning (2025) | A Kinodynamic Model for Dubins-Based Trajectory Planning in Precision Oyster Harvesting (2025)</t>
+          <t>SoilNutri: A Passive Metasurface-based, Low-cost System for Soil Moisture and Nitrogen Monitoring (2026) | Learning to Evade: Adaptive Attacks on Audio Watermarking (2026)</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.usf.edu/engineering/ece/faculty-staff/index.aspx</t>
+          <t>https://www.usf.edu/ai-cybersecurity-computing/people/faculty/index.aspx</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1462,22 +1462,26 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Yes: I am actively recruiting PhD students to join my lab starting Spring 2027 and Fall 2027.</t>
+          <t xml:space="preserve">Unspecified: </t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Please read my Research Statement (PDF) before applying. | Competitive applicants typically hold an MS in a related field and have at least one top-tier publication. | Prospective students (not currently at USF) — fill out this application form . Please send an email to me as well, with your CV, transcripts, and a brief statement of your research interests and career goals. Tell me which of my papers or directions interest you and why. | You wrote the email yourself: Prospective Student - Bulls </t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>multi-agent system with blind cross-model verification connects to his agentic-AI work.</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>site requires AI-disclosure tag (subject 'Prospective Student - Bulls 3Q') for AI-drafted emails; expects &gt;=1 top-tier publication (applicant has none); paper titles are only short names on homepage news (WaterGen ECCV 2026, RAZOR CVPR 2026 Findings)</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr"/>
+          <t>no personal/lab site found after 2 searches; official page only</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>fit based on name-matched papers only: check they are this person's</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1485,91 +1489,91 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Electrical &amp; Computer Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Neil Gong</t>
+          <t>Xiaomin Lin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Associate Professor of Electrical and Computer Engineering</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>AI-for-science</t>
+          <t>core-ML/CV</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>NeurIPS 3, ICLR 2, ACL (1) 1, ACL (Findings) 1, EMNLP 1</t>
+          <t>ICRA 4, IROS 3, WACV (Workshops) 1, AAAI 1, ECCV (65) 1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AI-type dept: Electrical &amp; Computer Engineering</t>
+          <t>AI-type dept: Electrical Engineering</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Zero-shot autonomous microscopy for scalable characterization of 2D materials.</t>
+          <t>Robotics, perception and edge AI for underwater and agricultural autonomy; deep learning rhino detection.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>neil.gong@duke.edu</t>
+          <t>xlin2@usf.edu</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>https://ece.duke.edu/people/neil-gong/</t>
+          <t>https://www.usf.edu/engineering/ece/faculty-staff/lin-xiaomin.aspx</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://people.duke.edu/~zg70/index.html</t>
+          <t>https://xiaominlin.github.io/</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>A Critical Evaluation of Defenses against Prompt Injection Attacks</t>
+          <t>WaterGen</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Fingerprinting LLMs via Prompt Injection</t>
+          <t>RAZOR</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Zero-Shot Autonomous Microscopy for Scalable and Intelligent Characterization of 2D Materials (2025)</t>
+          <t>Automated rhinoceros detection in satellite imagery using deep learning (2025) | A Kinodynamic Model for Dubins-Based Trajectory Planning in Precision Oyster Harvesting (2025)</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://ece.duke.edu/faculty</t>
+          <t>https://www.usf.edu/engineering/ece/faculty-staff/index.aspx</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1579,26 +1583,22 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Yes: I am looking for postdocs, Ph.D. students, master's students, and undergraduate researchers. If you are interested in pursuing a Ph.D., please submit your application to Duke ECE.</t>
+          <t>Yes: I am actively recruiting PhD students to join my lab starting Spring 2027 and Fall 2027.</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>His work on evaluating prompt-injection defenses and secure agentic AI connects to my multi-agent system with verification and trust gating (agents).</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Please read my Research Statement (PDF) before applying. | Competitive applicants typically hold an MS in a related field and have at least one top-tier publication. | Prospective students (not currently at USF) — fill out this application form . Please send an email to me as well, with your CV, transcripts, and a brief statement of your research interests and career goals. Tell me which of my papers or directions interest you and why. | You wrote the email yourself: Prospective Student - Bulls </t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>first-pass summary describes different work (microscopy of 2D materials); possibly wrong person/mismatch; warns he receives many emails and may not respond</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>associate: confirm promoted 2020+; fit based on name-matched papers only: check they are this person's</t>
-        </is>
-      </c>
+          <t>site requires AI-disclosure tag (subject 'Prospective Student - Bulls 3Q') for AI-drafted emails; expects &gt;=1 top-tier publication (applicant has none); paper titles are only short names on homepage news (WaterGen ECCV 2026, RAZOR CVPR 2026 Findings)</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
